--- a/resources/Kururugi-ESC-calculs.xlsx
+++ b/resources/Kururugi-ESC-calculs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\binon\Desktop\Kururugi-ESC-Dev-Board\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B719D61D-B802-46CC-A52F-B60611813A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8DDC3F-6373-4753-9F00-32AF70384FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
   </bookViews>
@@ -1328,7 +1328,7 @@
         <v>0.42033333333333328</v>
       </c>
       <c r="G7" s="6">
-        <f t="shared" si="5"/>
+        <f>$N$9*D7*$N$14</f>
         <v>420.33333333333331</v>
       </c>
       <c r="H7" s="6">

--- a/resources/Kururugi-ESC-calculs.xlsx
+++ b/resources/Kururugi-ESC-calculs.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\binon\Desktop\Kururugi-ESC-Dev-Board\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8DDC3F-6373-4753-9F00-32AF70384FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C0B332-76E9-4EB3-8047-242D388BD131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Vsensing computation" sheetId="1" r:id="rId1"/>
     <sheet name="Isensing computation" sheetId="2" r:id="rId2"/>
+    <sheet name="Mosfet" sheetId="3" r:id="rId3"/>
+    <sheet name="Feuil2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="110">
   <si>
     <t>R1 (kOhm)</t>
   </si>
@@ -201,9 +203,6 @@
     <t>ADC range</t>
   </si>
   <si>
-    <t>Mean Ibus</t>
-  </si>
-  <si>
     <t>Maximal Ibus</t>
   </si>
   <si>
@@ -280,6 +279,107 @@
   </si>
   <si>
     <t>ADC total time</t>
+  </si>
+  <si>
+    <t>I_D</t>
+  </si>
+  <si>
+    <t>Duty cycle</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Drain-to-Source voltage</t>
+  </si>
+  <si>
+    <t>V_DS</t>
+  </si>
+  <si>
+    <t>Drain-to-Source electrical resistance</t>
+  </si>
+  <si>
+    <t>Rise time</t>
+  </si>
+  <si>
+    <t>t_r</t>
+  </si>
+  <si>
+    <t>Fall time</t>
+  </si>
+  <si>
+    <t>t_f</t>
+  </si>
+  <si>
+    <t>Switching frequency (PWM)</t>
+  </si>
+  <si>
+    <t>f_pwm</t>
+  </si>
+  <si>
+    <t>Drained current mean</t>
+  </si>
+  <si>
+    <r>
+      <t>m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ω</t>
+    </r>
+  </si>
+  <si>
+    <t>R_DS,on</t>
+  </si>
+  <si>
+    <t>P_cond</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Switching thermal losses</t>
+  </si>
+  <si>
+    <t>P_sw</t>
+  </si>
+  <si>
+    <t>P_tot</t>
+  </si>
+  <si>
+    <t>Conduction thermal losses max</t>
+  </si>
+  <si>
+    <t>Total thermal losses for ESC</t>
+  </si>
+  <si>
+    <t>Sizing the ESC for 4 motors at 15A</t>
+  </si>
+  <si>
+    <t>Sizing for max duty cycle of 95%</t>
+  </si>
+  <si>
+    <t>V2 will be rated for 20A</t>
+  </si>
+  <si>
+    <t>Rated for 64kHz without active cooling for v1</t>
+  </si>
+  <si>
+    <t>Term goal is 128kHz but will require review of the gate resistor setup</t>
+  </si>
+  <si>
+    <t>95% duty is the goal for v1</t>
+  </si>
+  <si>
+    <t>Dissipation of the mosfet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size </t>
   </si>
 </sst>
 </file>
@@ -292,7 +392,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,8 +423,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,6 +467,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -557,7 +669,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -621,6 +733,23 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -628,14 +757,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -650,27 +771,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1052,18 +1167,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B2" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="39"/>
       <c r="M2" s="8" t="s">
         <v>22</v>
       </c>
@@ -1097,10 +1212,10 @@
         <v>4</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>37</v>
@@ -1139,7 +1254,7 @@
         <v>0.1</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C24" si="0">B4/$N$5</f>
+        <f t="shared" ref="C4:C22" si="0">B4/$N$5</f>
         <v>1.4000000000000001</v>
       </c>
       <c r="D4" s="6">
@@ -1147,11 +1262,11 @@
         <v>0.14033333333333331</v>
       </c>
       <c r="E4" s="7">
-        <f t="shared" ref="E4:E24" si="1">$N$4/D4</f>
+        <f t="shared" ref="E4:E22" si="1">$N$4/D4</f>
         <v>21.37767220902613</v>
       </c>
       <c r="F4" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D4,$N$23*(0.1)*D4)</f>
+        <f t="shared" ref="F4:F33" si="2">IF($N$9=0,$N$23*($N$8+$N$7)*D4,$N$23*(0.1)*D4)</f>
         <v>0.14033333333333331</v>
       </c>
       <c r="G4" s="6">
@@ -1167,15 +1282,15 @@
         <v>416.66666666666663</v>
       </c>
       <c r="J4" s="7">
-        <f>I4*$R$10/1000</f>
+        <f t="shared" ref="J4:J33" si="3">I4*$R$10/1000</f>
         <v>33.333333333333329</v>
       </c>
       <c r="K4" s="7">
-        <f>I4*$R$11/1000</f>
+        <f t="shared" ref="K4:K33" si="4">I4*$R$11/1000</f>
         <v>62.499999999999993</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N4" s="2">
         <v>3</v>
@@ -1203,7 +1318,7 @@
         <v>2.8000000000000003</v>
       </c>
       <c r="D5" s="6">
-        <f t="shared" ref="D5:D33" si="2">B5*C5/(B5+C5)+$N$17/1000</f>
+        <f t="shared" ref="D5:D33" si="5">B5*C5/(B5+C5)+$N$17/1000</f>
         <v>0.23366666666666663</v>
       </c>
       <c r="E5" s="7">
@@ -1211,7 +1326,7 @@
         <v>12.83880171184023</v>
       </c>
       <c r="F5" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D5,$N$23*(0.1)*D5)</f>
+        <f t="shared" si="2"/>
         <v>0.23366666666666663</v>
       </c>
       <c r="G5" s="6">
@@ -1219,19 +1334,19 @@
         <v>233.66666666666663</v>
       </c>
       <c r="H5" s="6">
-        <f t="shared" ref="H5:H33" si="3">1/(2*PI()*($N$8+$N$7+$N$9)*D5)*1000</f>
+        <f t="shared" ref="H5:H33" si="6">1/(2*PI()*($N$8+$N$7+$N$9)*D5)*1000</f>
         <v>5.9227790023653926</v>
       </c>
       <c r="I5" s="7">
-        <f t="shared" ref="I5:I13" si="4">$N$3*$N$3/(C5+B5)</f>
+        <f t="shared" ref="I5:I13" si="7">$N$3*$N$3/(C5+B5)</f>
         <v>208.33333333333331</v>
       </c>
       <c r="J5" s="7">
-        <f>I5*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>16.666666666666664</v>
       </c>
       <c r="K5" s="7">
-        <f>I5*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>31.249999999999996</v>
       </c>
       <c r="M5" s="8" t="s">
@@ -1264,7 +1379,7 @@
         <v>4.2</v>
       </c>
       <c r="D6" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.32700000000000001</v>
       </c>
       <c r="E6" s="7">
@@ -1272,38 +1387,38 @@
         <v>9.1743119266055047</v>
       </c>
       <c r="F6" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D6,$N$23*(0.1)*D6)</f>
+        <f t="shared" si="2"/>
         <v>0.32700000000000001</v>
       </c>
       <c r="G6" s="6">
-        <f t="shared" ref="G6:G33" si="5">$N$9*D6*$N$14</f>
+        <f t="shared" ref="G6:G33" si="8">$N$9*D6*$N$14</f>
         <v>327</v>
       </c>
       <c r="H6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4.2322814277860745</v>
       </c>
       <c r="I6" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>138.88888888888889</v>
       </c>
       <c r="J6" s="7">
-        <f>I6*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>11.111111111111111</v>
       </c>
       <c r="K6" s="7">
-        <f>I6*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>20.833333333333332</v>
       </c>
       <c r="N6" s="1"/>
       <c r="Q6" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R6" s="7">
         <f>N22</f>
         <v>41.666666666666664</v>
       </c>
-      <c r="S6" s="32" t="s">
+      <c r="S6" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1316,7 +1431,7 @@
         <v>5.6000000000000005</v>
       </c>
       <c r="D7" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.42033333333333328</v>
       </c>
       <c r="E7" s="7">
@@ -1324,7 +1439,7 @@
         <v>7.1371927042030148</v>
       </c>
       <c r="F7" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D7,$N$23*(0.1)*D7)</f>
+        <f t="shared" si="2"/>
         <v>0.42033333333333328</v>
       </c>
       <c r="G7" s="6">
@@ -1332,19 +1447,19 @@
         <v>420.33333333333331</v>
       </c>
       <c r="H7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.2925202860096268</v>
       </c>
       <c r="I7" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>104.16666666666666</v>
       </c>
       <c r="J7" s="7">
-        <f>I7*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="K7" s="7">
-        <f>I7*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>15.624999999999998</v>
       </c>
       <c r="M7" s="8" t="s">
@@ -1357,13 +1472,13 @@
         <v>9</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R7" s="9">
         <f>R2/N21*1000</f>
         <v>200</v>
       </c>
-      <c r="S7" s="32" t="s">
+      <c r="S7" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1376,7 +1491,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.51366666666666672</v>
       </c>
       <c r="E8" s="7">
@@ -1384,27 +1499,27 @@
         <v>5.8403634003893572</v>
       </c>
       <c r="F8" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D8,$N$23*(0.1)*D8)</f>
+        <f t="shared" si="2"/>
         <v>0.51366666666666672</v>
       </c>
       <c r="G8" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>513.66666666666674</v>
       </c>
       <c r="H8" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2.6942687090578445</v>
       </c>
       <c r="I8" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>83.333333333333329</v>
       </c>
       <c r="J8" s="7">
-        <f>I8*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>6.6666666666666661</v>
       </c>
       <c r="K8" s="7">
-        <f>I8*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>12.5</v>
       </c>
       <c r="M8" s="8" t="s">
@@ -1417,13 +1532,13 @@
         <v>9</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R8" s="7">
         <f>R7+R6</f>
         <v>241.66666666666666</v>
       </c>
-      <c r="S8" s="32" t="s">
+      <c r="S8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1436,7 +1551,7 @@
         <v>8.4</v>
       </c>
       <c r="D9" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.6070000000000001</v>
       </c>
       <c r="E9" s="7">
@@ -1444,27 +1559,27 @@
         <v>4.942339373970345</v>
       </c>
       <c r="F9" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D9,$N$23*(0.1)*D9)</f>
+        <f t="shared" si="2"/>
         <v>0.6070000000000001</v>
       </c>
       <c r="G9" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>607.00000000000011</v>
       </c>
       <c r="H9" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2.2799934545074896</v>
       </c>
       <c r="I9" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>69.444444444444443</v>
       </c>
       <c r="J9" s="7">
-        <f>I9*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>5.5555555555555554</v>
       </c>
       <c r="K9" s="7">
-        <f>I9*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>10.416666666666666</v>
       </c>
       <c r="M9" s="8" t="s">
@@ -1486,7 +1601,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="D10" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.70033333333333336</v>
       </c>
       <c r="E10" s="7">
@@ -1494,27 +1609,27 @@
         <v>4.2836744407425034</v>
       </c>
       <c r="F10" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D10,$N$23*(0.1)*D10)</f>
+        <f t="shared" si="2"/>
         <v>0.70033333333333336</v>
       </c>
       <c r="G10" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>700.33333333333326</v>
       </c>
       <c r="H10" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.9761390198277671</v>
       </c>
       <c r="I10" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>59.523809523809526</v>
       </c>
       <c r="J10" s="7">
-        <f>I10*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>4.7619047619047628</v>
       </c>
       <c r="K10" s="7">
-        <f>I10*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>8.9285714285714288</v>
       </c>
       <c r="M10" s="8" t="s">
@@ -1545,7 +1660,7 @@
         <v>11.200000000000001</v>
       </c>
       <c r="D11" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.79366666666666663</v>
       </c>
       <c r="E11" s="7">
@@ -1553,27 +1668,27 @@
         <v>3.7799244015119697</v>
       </c>
       <c r="F11" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D11,$N$23*(0.1)*D11)</f>
+        <f t="shared" si="2"/>
         <v>0.79366666666666663</v>
       </c>
       <c r="G11" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>793.66666666666663</v>
       </c>
       <c r="H11" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.7437497188820406</v>
       </c>
       <c r="I11" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>52.083333333333329</v>
       </c>
       <c r="J11" s="7">
-        <f>I11*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>4.1666666666666661</v>
       </c>
       <c r="K11" s="7">
-        <f>I11*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>7.8124999999999991</v>
       </c>
       <c r="M11" s="8" t="s">
@@ -1604,7 +1719,7 @@
         <v>12.600000000000001</v>
       </c>
       <c r="D12" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.88700000000000001</v>
       </c>
       <c r="E12" s="7">
@@ -1612,27 +1727,27 @@
         <v>3.3821871476888385</v>
       </c>
       <c r="F12" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D12,$N$23*(0.1)*D12)</f>
+        <f t="shared" si="2"/>
         <v>0.88700000000000001</v>
       </c>
       <c r="G12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>887</v>
       </c>
       <c r="H12" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.5602660957001651</v>
       </c>
       <c r="I12" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>46.296296296296291</v>
       </c>
       <c r="J12" s="7">
-        <f>I12*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>3.7037037037037033</v>
       </c>
       <c r="K12" s="7">
-        <f>I12*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>6.9444444444444438</v>
       </c>
       <c r="M12" s="8" t="s">
@@ -1664,7 +1779,7 @@
         <v>14</v>
       </c>
       <c r="D13" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.98033333333333339</v>
       </c>
       <c r="E13" s="7">
@@ -1672,27 +1787,27 @@
         <v>3.0601836110166607</v>
       </c>
       <c r="F13" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D13,$N$23*(0.1)*D13)</f>
+        <f t="shared" si="2"/>
         <v>0.98033333333333339</v>
       </c>
       <c r="G13" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>980.33333333333348</v>
       </c>
       <c r="H13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.4117198506148039</v>
       </c>
       <c r="I13" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>41.666666666666664</v>
       </c>
       <c r="J13" s="7">
-        <f>I13*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>3.333333333333333</v>
       </c>
       <c r="K13" s="7">
-        <f>I13*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>6.25</v>
       </c>
       <c r="M13" s="8" t="s">
@@ -1715,7 +1830,7 @@
         <v>15.400000000000002</v>
       </c>
       <c r="D14" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.0736666666666668</v>
       </c>
       <c r="E14" s="7">
@@ -1723,31 +1838,31 @@
         <v>2.7941633033219495</v>
       </c>
       <c r="F14" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D14,$N$23*(0.1)*D14)</f>
+        <f t="shared" si="2"/>
         <v>1.0736666666666668</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1073.6666666666667</v>
       </c>
       <c r="H14" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.2889997145787455</v>
       </c>
       <c r="I14" s="7">
-        <f t="shared" ref="I14:I21" si="6">$N$3*$N$3/(C14+B14)</f>
+        <f t="shared" ref="I14:I21" si="9">$N$3*$N$3/(C14+B14)</f>
         <v>37.878787878787868</v>
       </c>
       <c r="J14" s="7">
-        <f>I14*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>3.0303030303030294</v>
       </c>
       <c r="K14" s="7">
-        <f>I14*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>5.6818181818181799</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N14" s="2">
         <f>N23</f>
@@ -1769,7 +1884,7 @@
         <v>16.8</v>
       </c>
       <c r="D15" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.167</v>
       </c>
       <c r="E15" s="7">
@@ -1777,27 +1892,27 @@
         <v>2.5706940874035991</v>
       </c>
       <c r="F15" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D15,$N$23*(0.1)*D15)</f>
+        <f t="shared" si="2"/>
         <v>1.167</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1167</v>
       </c>
       <c r="H15" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.1859091918475118</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>34.722222222222221</v>
       </c>
       <c r="J15" s="7">
-        <f>I15*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>2.7777777777777777</v>
       </c>
       <c r="K15" s="7">
-        <f>I15*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>5.208333333333333</v>
       </c>
       <c r="M15" s="8" t="s">
@@ -1823,7 +1938,7 @@
         <v>18.200000000000003</v>
       </c>
       <c r="D16" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.2603333333333333</v>
       </c>
       <c r="E16" s="7">
@@ -1831,36 +1946,36 @@
         <v>2.3803226659613861</v>
       </c>
       <c r="F16" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D16,$N$23*(0.1)*D16)</f>
+        <f t="shared" si="2"/>
         <v>1.2603333333333333</v>
       </c>
       <c r="G16" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1260.3333333333333</v>
       </c>
       <c r="H16" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.0980872998302404</v>
       </c>
       <c r="I16" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>32.051282051282044</v>
       </c>
       <c r="J16" s="7">
-        <f>I16*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>2.5641025641025634</v>
       </c>
       <c r="K16" s="7">
-        <f>I16*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>4.8076923076923066</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N16" s="2">
         <v>480</v>
       </c>
-      <c r="O16" s="32" t="s">
+      <c r="O16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="Q16" s="10" t="s">
@@ -1876,7 +1991,7 @@
         <v>19.600000000000001</v>
       </c>
       <c r="D17" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.3536666666666666</v>
       </c>
       <c r="E17" s="7">
@@ -1884,37 +1999,37 @@
         <v>2.2162029056882542</v>
       </c>
       <c r="F17" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D17,$N$23*(0.1)*D17)</f>
+        <f t="shared" si="2"/>
         <v>1.3536666666666666</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1353.6666666666665</v>
       </c>
       <c r="H17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.0223757893765426</v>
       </c>
       <c r="I17" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>29.761904761904763</v>
       </c>
       <c r="J17" s="7">
-        <f>I17*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>2.3809523809523814</v>
       </c>
       <c r="K17" s="7">
-        <f>I17*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>4.4642857142857144</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N17" s="2">
         <v>47</v>
       </c>
-      <c r="O17" s="32" t="s">
-        <v>77</v>
+      <c r="O17" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1926,7 +2041,7 @@
         <v>21</v>
       </c>
       <c r="D18" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.4469999999999998</v>
       </c>
       <c r="E18" s="7">
@@ -1934,27 +2049,27 @@
         <v>2.0732550103662755</v>
       </c>
       <c r="F18" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D18,$N$23*(0.1)*D18)</f>
+        <f t="shared" si="2"/>
         <v>1.4469999999999998</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1447</v>
       </c>
       <c r="H18" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.95643125562269971</v>
       </c>
       <c r="I18" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>27.777777777777779</v>
       </c>
       <c r="J18" s="7">
-        <f>I18*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>2.2222222222222223</v>
       </c>
       <c r="K18" s="7">
-        <f>I18*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q18" t="s">
@@ -1970,7 +2085,7 @@
         <v>22.400000000000002</v>
       </c>
       <c r="D19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.5403333333333331</v>
       </c>
       <c r="E19" s="7">
@@ -1978,34 +2093,34 @@
         <v>1.9476303830339756</v>
       </c>
       <c r="F19" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D19,$N$23*(0.1)*D19)</f>
+        <f t="shared" si="2"/>
         <v>1.5403333333333331</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1540.333333333333</v>
       </c>
       <c r="H19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.89847826891541649</v>
       </c>
       <c r="I19" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>26.041666666666664</v>
       </c>
       <c r="J19" s="7">
-        <f>I19*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>2.083333333333333</v>
       </c>
       <c r="K19" s="7">
-        <f>I19*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>3.9062499999999996</v>
       </c>
-      <c r="M19" s="27" t="s">
+      <c r="M19" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="N19" s="28"/>
-      <c r="O19" s="29"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="36"/>
       <c r="Q19" t="s">
         <v>20</v>
       </c>
@@ -2019,7 +2134,7 @@
         <v>23.8</v>
       </c>
       <c r="D20" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.6336666666666666</v>
       </c>
       <c r="E20" s="7">
@@ -2027,27 +2142,27 @@
         <v>1.836359926545603</v>
       </c>
       <c r="F20" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D20,$N$23*(0.1)*D20)</f>
+        <f t="shared" si="2"/>
         <v>1.6336666666666666</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1633.6666666666667</v>
       </c>
       <c r="H20" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.84714712929160152</v>
       </c>
       <c r="I20" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>24.509803921568629</v>
       </c>
       <c r="J20" s="7">
-        <f>I20*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>1.9607843137254903</v>
       </c>
       <c r="K20" s="7">
-        <f>I20*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>3.6764705882352944</v>
       </c>
       <c r="M20" s="12" t="s">
@@ -2072,7 +2187,7 @@
         <v>25.200000000000003</v>
       </c>
       <c r="D21" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.7269999999999999</v>
       </c>
       <c r="E21" s="7">
@@ -2080,27 +2195,27 @@
         <v>1.7371163867979156</v>
       </c>
       <c r="F21" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D21,$N$23*(0.1)*D21)</f>
+        <f t="shared" si="2"/>
         <v>1.7269999999999999</v>
       </c>
       <c r="G21" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1727</v>
       </c>
       <c r="H21" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.80136423097049603</v>
       </c>
       <c r="I21" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>23.148148148148145</v>
       </c>
       <c r="J21" s="7">
-        <f>I21*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>1.8518518518518516</v>
       </c>
       <c r="K21" s="7">
-        <f>I21*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>3.4722222222222219</v>
       </c>
       <c r="M21" s="12" t="s">
@@ -2122,7 +2237,7 @@
         <v>26.6</v>
       </c>
       <c r="D22" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.8203333333333331</v>
       </c>
       <c r="E22" s="7">
@@ -2130,27 +2245,27 @@
         <v>1.6480498077275225</v>
       </c>
       <c r="F22" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D22,$N$23*(0.1)*D22)</f>
+        <f t="shared" si="2"/>
         <v>1.8203333333333331</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1820.333333333333</v>
       </c>
       <c r="H22" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.76027615467096499</v>
       </c>
       <c r="I22" s="7">
-        <f t="shared" ref="I22" si="7">$N$3*$N$3/(C22+B22)</f>
+        <f t="shared" ref="I22" si="10">$N$3*$N$3/(C22+B22)</f>
         <v>21.92982456140351</v>
       </c>
       <c r="J22" s="7">
-        <f>I22*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>1.7543859649122808</v>
       </c>
       <c r="K22" s="7">
-        <f>I22*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>3.2894736842105265</v>
       </c>
       <c r="M22" s="12" t="s">
@@ -2169,43 +2284,43 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <f>B23/$N$5</f>
+        <f t="shared" ref="C23:C33" si="11">B23/$N$5</f>
         <v>28</v>
       </c>
       <c r="D23" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.9136666666666666</v>
       </c>
       <c r="E23" s="7">
-        <f>$N$4/D23</f>
+        <f t="shared" ref="E23:E33" si="12">$N$4/D23</f>
         <v>1.567671137432503</v>
       </c>
       <c r="F23" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D23,$N$23*(0.1)*D23)</f>
+        <f t="shared" si="2"/>
         <v>1.9136666666666666</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1913.6666666666667</v>
       </c>
       <c r="H23" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.72319597294167204</v>
       </c>
       <c r="I23" s="7">
-        <f>$N$3*$N$3/(C23+B23)</f>
+        <f t="shared" ref="I23:I33" si="13">$N$3*$N$3/(C23+B23)</f>
         <v>20.833333333333332</v>
       </c>
       <c r="J23" s="7">
-        <f>I23*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>1.6666666666666665</v>
       </c>
       <c r="K23" s="7">
-        <f>I23*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>3.125</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N23" s="2">
         <v>10</v>
@@ -2219,39 +2334,39 @@
         <v>3</v>
       </c>
       <c r="C24" s="5">
-        <f>B24/$N$5</f>
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
       <c r="D24" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.847</v>
       </c>
       <c r="E24" s="7">
-        <f>$N$4/D24</f>
+        <f t="shared" si="12"/>
         <v>1.053740779768177</v>
       </c>
       <c r="F24" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D24,$N$23*(0.1)*D24)</f>
+        <f t="shared" si="2"/>
         <v>2.847</v>
       </c>
       <c r="G24" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2847</v>
       </c>
       <c r="H24" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.48611030097859032</v>
       </c>
       <c r="I24" s="7">
-        <f>$N$3*$N$3/(C24+B24)</f>
+        <f t="shared" si="13"/>
         <v>13.888888888888889</v>
       </c>
       <c r="J24" s="7">
-        <f>I24*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="K24" s="7">
-        <f>I24*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>2.0833333333333335</v>
       </c>
       <c r="M24" s="12" t="s">
@@ -2270,39 +2385,39 @@
         <v>4</v>
       </c>
       <c r="C25" s="5">
-        <f>B25/$N$5</f>
+        <f t="shared" si="11"/>
         <v>56</v>
       </c>
       <c r="D25" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3.7803333333333335</v>
       </c>
       <c r="E25" s="7">
-        <f>$N$4/D25</f>
+        <f t="shared" si="12"/>
         <v>0.79358081297945504</v>
       </c>
       <c r="F25" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D25,$N$23*(0.1)*D25)</f>
+        <f t="shared" si="2"/>
         <v>3.7803333333333335</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3780.3333333333335</v>
       </c>
       <c r="H25" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.36609364964801505</v>
       </c>
       <c r="I25" s="7">
-        <f>$N$3*$N$3/(C25+B25)</f>
+        <f t="shared" si="13"/>
         <v>10.416666666666666</v>
       </c>
       <c r="J25" s="7">
-        <f>I25*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>0.83333333333333326</v>
       </c>
       <c r="K25" s="7">
-        <f>I25*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>1.5625</v>
       </c>
       <c r="M25" s="12" t="s">
@@ -2321,50 +2436,50 @@
         <v>5</v>
       </c>
       <c r="C26" s="5">
-        <f>B26/$N$5</f>
+        <f t="shared" si="11"/>
         <v>70</v>
       </c>
       <c r="D26" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4.7136666666666667</v>
       </c>
       <c r="E26" s="7">
-        <f>$N$4/D26</f>
+        <f t="shared" si="12"/>
         <v>0.6364472102397285</v>
       </c>
       <c r="F26" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D26,$N$23*(0.1)*D26)</f>
+        <f t="shared" si="2"/>
         <v>4.7136666666666667</v>
       </c>
       <c r="G26" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>4713.666666666667</v>
       </c>
       <c r="H26" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.29360498413536096</v>
       </c>
       <c r="I26" s="7">
-        <f>$N$3*$N$3/(C26+B26)</f>
+        <f t="shared" si="13"/>
         <v>8.3333333333333339</v>
       </c>
       <c r="J26" s="7">
-        <f>I26*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="K26" s="7">
-        <f>I26*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>1.25</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="N26" s="46">
+      <c r="N26" s="33">
         <f>R4*N25*1000</f>
         <v>2.0429968393118183</v>
       </c>
-      <c r="O26" s="45" t="s">
-        <v>58</v>
+      <c r="O26" s="32" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2372,39 +2487,39 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <f>B27/$N$5</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="D27" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5.6469999999999994</v>
       </c>
       <c r="E27" s="7">
-        <f>$N$4/D27</f>
+        <f t="shared" si="12"/>
         <v>0.53125553391181168</v>
       </c>
       <c r="F27" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D27,$N$23*(0.1)*D27)</f>
+        <f t="shared" si="2"/>
         <v>5.6469999999999994</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>5646.9999999999991</v>
       </c>
       <c r="H27" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.24507809932460536</v>
       </c>
       <c r="I27" s="7">
-        <f>$N$3*$N$3/(C27+B27)</f>
+        <f t="shared" si="13"/>
         <v>6.9444444444444446</v>
       </c>
       <c r="J27" s="7">
-        <f>I27*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="K27" s="7">
-        <f>I27*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>1.0416666666666667</v>
       </c>
       <c r="M27" s="14" t="s">
@@ -2423,39 +2538,39 @@
         <v>7</v>
       </c>
       <c r="C28" s="5">
-        <f>B28/$N$5</f>
+        <f t="shared" si="11"/>
         <v>98</v>
       </c>
       <c r="D28" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.5803333333333329</v>
       </c>
       <c r="E28" s="7">
-        <f>$N$4/D28</f>
+        <f t="shared" si="12"/>
         <v>0.45590395623322022</v>
       </c>
       <c r="F28" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D28,$N$23*(0.1)*D28)</f>
+        <f t="shared" si="2"/>
         <v>6.5803333333333329</v>
       </c>
       <c r="G28" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>6580.333333333333</v>
       </c>
       <c r="H28" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.21031700930338582</v>
       </c>
       <c r="I28" s="7">
-        <f>$N$3*$N$3/(C28+B28)</f>
+        <f t="shared" si="13"/>
         <v>5.9523809523809526</v>
       </c>
       <c r="J28" s="7">
-        <f>I28*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>0.47619047619047622</v>
       </c>
       <c r="K28" s="7">
-        <f>I28*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>0.8928571428571429</v>
       </c>
     </row>
@@ -2464,43 +2579,43 @@
         <v>8</v>
       </c>
       <c r="C29" s="5">
-        <f>B29/$N$5</f>
+        <f t="shared" si="11"/>
         <v>112</v>
       </c>
       <c r="D29" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7.5136666666666665</v>
       </c>
       <c r="E29" s="7">
-        <f>$N$4/D29</f>
+        <f t="shared" si="12"/>
         <v>0.3992724368927732</v>
       </c>
       <c r="F29" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D29,$N$23*(0.1)*D29)</f>
+        <f t="shared" si="2"/>
         <v>7.5136666666666665</v>
       </c>
       <c r="G29" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>7513.666666666667</v>
       </c>
       <c r="H29" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.18419183180241067</v>
       </c>
       <c r="I29" s="7">
-        <f>$N$3*$N$3/(C29+B29)</f>
+        <f t="shared" si="13"/>
         <v>5.208333333333333</v>
       </c>
       <c r="J29" s="7">
-        <f>I29*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>0.41666666666666663</v>
       </c>
       <c r="K29" s="7">
-        <f>I29*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>0.78125</v>
       </c>
-      <c r="M29" s="30" t="s">
-        <v>74</v>
+      <c r="M29" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.35">
@@ -2508,39 +2623,39 @@
         <v>9</v>
       </c>
       <c r="C30" s="5">
-        <f>B30/$N$5</f>
+        <f t="shared" si="11"/>
         <v>126</v>
       </c>
       <c r="D30" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>8.447000000000001</v>
       </c>
       <c r="E30" s="7">
-        <f>$N$4/D30</f>
+        <f t="shared" si="12"/>
         <v>0.35515567657156383</v>
       </c>
       <c r="F30" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D30,$N$23*(0.1)*D30)</f>
+        <f t="shared" si="2"/>
         <v>8.447000000000001</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>8447</v>
       </c>
       <c r="H30" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.16383994635800239</v>
       </c>
       <c r="I30" s="7">
-        <f>$N$3*$N$3/(C30+B30)</f>
+        <f t="shared" si="13"/>
         <v>4.6296296296296298</v>
       </c>
       <c r="J30" s="7">
-        <f>I30*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>0.37037037037037041</v>
       </c>
       <c r="K30" s="7">
-        <f>I30*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>0.69444444444444442</v>
       </c>
     </row>
@@ -2549,39 +2664,39 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <f>B31/$N$5</f>
+        <f t="shared" si="11"/>
         <v>140</v>
       </c>
       <c r="D31" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9.3803333333333345</v>
       </c>
       <c r="E31" s="7">
-        <f>$N$4/D31</f>
+        <f t="shared" si="12"/>
         <v>0.31981805905973487</v>
       </c>
       <c r="F31" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D31,$N$23*(0.1)*D31)</f>
+        <f t="shared" si="2"/>
         <v>9.3803333333333345</v>
       </c>
       <c r="G31" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>9380.3333333333339</v>
       </c>
       <c r="H31" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.14753804344757254</v>
       </c>
       <c r="I31" s="7">
-        <f>$N$3*$N$3/(C31+B31)</f>
+        <f t="shared" si="13"/>
         <v>4.166666666666667</v>
       </c>
       <c r="J31" s="7">
-        <f>I31*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>0.33333333333333337</v>
       </c>
       <c r="K31" s="7">
-        <f>I31*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>0.625</v>
       </c>
     </row>
@@ -2590,39 +2705,39 @@
         <v>20</v>
       </c>
       <c r="C32" s="5">
-        <f>B32/$N$5</f>
+        <f t="shared" si="11"/>
         <v>280</v>
       </c>
       <c r="D32" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>18.713666666666668</v>
       </c>
       <c r="E32" s="7">
-        <f>$N$4/D32</f>
+        <f t="shared" si="12"/>
         <v>0.1603106464081509</v>
       </c>
       <c r="F32" s="6">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D32,$N$23*(0.1)*D32)</f>
+        <f t="shared" si="2"/>
         <v>18.713666666666668</v>
       </c>
       <c r="G32" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>18713.666666666668</v>
       </c>
       <c r="H32" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.3954295090186112E-2</v>
       </c>
       <c r="I32" s="7">
-        <f>$N$3*$N$3/(C32+B32)</f>
+        <f t="shared" si="13"/>
         <v>2.0833333333333335</v>
       </c>
       <c r="J32" s="7">
-        <f>I32*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>0.16666666666666669</v>
       </c>
       <c r="K32" s="7">
-        <f>I32*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>0.3125</v>
       </c>
     </row>
@@ -2631,39 +2746,39 @@
         <v>1.3068</v>
       </c>
       <c r="C33" s="22">
-        <f>B33/$N$5</f>
+        <f t="shared" si="11"/>
         <v>18.295200000000001</v>
       </c>
       <c r="D33" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1.26668</v>
       </c>
       <c r="E33" s="20">
-        <f>$N$4/D33</f>
+        <f t="shared" si="12"/>
         <v>2.3683961221460827</v>
       </c>
       <c r="F33" s="25">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D33,$N$23*(0.1)*D33)</f>
+        <f t="shared" si="2"/>
         <v>1.26668</v>
       </c>
       <c r="G33" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1266.68</v>
       </c>
       <c r="H33" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1.0925853624325372</v>
       </c>
       <c r="I33" s="20">
-        <f>$N$3*$N$3/(C33+B33)</f>
+        <f t="shared" si="13"/>
         <v>31.884501581471277</v>
       </c>
       <c r="J33" s="20">
-        <f>I33*$R$10/1000</f>
+        <f t="shared" si="3"/>
         <v>2.5507601265177025</v>
       </c>
       <c r="K33" s="20">
-        <f>I33*$R$11/1000</f>
+        <f t="shared" si="4"/>
         <v>4.7826752372206913</v>
       </c>
     </row>
@@ -2673,8 +2788,8 @@
       <c r="D34" s="24"/>
       <c r="E34" s="24"/>
       <c r="F34" s="26"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="40"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="29"/>
       <c r="I34" s="24"/>
       <c r="J34" s="24"/>
       <c r="K34" s="24"/>
@@ -2698,7 +2813,7 @@
         <f>IF($N$9=0,$N$23*($N$8+$N$7)*D35,$N$23*(0.1)*D35)</f>
         <v>1.2023121387283238</v>
       </c>
-      <c r="G35" s="41">
+      <c r="G35" s="6">
         <f>C35*D35*$N$14</f>
         <v>192.36994219653181</v>
       </c>
@@ -2720,7 +2835,7 @@
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="G36" s="43"/>
+      <c r="G36" s="30"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.35">
       <c r="F37" s="11" t="s">
@@ -2738,9 +2853,10 @@
     <mergeCell ref="M19:O19"/>
     <mergeCell ref="B2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H4:H35">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
-      <formula>$N$10/1000*$N$11</formula>
+  <conditionalFormatting sqref="F4:F35">
+    <cfRule type="cellIs" dxfId="2" priority="14" operator="between">
+      <formula>0</formula>
+      <formula>$N$22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G36">
@@ -2748,10 +2864,9 @@
       <formula>$N$16</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F35">
-    <cfRule type="cellIs" dxfId="0" priority="14" operator="between">
-      <formula>0</formula>
-      <formula>$N$22</formula>
+  <conditionalFormatting sqref="H4:H35">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>$N$10/1000*$N$11</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2761,7 +2876,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CCAFF9-1F43-40BD-BD89-61BF0CE5890D}">
-  <dimension ref="B2:K16"/>
+  <dimension ref="B2:K17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2778,36 +2893,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B3" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B3" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="G3" s="33" t="s">
-        <v>68</v>
-      </c>
       <c r="I3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J3" s="2">
         <v>200</v>
@@ -2822,58 +2937,52 @@
         <v>100</v>
       </c>
       <c r="C4" s="6">
-        <f>B4*$J$7*$J$7/1000/1000*$J$6/100</f>
-        <v>0.34199999999999997</v>
+        <f t="shared" ref="C4:C14" si="0">B4*$J$7*$J$7/1000/1000*$J$6/100</f>
+        <v>2.1374999999999998E-2</v>
       </c>
       <c r="D4" s="9">
-        <f>$J$7*B4/1000</f>
-        <v>6</v>
+        <f t="shared" ref="D4:D14" si="1">$J$7*B4/1000</f>
+        <v>1.5</v>
       </c>
       <c r="E4" s="9">
-        <f>D4/$J$12</f>
-        <v>7.4472727272727273</v>
+        <f t="shared" ref="E4:E14" si="2">D4/$J$12</f>
+        <v>1.8618181818181818</v>
       </c>
       <c r="F4" s="9">
-        <f>D4/$J$12*$J$13</f>
-        <v>476.62545454545455</v>
+        <f t="shared" ref="F4:F14" si="3">D4/$J$12*$J$13</f>
+        <v>119.15636363636364</v>
       </c>
       <c r="G4" s="6">
-        <f>$J$7/F4*1000</f>
+        <f t="shared" ref="G4:G14" si="4">$J$7/F4*1000</f>
         <v>125.885009765625</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="2">
-        <v>90</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B5" s="44">
+      <c r="B5" s="50">
         <f>B4+100</f>
         <v>200</v>
       </c>
-      <c r="C5" s="39">
-        <f>B5*$J$7*$J$7/1000/1000*$J$6/100</f>
-        <v>0.68399999999999994</v>
-      </c>
-      <c r="D5" s="44">
-        <f>$J$7*B5/1000</f>
-        <v>12</v>
-      </c>
-      <c r="E5" s="44">
-        <f>D5/$J$12</f>
-        <v>14.894545454545455</v>
-      </c>
-      <c r="F5" s="44">
-        <f>D5/$J$12*$J$13</f>
-        <v>953.25090909090909</v>
-      </c>
-      <c r="G5" s="39">
-        <f>$J$7/F5*1000</f>
+      <c r="C5" s="51">
+        <f t="shared" si="0"/>
+        <v>4.2749999999999996E-2</v>
+      </c>
+      <c r="D5" s="50">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="E5" s="50">
+        <f t="shared" si="2"/>
+        <v>3.7236363636363636</v>
+      </c>
+      <c r="F5" s="50">
+        <f t="shared" si="3"/>
+        <v>238.31272727272727</v>
+      </c>
+      <c r="G5" s="51">
+        <f t="shared" si="4"/>
         <v>62.9425048828125</v>
       </c>
       <c r="I5" s="8" t="s">
@@ -2887,36 +2996,36 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B6" s="44">
+      <c r="B6" s="50">
         <v>250</v>
       </c>
-      <c r="C6" s="39">
-        <f>B6*$J$7*$J$7/1000/1000*$J$6/100</f>
-        <v>0.85499999999999998</v>
-      </c>
-      <c r="D6" s="44">
-        <f>$J$7*B6/1000</f>
-        <v>15</v>
-      </c>
-      <c r="E6" s="44">
-        <f>D6/$J$12</f>
-        <v>18.618181818181817</v>
-      </c>
-      <c r="F6" s="44">
-        <f>D6/$J$12*$J$13</f>
-        <v>1191.5636363636363</v>
-      </c>
-      <c r="G6" s="39">
-        <f>$J$7/F6*1000</f>
+      <c r="C6" s="51">
+        <f t="shared" si="0"/>
+        <v>5.3437499999999999E-2</v>
+      </c>
+      <c r="D6" s="50">
+        <f t="shared" si="1"/>
+        <v>3.75</v>
+      </c>
+      <c r="E6" s="50">
+        <f t="shared" si="2"/>
+        <v>4.6545454545454543</v>
+      </c>
+      <c r="F6" s="50">
+        <f t="shared" si="3"/>
+        <v>297.89090909090908</v>
+      </c>
+      <c r="G6" s="51">
+        <f t="shared" si="4"/>
         <v>50.35400390625</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="31">
+        <v>56</v>
+      </c>
+      <c r="J6" s="2">
         <v>95</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="K6" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2926,30 +3035,30 @@
         <v>300</v>
       </c>
       <c r="C7" s="6">
-        <f>B7*$J$7*$J$7/1000/1000*$J$6/100</f>
-        <v>1.026</v>
+        <f t="shared" si="0"/>
+        <v>6.4125000000000001E-2</v>
       </c>
       <c r="D7" s="9">
-        <f>$J$7*B7/1000</f>
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>4.5</v>
       </c>
       <c r="E7" s="9">
-        <f>D7/$J$12</f>
-        <v>22.341818181818184</v>
+        <f t="shared" si="2"/>
+        <v>5.5854545454545459</v>
       </c>
       <c r="F7" s="9">
-        <f>D7/$J$12*$J$13</f>
-        <v>1429.8763636363637</v>
+        <f t="shared" si="3"/>
+        <v>357.46909090909094</v>
       </c>
       <c r="G7" s="6">
-        <f>$J$7/F7*1000</f>
+        <f t="shared" si="4"/>
         <v>41.961669921875</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J7" s="2">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>52</v>
@@ -2957,53 +3066,53 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B8" s="9">
-        <f t="shared" ref="B8:B14" si="0">B7+100</f>
+        <f t="shared" ref="B8:B14" si="5">B7+100</f>
         <v>400</v>
       </c>
       <c r="C8" s="6">
-        <f>B8*$J$7*$J$7/1000/1000*$J$6/100</f>
-        <v>1.3679999999999999</v>
+        <f t="shared" si="0"/>
+        <v>8.5499999999999993E-2</v>
       </c>
       <c r="D8" s="9">
-        <f>$J$7*B8/1000</f>
-        <v>24</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="E8" s="9">
-        <f>D8/$J$12</f>
-        <v>29.789090909090909</v>
+        <f t="shared" si="2"/>
+        <v>7.4472727272727273</v>
       </c>
       <c r="F8" s="9">
-        <f>D8/$J$12*$J$13</f>
-        <v>1906.5018181818182</v>
+        <f t="shared" si="3"/>
+        <v>476.62545454545455</v>
       </c>
       <c r="G8" s="6">
-        <f>$J$7/F8*1000</f>
+        <f t="shared" si="4"/>
         <v>31.47125244140625</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B9" s="9">
+      <c r="B9" s="31">
+        <f t="shared" si="5"/>
+        <v>500</v>
+      </c>
+      <c r="C9" s="28">
         <f t="shared" si="0"/>
-        <v>500</v>
-      </c>
-      <c r="C9" s="6">
-        <f>B9*$J$7*$J$7/1000/1000*$J$6/100</f>
-        <v>1.71</v>
-      </c>
-      <c r="D9" s="9">
-        <f>$J$7*B9/1000</f>
-        <v>30</v>
-      </c>
-      <c r="E9" s="9">
-        <f>D9/$J$12</f>
-        <v>37.236363636363635</v>
-      </c>
-      <c r="F9" s="9">
-        <f>D9/$J$12*$J$13</f>
-        <v>2383.1272727272726</v>
-      </c>
-      <c r="G9" s="6">
-        <f>$J$7/F9*1000</f>
+        <v>0.106875</v>
+      </c>
+      <c r="D9" s="31">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="E9" s="31">
+        <f t="shared" si="2"/>
+        <v>9.3090909090909086</v>
+      </c>
+      <c r="F9" s="31">
+        <f t="shared" si="3"/>
+        <v>595.78181818181815</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" si="4"/>
         <v>25.177001953125</v>
       </c>
       <c r="I9" s="8" t="s">
@@ -3018,27 +3127,27 @@
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B10" s="9">
+        <f t="shared" si="5"/>
+        <v>600</v>
+      </c>
+      <c r="C10" s="6">
         <f t="shared" si="0"/>
-        <v>600</v>
-      </c>
-      <c r="C10" s="6">
-        <f>B10*$J$7*$J$7/1000/1000*$J$6/100</f>
-        <v>2.052</v>
+        <v>0.12825</v>
       </c>
       <c r="D10" s="9">
-        <f>$J$7*B10/1000</f>
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="E10" s="9">
-        <f>D10/$J$12</f>
-        <v>44.683636363636367</v>
+        <f t="shared" si="2"/>
+        <v>11.170909090909092</v>
       </c>
       <c r="F10" s="9">
-        <f>D10/$J$12*$J$13</f>
-        <v>2859.7527272727275</v>
+        <f t="shared" si="3"/>
+        <v>714.93818181818187</v>
       </c>
       <c r="G10" s="6">
-        <f>$J$7/F10*1000</f>
+        <f t="shared" si="4"/>
         <v>20.9808349609375</v>
       </c>
       <c r="I10" s="8" t="s">
@@ -3053,27 +3162,27 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B11" s="9">
+        <f t="shared" si="5"/>
+        <v>700</v>
+      </c>
+      <c r="C11" s="6">
         <f t="shared" si="0"/>
-        <v>700</v>
-      </c>
-      <c r="C11" s="6">
-        <f>B11*$J$7*$J$7/1000/1000*$J$6/100</f>
-        <v>2.3940000000000001</v>
+        <v>0.14962500000000001</v>
       </c>
       <c r="D11" s="9">
-        <f>$J$7*B11/1000</f>
-        <v>42</v>
+        <f t="shared" si="1"/>
+        <v>10.5</v>
       </c>
       <c r="E11" s="9">
-        <f>D11/$J$12</f>
-        <v>52.130909090909093</v>
+        <f t="shared" si="2"/>
+        <v>13.032727272727273</v>
       </c>
       <c r="F11" s="9">
-        <f>D11/$J$12*$J$13</f>
-        <v>3336.3781818181819</v>
+        <f t="shared" si="3"/>
+        <v>834.09454545454548</v>
       </c>
       <c r="G11" s="6">
-        <f>$J$7/F11*1000</f>
+        <f t="shared" si="4"/>
         <v>17.983572823660712</v>
       </c>
       <c r="I11" s="8" t="s">
@@ -3089,27 +3198,27 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B12" s="9">
+        <f t="shared" si="5"/>
+        <v>800</v>
+      </c>
+      <c r="C12" s="6">
         <f t="shared" si="0"/>
-        <v>800</v>
-      </c>
-      <c r="C12" s="6">
-        <f>B12*$J$7*$J$7/1000/1000*$J$6/100</f>
-        <v>2.7359999999999998</v>
+        <v>0.17099999999999999</v>
       </c>
       <c r="D12" s="9">
-        <f>$J$7*B12/1000</f>
-        <v>48</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="E12" s="9">
-        <f>D12/$J$12</f>
-        <v>59.578181818181818</v>
+        <f t="shared" si="2"/>
+        <v>14.894545454545455</v>
       </c>
       <c r="F12" s="9">
-        <f>D12/$J$12*$J$13</f>
-        <v>3813.0036363636364</v>
+        <f t="shared" si="3"/>
+        <v>953.25090909090909</v>
       </c>
       <c r="G12" s="6">
-        <f>$J$7/F12*1000</f>
+        <f t="shared" si="4"/>
         <v>15.735626220703125</v>
       </c>
       <c r="I12" s="8" t="s">
@@ -3120,36 +3229,36 @@
         <v>0.8056640625</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B13" s="9">
+        <f t="shared" si="5"/>
+        <v>900</v>
+      </c>
+      <c r="C13" s="6">
         <f t="shared" si="0"/>
-        <v>900</v>
-      </c>
-      <c r="C13" s="6">
-        <f>B13*$J$7*$J$7/1000/1000*$J$6/100</f>
-        <v>3.0780000000000003</v>
+        <v>0.19237500000000002</v>
       </c>
       <c r="D13" s="9">
-        <f>$J$7*B13/1000</f>
-        <v>54</v>
+        <f t="shared" si="1"/>
+        <v>13.5</v>
       </c>
       <c r="E13" s="9">
-        <f>D13/$J$12</f>
-        <v>67.025454545454551</v>
+        <f t="shared" si="2"/>
+        <v>16.756363636363638</v>
       </c>
       <c r="F13" s="9">
-        <f>D13/$J$12*$J$13</f>
-        <v>4289.6290909090912</v>
+        <f t="shared" si="3"/>
+        <v>1072.4072727272728</v>
       </c>
       <c r="G13" s="6">
-        <f>$J$7/F13*1000</f>
+        <f t="shared" si="4"/>
         <v>13.987223307291666</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J13" s="9">
         <v>64</v>
@@ -3160,32 +3269,42 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B14" s="9">
+        <f t="shared" si="5"/>
+        <v>1000</v>
+      </c>
+      <c r="C14" s="6">
         <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="C14" s="6">
-        <f>B14*$J$7*$J$7/1000/1000*$J$6/100</f>
-        <v>3.42</v>
+        <v>0.21375</v>
       </c>
       <c r="D14" s="9">
-        <f>$J$7*B14/1000</f>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="E14" s="9">
-        <f>D14/$J$12</f>
-        <v>74.472727272727269</v>
+        <f t="shared" si="2"/>
+        <v>18.618181818181817</v>
       </c>
       <c r="F14" s="9">
-        <f>D14/$J$12*$J$13</f>
-        <v>4766.2545454545452</v>
+        <f t="shared" si="3"/>
+        <v>1191.5636363636363</v>
       </c>
       <c r="G14" s="6">
-        <f>$J$7/F14*1000</f>
+        <f t="shared" si="4"/>
         <v>12.5885009765625</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="D16" s="38"/>
+      <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>103</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3193,4 +3312,238 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE2F4E60-E2C6-48B6-8B32-33733DDD0651}">
+  <dimension ref="B2:P16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="2" max="2" width="30.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" customWidth="1"/>
+    <col min="7" max="7" width="30.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B2" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="3">
+        <v>15</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B3" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="3">
+        <v>95</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B4" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="3">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B5" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B6" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="3">
+        <v>79</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B7" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="3">
+        <v>81</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B8" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="3">
+        <v>64</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="43"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="42"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="N9" s="42"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="42"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B10" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="45">
+        <f>D5/1000*D2^2*D3/100</f>
+        <v>0.25649999999999995</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="42"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="42"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B11" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="45">
+        <f>1/2*D4*D2*(D6+D7)*D8/1000000</f>
+        <v>1.9967999999999999</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B12" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="47">
+        <f>D10*2+D11</f>
+        <v>2.5097999999999998</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="46"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B14" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B15" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="42"/>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B16" s="46" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FD2DCF-3994-4A7C-BD62-D1225B43EB25}">
+  <dimension ref="B2:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/resources/Kururugi-ESC-calculs.xlsx
+++ b/resources/Kururugi-ESC-calculs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\binon\Desktop\Kururugi-ESC-Dev-Board\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C0B332-76E9-4EB3-8047-242D388BD131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEB0AB0-B861-43F3-8AFC-2947B78D0D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
+    <workbookView xWindow="5775" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Vsensing computation" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="137">
   <si>
     <t>R1 (kOhm)</t>
   </si>
@@ -376,10 +376,120 @@
     <t>95% duty is the goal for v1</t>
   </si>
   <si>
-    <t>Dissipation of the mosfet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size </t>
+    <t>Vdd (V)</t>
+  </si>
+  <si>
+    <t>Vhbr (V)</t>
+  </si>
+  <si>
+    <t>Vhbh (V)</t>
+  </si>
+  <si>
+    <t>Qg (nC)</t>
+  </si>
+  <si>
+    <t>Ipulldown (mA)</t>
+  </si>
+  <si>
+    <t>Ihbs (mA)</t>
+  </si>
+  <si>
+    <t>Ihb (mA)</t>
+  </si>
+  <si>
+    <t>Fsw min (kHz)</t>
+  </si>
+  <si>
+    <t>Qt (nC)</t>
+  </si>
+  <si>
+    <t>Cbootmin (nC)</t>
+  </si>
+  <si>
+    <t>V0 (V)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vbootmax (V)</t>
+    </r>
+  </si>
+  <si>
+    <t>ΔVboot (V)</t>
+  </si>
+  <si>
+    <t>Vddboot (V)</t>
+  </si>
+  <si>
+    <t>C secu (NU)</t>
+  </si>
+  <si>
+    <t>Fmax (kHz)</t>
+  </si>
+  <si>
+    <t>Max duty (%)</t>
+  </si>
+  <si>
+    <t>Toff (µs)</t>
+  </si>
+  <si>
+    <t>Toff secu (NU)</t>
+  </si>
+  <si>
+    <t>Tcharge (µs)</t>
+  </si>
+  <si>
+    <t>Vfinal (V)</t>
+  </si>
+  <si>
+    <r>
+      <t>Rfint (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ω)</t>
+    </r>
+  </si>
+  <si>
+    <t>Rf (Ω)</t>
+  </si>
+  <si>
+    <t>Rfext (Ω)</t>
+  </si>
+  <si>
+    <t>Vf,100mA (V)</t>
+  </si>
+  <si>
+    <t>Vr,100mA (V)</t>
+  </si>
+  <si>
+    <t>Imaxext (A)</t>
+  </si>
+  <si>
+    <t>3Tau (µs)</t>
+  </si>
+  <si>
+    <t>Cboot (nF)</t>
   </si>
 </sst>
 </file>
@@ -392,7 +502,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,6 +538,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -669,7 +785,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -715,9 +831,6 @@
     <xf numFmtId="167" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="166" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -750,6 +863,13 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -771,28 +891,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="33">
     <dxf>
       <fill>
         <patternFill>
@@ -814,6 +926,110 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -825,6 +1041,75 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B25A5C38-85C7-4CC9-A2E7-8CC77C0ABABE}" name="Tableau1" displayName="Tableau1" ref="A1:AC3" totalsRowShown="0" dataDxfId="32">
+  <autoFilter ref="A1:AC3" xr:uid="{B25A5C38-85C7-4CC9-A2E7-8CC77C0ABABE}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC3">
+    <sortCondition ref="A1:A3"/>
+  </sortState>
+  <tableColumns count="29">
+    <tableColumn id="1" xr3:uid="{8D98E4BE-CBC8-4993-8988-6AA9DD987F18}" name="Vdd (V)" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{9D660013-882C-48E1-9078-C0D5B2A80597}" name="Vf,100mA (V)" dataDxfId="30"/>
+    <tableColumn id="28" xr3:uid="{36BE38BC-4343-43D2-A6AB-DF7CBCB8D288}" name="Vr,100mA (V)" dataDxfId="29">
+      <calculatedColumnFormula>Tableau1[[#This Row],[Rfext (Ω)]]*0.1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{3510157E-7A02-4689-8664-3BE0329D115D}" name="Vhbr (V)" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{ECB1DE36-B875-416D-8E2C-DEF25492B782}" name="Vhbh (V)" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{FD7B4A02-8912-4F70-8F8F-E3160EF255C7}" name="ΔVbootmax (V)" dataDxfId="26">
+      <calculatedColumnFormula>A2-B2-D2-E2-Tableau1[[#This Row],[Vr,100mA (V)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{67DE6560-3A18-4706-8C36-B17ACB24E0A0}" name="Qg (nC)" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{1F6CBA99-F458-419E-95F9-04D2A3D6DC26}" name="Ihb (mA)" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{BABC204A-8EFE-4167-9EF4-887D78DD0CDA}" name="Ihbs (mA)" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{BA788F06-CA53-4E0A-AE4D-896E43A6EDE5}" name="Ipulldown (mA)" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{DB260FB3-06E8-4730-847C-5E6BD063D326}" name="Max duty (%)" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{1CBF1355-D31F-456C-80BE-6CC8C444F650}" name="Fsw min (kHz)" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{1E038DBA-495F-43B9-B606-822FB74520D5}" name="Qt (nC)" dataDxfId="19">
+      <calculatedColumnFormula>(G2*10^-9+H2/L2*10^-6+(I2+J2)/L2*10^-6*K2/100)/10^-9</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{C79274CC-E2A1-41D2-A761-D54CC7A29829}" name="Cbootmin (nC)" dataDxfId="18">
+      <calculatedColumnFormula>M2/F2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{FA3E1CDB-C23D-4FB1-B19E-9DA04D3955EB}" name="C secu (NU)" dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{F2329A40-7530-43DD-9A8D-D9481FE6DDA8}" name="Cboot (nF)" dataDxfId="16">
+      <calculatedColumnFormula>N2*O2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{E7529637-516C-4BAC-9F9C-F3BCAD77EB6C}" name="ΔVboot (V)" dataDxfId="15">
+      <calculatedColumnFormula>P2/M2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{A1106862-E575-4A15-BDC9-291F1DC16EA8}" name="Fmax (kHz)" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{ED56DF9B-39E7-4337-92AA-A19107C957F6}" name="Toff (µs)" dataDxfId="13">
+      <calculatedColumnFormula>1/R2/1000*(1-K2/100)*1000000</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="19" xr3:uid="{5EF5F032-1924-4722-B113-497A8A53F9F9}" name="Toff secu (NU)" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{317078D3-172D-4084-B914-D44E27AF4622}" name="Tcharge (µs)" dataDxfId="11">
+      <calculatedColumnFormula>S2/T2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" xr3:uid="{C74CCBDA-ECD0-48F4-BDD1-B7B52CDCD12C}" name="V0 (V)" dataDxfId="10">
+      <calculatedColumnFormula>A2-B2-Q2-Tableau1[[#This Row],[Vr,100mA (V)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="22" xr3:uid="{24CB70CF-920B-4509-9638-5D3F89476E1B}" name="Vddboot (V)" dataDxfId="9">
+      <calculatedColumnFormula>A2-B2-Tableau1[[#This Row],[Vr,100mA (V)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="23" xr3:uid="{97086D48-76D1-44FE-9798-1E4B672A9D3C}" name="Rfint (Ω)" dataDxfId="8"/>
+    <tableColumn id="25" xr3:uid="{CA25B27B-2081-46A3-A11C-C04EC8E9925A}" name="Rfext (Ω)" dataDxfId="7"/>
+    <tableColumn id="26" xr3:uid="{D571851B-D502-4394-822B-26D2605F0715}" name="Rf (Ω)" dataDxfId="6">
+      <calculatedColumnFormula>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0, 1/(1/Tableau1[[#This Row],[Rfint (Ω)]]+1/Tableau1[[#This Row],[Rfext (Ω)]]), Tableau1[[#This Row],[Rfint (Ω)]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="24" xr3:uid="{C72492AB-BD7B-405B-867F-5ADF45417C24}" name="Vfinal (V)" dataDxfId="5">
+      <calculatedColumnFormula>(V2-W2)*EXP(-U2*10^-6/Tableau1[[#This Row],[Rf (Ω)]]/(P2*10^-9))+W2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="30" xr3:uid="{4A2A1E44-66D8-4309-9DC7-637AF6F8770A}" name="Imaxext (A)" dataDxfId="4">
+      <calculatedColumnFormula>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0,Tableau1[[#This Row],[Vdd (V)]]/Tableau1[[#This Row],[Rfext (Ω)]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="31" xr3:uid="{B3DB0F25-7B1B-46E1-B7A4-6C280BA75465}" name="3Tau (µs)" dataDxfId="3">
+      <calculatedColumnFormula>IF(Tableau1[[#This Row],[Imaxext (A)]]&gt;0,3*Tableau1[[#This Row],[Rf (Ω)]]*Tableau1[[#This Row],[Cboot (nF)]]*10^-3,0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1167,18 +1452,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="39"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="43"/>
       <c r="M2" s="8" t="s">
         <v>22</v>
       </c>
@@ -2116,11 +2401,11 @@
         <f t="shared" si="4"/>
         <v>3.9062499999999996</v>
       </c>
-      <c r="M19" s="34" t="s">
+      <c r="M19" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="N19" s="35"/>
-      <c r="O19" s="36"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="40"/>
       <c r="Q19" t="s">
         <v>20</v>
       </c>
@@ -2474,11 +2759,11 @@
       <c r="M26" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="N26" s="33">
+      <c r="N26" s="32">
         <f>R4*N25*1000</f>
         <v>2.0429968393118183</v>
       </c>
-      <c r="O26" s="32" t="s">
+      <c r="O26" s="31" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2742,100 +3027,100 @@
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B33" s="22">
-        <v>1.3068</v>
-      </c>
-      <c r="C33" s="22">
+      <c r="B33" s="21">
+        <v>0.39</v>
+      </c>
+      <c r="C33" s="21">
         <f t="shared" si="11"/>
-        <v>18.295200000000001</v>
-      </c>
-      <c r="D33" s="6">
+        <v>5.4600000000000009</v>
+      </c>
+      <c r="D33" s="20">
         <f t="shared" si="5"/>
-        <v>1.26668</v>
+        <v>0.41100000000000003</v>
       </c>
       <c r="E33" s="20">
         <f t="shared" si="12"/>
-        <v>2.3683961221460827</v>
-      </c>
-      <c r="F33" s="25">
+        <v>7.2992700729926998</v>
+      </c>
+      <c r="F33" s="24">
         <f t="shared" si="2"/>
-        <v>1.26668</v>
+        <v>0.41100000000000003</v>
       </c>
       <c r="G33" s="6">
         <f t="shared" si="8"/>
-        <v>1266.68</v>
+        <v>411</v>
       </c>
       <c r="H33" s="6">
         <f t="shared" si="6"/>
-        <v>1.0925853624325372</v>
+        <v>3.3672896031290667</v>
       </c>
       <c r="I33" s="20">
         <f t="shared" si="13"/>
-        <v>31.884501581471277</v>
+        <v>106.83760683760683</v>
       </c>
       <c r="J33" s="20">
         <f t="shared" si="3"/>
-        <v>2.5507601265177025</v>
+        <v>8.5470085470085468</v>
       </c>
       <c r="K33" s="20">
         <f t="shared" si="4"/>
-        <v>4.7826752372206913</v>
+        <v>16.025641025641022</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="23"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B35" s="22">
-        <v>1.3</v>
-      </c>
-      <c r="C35" s="22">
-        <v>16</v>
+      <c r="B35" s="21">
+        <v>0.39</v>
+      </c>
+      <c r="C35" s="21">
+        <v>5.6</v>
       </c>
       <c r="D35" s="20">
-        <f>B35*C35/(B35+C35)</f>
-        <v>1.2023121387283238</v>
+        <f t="shared" ref="D35" si="14">B35*C35/(B35+C35)+$N$17/1000</f>
+        <v>0.41160767946577625</v>
       </c>
       <c r="E35" s="20">
-        <f>$N$4/D35</f>
-        <v>2.4951923076923075</v>
-      </c>
-      <c r="F35" s="25">
-        <f>IF($N$9=0,$N$23*($N$8+$N$7)*D35,$N$23*(0.1)*D35)</f>
-        <v>1.2023121387283238</v>
+        <f t="shared" ref="E35" si="15">$N$4/D35</f>
+        <v>7.288493751850516</v>
+      </c>
+      <c r="F35" s="24">
+        <f t="shared" ref="F35" si="16">IF($N$9=0,$N$23*($N$8+$N$7)*D35,$N$23*(0.1)*D35)</f>
+        <v>0.41160767946577625</v>
       </c>
       <c r="G35" s="6">
-        <f>C35*D35*$N$14</f>
-        <v>192.36994219653181</v>
-      </c>
-      <c r="H35" s="21">
-        <f>1/(($N$8+$N$7+$N$9)*D35)*1000</f>
-        <v>7.2324414715719065</v>
+        <f t="shared" ref="G35" si="17">$N$9*D35*$N$14</f>
+        <v>411.6076794657763</v>
+      </c>
+      <c r="H35" s="6">
+        <f t="shared" ref="H35" si="18">1/(2*PI()*($N$8+$N$7+$N$9)*D35)*1000</f>
+        <v>3.3623182849316042</v>
       </c>
       <c r="I35" s="20">
-        <f>$N$3*$N$3/(C35+B35)</f>
-        <v>36.127167630057805</v>
+        <f t="shared" ref="I35" si="19">$N$3*$N$3/(C35+B35)</f>
+        <v>104.34056761268782</v>
       </c>
       <c r="J35" s="20">
-        <f>I35*$R$10/1000</f>
-        <v>2.8901734104046244</v>
+        <f t="shared" ref="J35" si="20">I35*$R$10/1000</f>
+        <v>8.3472454090150254</v>
       </c>
       <c r="K35" s="20">
-        <f>I35*$R$11/1000</f>
-        <v>5.4190751445086711</v>
+        <f t="shared" ref="K35" si="21">I35*$R$11/1000</f>
+        <v>15.651085141903174</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="G36" s="30"/>
+      <c r="G36" s="29"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.35">
       <c r="F37" s="11" t="s">
@@ -2893,32 +3178,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="26" t="s">
         <v>67</v>
       </c>
       <c r="I3" s="8" t="s">
@@ -2961,27 +3246,27 @@
       <c r="K4" s="3"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B5" s="50">
+      <c r="B5" s="9">
         <f>B4+100</f>
         <v>200</v>
       </c>
-      <c r="C5" s="51">
+      <c r="C5" s="6">
         <f t="shared" si="0"/>
         <v>4.2749999999999996E-2</v>
       </c>
-      <c r="D5" s="50">
+      <c r="D5" s="9">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="9">
         <f t="shared" si="2"/>
         <v>3.7236363636363636</v>
       </c>
-      <c r="F5" s="50">
+      <c r="F5" s="9">
         <f t="shared" si="3"/>
         <v>238.31272727272727</v>
       </c>
-      <c r="G5" s="51">
+      <c r="G5" s="6">
         <f t="shared" si="4"/>
         <v>62.9425048828125</v>
       </c>
@@ -2996,26 +3281,26 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B6" s="50">
+      <c r="B6" s="9">
         <v>250</v>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="6">
         <f t="shared" si="0"/>
         <v>5.3437499999999999E-2</v>
       </c>
-      <c r="D6" s="50">
+      <c r="D6" s="9">
         <f t="shared" si="1"/>
         <v>3.75</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="9">
         <f t="shared" si="2"/>
         <v>4.6545454545454543</v>
       </c>
-      <c r="F6" s="50">
+      <c r="F6" s="9">
         <f t="shared" si="3"/>
         <v>297.89090909090908</v>
       </c>
-      <c r="G6" s="51">
+      <c r="G6" s="6">
         <f t="shared" si="4"/>
         <v>50.35400390625</v>
       </c>
@@ -3091,27 +3376,27 @@
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B9" s="31">
+      <c r="B9" s="30">
         <f t="shared" si="5"/>
         <v>500</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <f t="shared" si="0"/>
         <v>0.106875</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <f t="shared" si="2"/>
         <v>9.3090909090909086</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <f t="shared" si="3"/>
         <v>595.78181818181815</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="27">
         <f t="shared" si="4"/>
         <v>25.177001953125</v>
       </c>
@@ -3297,7 +3582,7 @@
       <c r="B16" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="37" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3316,7 +3601,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE2F4E60-E2C6-48B6-8B32-33733DDD0651}">
-  <dimension ref="B2:P16"/>
+  <dimension ref="B2:N16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.453125" customWidth="1"/>
@@ -3327,8 +3612,8 @@
     <col min="10" max="10" width="30.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B2" s="44" t="s">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B2" s="34" t="s">
         <v>92</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -3341,8 +3626,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B3" s="44" t="s">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B3" s="34" t="s">
         <v>81</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -3355,8 +3640,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B4" s="44" t="s">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B4" s="34" t="s">
         <v>83</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -3369,8 +3654,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B5" s="44" t="s">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B5" s="34" t="s">
         <v>85</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -3379,12 +3664,12 @@
       <c r="D5" s="3">
         <v>1.2</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B6" s="44" t="s">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B6" s="34" t="s">
         <v>86</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -3393,15 +3678,12 @@
       <c r="D6" s="3">
         <v>79</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B7" s="44" t="s">
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B7" s="34" t="s">
         <v>88</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -3410,15 +3692,12 @@
       <c r="D7" s="3">
         <v>81</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B8" s="44" t="s">
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B8" s="34" t="s">
         <v>90</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -3427,99 +3706,71 @@
       <c r="D8" s="3">
         <v>64</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N8" s="43"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="42"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="N9" s="42"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="42"/>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B10" s="44" t="s">
+      <c r="N8" s="33"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B10" s="34" t="s">
         <v>100</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="35">
         <f>D5/1000*D2^2*D3/100</f>
         <v>0.25649999999999995</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B11" s="44" t="s">
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B11" s="34" t="s">
         <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="35">
         <f>1/2*D4*D2*(D6+D7)*D8/1000000</f>
         <v>1.9967999999999999</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="N11" s="42"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="42"/>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B12" s="44" t="s">
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B12" s="34" t="s">
         <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="35">
         <f>D10*2+D11</f>
         <v>2.5097999999999998</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="46"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B14" s="46" t="s">
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="D13" s="36"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
         <v>105</v>
       </c>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B15" s="46" t="s">
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
         <v>106</v>
       </c>
-      <c r="N15" s="42"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B16" s="46" t="s">
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3530,20 +3781,334 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FD2DCF-3994-4A7C-BD62-D1225B43EB25}">
-  <dimension ref="B2:B4"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="1.6328125" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="1.6328125" customWidth="1"/>
+    <col min="11" max="11" width="13.81640625" customWidth="1"/>
+    <col min="12" max="12" width="1.6328125" customWidth="1"/>
+    <col min="13" max="13" width="9.1796875" customWidth="1"/>
+    <col min="14" max="14" width="16.36328125" customWidth="1"/>
+    <col min="15" max="15" width="13.08984375" customWidth="1"/>
+    <col min="16" max="16" width="12.453125" customWidth="1"/>
+    <col min="17" max="17" width="11.90625" customWidth="1"/>
+    <col min="18" max="18" width="12.26953125" customWidth="1"/>
+    <col min="19" max="20" width="1.6328125" customWidth="1"/>
+    <col min="21" max="21" width="13.36328125" customWidth="1"/>
+    <col min="22" max="22" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13" customWidth="1"/>
+    <col min="24" max="24" width="1.6328125" customWidth="1"/>
+    <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
+      <c r="B1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" t="s">
         <v>109</v>
       </c>
+      <c r="E1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" t="s">
+        <v>117</v>
+      </c>
+      <c r="O1" t="s">
+        <v>122</v>
+      </c>
+      <c r="P1" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>120</v>
+      </c>
+      <c r="R1" t="s">
+        <v>123</v>
+      </c>
+      <c r="S1" t="s">
+        <v>125</v>
+      </c>
+      <c r="T1" t="s">
+        <v>126</v>
+      </c>
+      <c r="U1" t="s">
+        <v>127</v>
+      </c>
+      <c r="V1" t="s">
+        <v>118</v>
+      </c>
+      <c r="W1" t="s">
+        <v>121</v>
+      </c>
+      <c r="X1" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="C2" s="1">
+        <f>Tableau1[[#This Row],[Rfext (Ω)]]*0.1</f>
+        <v>0.51</v>
+      </c>
+      <c r="D2" s="1">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="F2" s="1">
+        <f>A2-B2-D2-E2-Tableau1[[#This Row],[Vr,100mA (V)]]</f>
+        <v>2.919999999999999</v>
+      </c>
+      <c r="G2" s="1">
+        <v>120</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1">
+        <v>95</v>
+      </c>
+      <c r="L2" s="1">
+        <v>24</v>
+      </c>
+      <c r="M2" s="32">
+        <f>(G2*10^-9+H2/L2*10^-6+(I2+J2)/L2*10^-6*K2/100)/10^-9</f>
+        <v>238.22916666666666</v>
+      </c>
+      <c r="N2" s="32">
+        <f>M2/F2</f>
+        <v>81.585331050228334</v>
+      </c>
+      <c r="O2" s="1">
+        <v>2</v>
+      </c>
+      <c r="P2" s="32">
+        <v>300</v>
+      </c>
+      <c r="Q2" s="45">
+        <f>P2/M2</f>
+        <v>1.2592916484477481</v>
+      </c>
+      <c r="R2" s="1">
+        <v>128</v>
+      </c>
+      <c r="S2" s="46">
+        <f>1/R2/1000*(1-K2/100)*1000000</f>
+        <v>0.39062500000000033</v>
+      </c>
+      <c r="T2" s="1">
+        <v>2</v>
+      </c>
+      <c r="U2" s="46">
+        <f>S2/T2</f>
+        <v>0.19531250000000017</v>
+      </c>
+      <c r="V2" s="46">
+        <f>A2-B2-Q2-Tableau1[[#This Row],[Vr,100mA (V)]]</f>
+        <v>7.9307083515522514</v>
+      </c>
+      <c r="W2" s="1">
+        <f>A2-B2-Tableau1[[#This Row],[Vr,100mA (V)]]</f>
+        <v>9.19</v>
+      </c>
+      <c r="X2" s="1">
+        <v>21.5</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Z2" s="46">
+        <f>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0, 1/(1/Tableau1[[#This Row],[Rfint (Ω)]]+1/Tableau1[[#This Row],[Rfext (Ω)]]), Tableau1[[#This Row],[Rfint (Ω)]])</f>
+        <v>4.1221804511278188</v>
+      </c>
+      <c r="AA2" s="46">
+        <f>(V2-W2)*EXP(-U2*10^-6/Tableau1[[#This Row],[Rf (Ω)]]/(P2*10^-9))+W2</f>
+        <v>8.114685536921213</v>
+      </c>
+      <c r="AB2" s="45">
+        <f>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0,Tableau1[[#This Row],[Vdd (V)]]/Tableau1[[#This Row],[Rfext (Ω)]],0)</f>
+        <v>1.9607843137254903</v>
+      </c>
+      <c r="AC2" s="46">
+        <f>IF(Tableau1[[#This Row],[Imaxext (A)]]&gt;0,3*Tableau1[[#This Row],[Rf (Ω)]]*Tableau1[[#This Row],[Cboot (nF)]]*10^-3,0)</f>
+        <v>3.7099624060150371</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="C3" s="47">
+        <f>Tableau1[[#This Row],[Rfext (Ω)]]*0.1</f>
+        <v>0.51</v>
+      </c>
+      <c r="D3" s="1">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="F3" s="47">
+        <f>A3-B3-D3-E3-Tableau1[[#This Row],[Vr,100mA (V)]]</f>
+        <v>2.919999999999999</v>
+      </c>
+      <c r="G3" s="1">
+        <v>120</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>95</v>
+      </c>
+      <c r="L3" s="1">
+        <v>10</v>
+      </c>
+      <c r="M3" s="32">
+        <f>(G3*10^-9+H3/L3*10^-6+(I3+J3)/L3*10^-6*K3/100)/10^-9</f>
+        <v>403.74999999999994</v>
+      </c>
+      <c r="N3" s="32">
+        <f>M3/F3</f>
+        <v>138.27054794520549</v>
+      </c>
+      <c r="O3" s="1">
+        <v>3</v>
+      </c>
+      <c r="P3" s="32">
+        <f>N3*O3</f>
+        <v>414.81164383561645</v>
+      </c>
+      <c r="Q3" s="45">
+        <f>P3/M3</f>
+        <v>1.0273972602739727</v>
+      </c>
+      <c r="R3" s="1">
+        <v>128</v>
+      </c>
+      <c r="S3" s="46">
+        <f>1/R3/1000*(1-K3/100)*1000000</f>
+        <v>0.39062500000000033</v>
+      </c>
+      <c r="T3" s="1">
+        <v>2</v>
+      </c>
+      <c r="U3" s="46">
+        <f>S3/T3</f>
+        <v>0.19531250000000017</v>
+      </c>
+      <c r="V3" s="46">
+        <f>A3-B3-Q3-Tableau1[[#This Row],[Vr,100mA (V)]]</f>
+        <v>8.1626027397260277</v>
+      </c>
+      <c r="W3" s="47">
+        <f>A3-B3-Tableau1[[#This Row],[Vr,100mA (V)]]</f>
+        <v>9.19</v>
+      </c>
+      <c r="X3" s="1">
+        <v>21.5</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Z3" s="46">
+        <f>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0, 1/(1/Tableau1[[#This Row],[Rfint (Ω)]]+1/Tableau1[[#This Row],[Rfext (Ω)]]), Tableau1[[#This Row],[Rfint (Ω)]])</f>
+        <v>4.1221804511278188</v>
+      </c>
+      <c r="AA3" s="46">
+        <f>(V3-W3)*EXP(-U3*10^-6/Tableau1[[#This Row],[Rf (Ω)]]/(P3*10^-9))+W3</f>
+        <v>8.2735006704566629</v>
+      </c>
+      <c r="AB3" s="45">
+        <f>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0,Tableau1[[#This Row],[Vdd (V)]]/Tableau1[[#This Row],[Rfext (Ω)]],0)</f>
+        <v>1.9607843137254903</v>
+      </c>
+      <c r="AC3" s="46">
+        <f>IF(Tableau1[[#This Row],[Imaxext (A)]]&gt;0,3*Tableau1[[#This Row],[Rf (Ω)]]*Tableau1[[#This Row],[Cboot (nF)]]*10^-3,0)</f>
+        <v>5.129785347358121</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/resources/Kururugi-ESC-calculs.xlsx
+++ b/resources/Kururugi-ESC-calculs.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\binon\Desktop\Kururugi-ESC-Dev-Board\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEB0AB0-B861-43F3-8AFC-2947B78D0D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B2B5A0-7BBE-4CD2-A323-6C36F872F9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5775" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
+    <workbookView xWindow="5775" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Vsensing computation" sheetId="1" r:id="rId1"/>
     <sheet name="Isensing computation" sheetId="2" r:id="rId2"/>
     <sheet name="Mosfet" sheetId="3" r:id="rId3"/>
-    <sheet name="Feuil2" sheetId="4" r:id="rId4"/>
+    <sheet name="GD Cboot" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="138">
   <si>
     <t>R1 (kOhm)</t>
   </si>
@@ -490,6 +490,9 @@
   </si>
   <si>
     <t>Cboot (nF)</t>
+  </si>
+  <si>
+    <t>dx</t>
   </si>
 </sst>
 </file>
@@ -1429,7 +1432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46177FA7-98B1-43B3-8996-93B4082609D4}">
-  <dimension ref="B2:S38"/>
+  <dimension ref="B2:S41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.453125" customWidth="1"/>
@@ -3131,6 +3134,11 @@
     <row r="38" spans="2:11" x14ac:dyDescent="0.35">
       <c r="H38" s="11" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="H41" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Kururugi-ESC-calculs.xlsx
+++ b/resources/Kururugi-ESC-calculs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\binon\Desktop\Kururugi-ESC-Dev-Board\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B2B5A0-7BBE-4CD2-A323-6C36F872F9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022EFFC5-314D-4BF4-81A0-FE89DAE72F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5775" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="141">
   <si>
     <t>R1 (kOhm)</t>
   </si>
@@ -401,9 +401,6 @@
   </si>
   <si>
     <t>Qt (nC)</t>
-  </si>
-  <si>
-    <t>Cbootmin (nC)</t>
   </si>
   <si>
     <t>V0 (V)</t>
@@ -492,7 +489,19 @@
     <t>Cboot (nF)</t>
   </si>
   <si>
-    <t>dx</t>
+    <t>Cbootmin (nF)</t>
+  </si>
+  <si>
+    <t>Qfreq_max (nC)</t>
+  </si>
+  <si>
+    <t>Max Fsw (kHz)</t>
+  </si>
+  <si>
+    <t>Safety (NU)</t>
+  </si>
+  <si>
+    <t>ImaxIn (mA)</t>
   </si>
 </sst>
 </file>
@@ -788,7 +797,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -873,6 +882,12 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -894,20 +909,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="37">
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -928,6 +938,18 @@
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="167" formatCode="0.0"/>
@@ -1047,68 +1069,76 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B25A5C38-85C7-4CC9-A2E7-8CC77C0ABABE}" name="Tableau1" displayName="Tableau1" ref="A1:AC3" totalsRowShown="0" dataDxfId="32">
-  <autoFilter ref="A1:AC3" xr:uid="{B25A5C38-85C7-4CC9-A2E7-8CC77C0ABABE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B25A5C38-85C7-4CC9-A2E7-8CC77C0ABABE}" name="Tableau1" displayName="Tableau1" ref="A1:AG3" totalsRowShown="0" dataDxfId="36">
+  <autoFilter ref="A1:AG3" xr:uid="{B25A5C38-85C7-4CC9-A2E7-8CC77C0ABABE}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC3">
     <sortCondition ref="A1:A3"/>
   </sortState>
-  <tableColumns count="29">
-    <tableColumn id="1" xr3:uid="{8D98E4BE-CBC8-4993-8988-6AA9DD987F18}" name="Vdd (V)" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{9D660013-882C-48E1-9078-C0D5B2A80597}" name="Vf,100mA (V)" dataDxfId="30"/>
-    <tableColumn id="28" xr3:uid="{36BE38BC-4343-43D2-A6AB-DF7CBCB8D288}" name="Vr,100mA (V)" dataDxfId="29">
+  <tableColumns count="33">
+    <tableColumn id="1" xr3:uid="{8D98E4BE-CBC8-4993-8988-6AA9DD987F18}" name="Vdd (V)" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{9D660013-882C-48E1-9078-C0D5B2A80597}" name="Vf,100mA (V)" dataDxfId="34"/>
+    <tableColumn id="28" xr3:uid="{36BE38BC-4343-43D2-A6AB-DF7CBCB8D288}" name="Vr,100mA (V)" dataDxfId="33">
       <calculatedColumnFormula>Tableau1[[#This Row],[Rfext (Ω)]]*0.1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{3510157E-7A02-4689-8664-3BE0329D115D}" name="Vhbr (V)" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{ECB1DE36-B875-416D-8E2C-DEF25492B782}" name="Vhbh (V)" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{FD7B4A02-8912-4F70-8F8F-E3160EF255C7}" name="ΔVbootmax (V)" dataDxfId="26">
+    <tableColumn id="3" xr3:uid="{3510157E-7A02-4689-8664-3BE0329D115D}" name="Vhbr (V)" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{ECB1DE36-B875-416D-8E2C-DEF25492B782}" name="Vhbh (V)" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{FD7B4A02-8912-4F70-8F8F-E3160EF255C7}" name="ΔVbootmax (V)" dataDxfId="30">
       <calculatedColumnFormula>A2-B2-D2-E2-Tableau1[[#This Row],[Vr,100mA (V)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{67DE6560-3A18-4706-8C36-B17ACB24E0A0}" name="Qg (nC)" dataDxfId="25"/>
-    <tableColumn id="7" xr3:uid="{1F6CBA99-F458-419E-95F9-04D2A3D6DC26}" name="Ihb (mA)" dataDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{BABC204A-8EFE-4167-9EF4-887D78DD0CDA}" name="Ihbs (mA)" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{BA788F06-CA53-4E0A-AE4D-896E43A6EDE5}" name="Ipulldown (mA)" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{DB260FB3-06E8-4730-847C-5E6BD063D326}" name="Max duty (%)" dataDxfId="21"/>
-    <tableColumn id="11" xr3:uid="{1CBF1355-D31F-456C-80BE-6CC8C444F650}" name="Fsw min (kHz)" dataDxfId="20"/>
-    <tableColumn id="12" xr3:uid="{1E038DBA-495F-43B9-B606-822FB74520D5}" name="Qt (nC)" dataDxfId="19">
+    <tableColumn id="6" xr3:uid="{67DE6560-3A18-4706-8C36-B17ACB24E0A0}" name="Qg (nC)" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{1F6CBA99-F458-419E-95F9-04D2A3D6DC26}" name="Ihb (mA)" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{BABC204A-8EFE-4167-9EF4-887D78DD0CDA}" name="Ihbs (mA)" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{BA788F06-CA53-4E0A-AE4D-896E43A6EDE5}" name="Ipulldown (mA)" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{DB260FB3-06E8-4730-847C-5E6BD063D326}" name="Max duty (%)" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{1CBF1355-D31F-456C-80BE-6CC8C444F650}" name="Fsw min (kHz)" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{1E038DBA-495F-43B9-B606-822FB74520D5}" name="Qt (nC)" dataDxfId="23">
       <calculatedColumnFormula>(G2*10^-9+H2/L2*10^-6+(I2+J2)/L2*10^-6*K2/100)/10^-9</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{C79274CC-E2A1-41D2-A761-D54CC7A29829}" name="Cbootmin (nC)" dataDxfId="18">
+    <tableColumn id="13" xr3:uid="{C79274CC-E2A1-41D2-A761-D54CC7A29829}" name="Cbootmin (nF)" dataDxfId="22">
       <calculatedColumnFormula>M2/F2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FA3E1CDB-C23D-4FB1-B19E-9DA04D3955EB}" name="C secu (NU)" dataDxfId="17"/>
-    <tableColumn id="15" xr3:uid="{F2329A40-7530-43DD-9A8D-D9481FE6DDA8}" name="Cboot (nF)" dataDxfId="16">
+    <tableColumn id="14" xr3:uid="{FA3E1CDB-C23D-4FB1-B19E-9DA04D3955EB}" name="C secu (NU)" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{F2329A40-7530-43DD-9A8D-D9481FE6DDA8}" name="Cboot (nF)" dataDxfId="20">
       <calculatedColumnFormula>N2*O2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{E7529637-516C-4BAC-9F9C-F3BCAD77EB6C}" name="ΔVboot (V)" dataDxfId="15">
+    <tableColumn id="16" xr3:uid="{E7529637-516C-4BAC-9F9C-F3BCAD77EB6C}" name="ΔVboot (V)" dataDxfId="19">
       <calculatedColumnFormula>P2/M2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{A1106862-E575-4A15-BDC9-291F1DC16EA8}" name="Fmax (kHz)" dataDxfId="14"/>
-    <tableColumn id="18" xr3:uid="{ED56DF9B-39E7-4337-92AA-A19107C957F6}" name="Toff (µs)" dataDxfId="13">
+    <tableColumn id="17" xr3:uid="{A1106862-E575-4A15-BDC9-291F1DC16EA8}" name="Fmax (kHz)" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{ED56DF9B-39E7-4337-92AA-A19107C957F6}" name="Toff (µs)" dataDxfId="17">
       <calculatedColumnFormula>1/R2/1000*(1-K2/100)*1000000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{5EF5F032-1924-4722-B113-497A8A53F9F9}" name="Toff secu (NU)" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{317078D3-172D-4084-B914-D44E27AF4622}" name="Tcharge (µs)" dataDxfId="11">
+    <tableColumn id="19" xr3:uid="{5EF5F032-1924-4722-B113-497A8A53F9F9}" name="Toff secu (NU)" dataDxfId="16"/>
+    <tableColumn id="20" xr3:uid="{317078D3-172D-4084-B914-D44E27AF4622}" name="Tcharge (µs)" dataDxfId="15">
       <calculatedColumnFormula>S2/T2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{C74CCBDA-ECD0-48F4-BDD1-B7B52CDCD12C}" name="V0 (V)" dataDxfId="10">
+    <tableColumn id="21" xr3:uid="{C74CCBDA-ECD0-48F4-BDD1-B7B52CDCD12C}" name="V0 (V)" dataDxfId="14">
       <calculatedColumnFormula>A2-B2-Q2-Tableau1[[#This Row],[Vr,100mA (V)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{24CB70CF-920B-4509-9638-5D3F89476E1B}" name="Vddboot (V)" dataDxfId="9">
+    <tableColumn id="22" xr3:uid="{24CB70CF-920B-4509-9638-5D3F89476E1B}" name="Vddboot (V)" dataDxfId="13">
       <calculatedColumnFormula>A2-B2-Tableau1[[#This Row],[Vr,100mA (V)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{97086D48-76D1-44FE-9798-1E4B672A9D3C}" name="Rfint (Ω)" dataDxfId="8"/>
-    <tableColumn id="25" xr3:uid="{CA25B27B-2081-46A3-A11C-C04EC8E9925A}" name="Rfext (Ω)" dataDxfId="7"/>
-    <tableColumn id="26" xr3:uid="{D571851B-D502-4394-822B-26D2605F0715}" name="Rf (Ω)" dataDxfId="6">
+    <tableColumn id="23" xr3:uid="{97086D48-76D1-44FE-9798-1E4B672A9D3C}" name="Rfint (Ω)" dataDxfId="12"/>
+    <tableColumn id="25" xr3:uid="{CA25B27B-2081-46A3-A11C-C04EC8E9925A}" name="Rfext (Ω)" dataDxfId="11"/>
+    <tableColumn id="26" xr3:uid="{D571851B-D502-4394-822B-26D2605F0715}" name="Rf (Ω)" dataDxfId="10">
       <calculatedColumnFormula>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0, 1/(1/Tableau1[[#This Row],[Rfint (Ω)]]+1/Tableau1[[#This Row],[Rfext (Ω)]]), Tableau1[[#This Row],[Rfint (Ω)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{C72492AB-BD7B-405B-867F-5ADF45417C24}" name="Vfinal (V)" dataDxfId="5">
+    <tableColumn id="24" xr3:uid="{C72492AB-BD7B-405B-867F-5ADF45417C24}" name="Vfinal (V)" dataDxfId="9">
       <calculatedColumnFormula>(V2-W2)*EXP(-U2*10^-6/Tableau1[[#This Row],[Rf (Ω)]]/(P2*10^-9))+W2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{4A2A1E44-66D8-4309-9DC7-637AF6F8770A}" name="Imaxext (A)" dataDxfId="4">
+    <tableColumn id="30" xr3:uid="{4A2A1E44-66D8-4309-9DC7-637AF6F8770A}" name="Imaxext (A)" dataDxfId="8">
       <calculatedColumnFormula>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0,Tableau1[[#This Row],[Vdd (V)]]/Tableau1[[#This Row],[Rfext (Ω)]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{B3DB0F25-7B1B-46E1-B7A4-6C280BA75465}" name="3Tau (µs)" dataDxfId="3">
+    <tableColumn id="31" xr3:uid="{B3DB0F25-7B1B-46E1-B7A4-6C280BA75465}" name="3Tau (µs)" dataDxfId="7">
       <calculatedColumnFormula>IF(Tableau1[[#This Row],[Imaxext (A)]]&gt;0,3*Tableau1[[#This Row],[Rf (Ω)]]*Tableau1[[#This Row],[Cboot (nF)]]*10^-3,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="27" xr3:uid="{35D08FA4-5098-49A1-96BF-78D1CE0C53DF}" name="Max Fsw (kHz)" dataDxfId="6"/>
+    <tableColumn id="29" xr3:uid="{3AF36601-E787-45F8-A32B-D5DA2AC7BD86}" name="Qfreq_max (nC)" dataDxfId="5">
+      <calculatedColumnFormula>(G2*10^-9+H2/L2*10^-6+(I2+J2)/L2*10^-6*K2/100)/10^-9</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="32" xr3:uid="{35C9A496-3EC8-43C9-89D9-26990B92E82D}" name="Safety (NU)" dataDxfId="4"/>
+    <tableColumn id="33" xr3:uid="{44D3BF9C-C6B6-41CA-BB2A-43E2DA8DB723}" name="ImaxIn (mA)" dataDxfId="0">
+      <calculatedColumnFormula>Tableau1[[#This Row],[Qfreq_max (nC)]]*Tableau1[[#This Row],[Max Fsw (kHz)]]*0.001</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1432,7 +1462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46177FA7-98B1-43B3-8996-93B4082609D4}">
-  <dimension ref="B2:S41"/>
+  <dimension ref="B2:S38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.453125" customWidth="1"/>
@@ -1455,18 +1485,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="43"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="45"/>
       <c r="M2" s="8" t="s">
         <v>22</v>
       </c>
@@ -2404,11 +2434,11 @@
         <f t="shared" si="4"/>
         <v>3.9062499999999996</v>
       </c>
-      <c r="M19" s="38" t="s">
+      <c r="M19" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="N19" s="39"/>
-      <c r="O19" s="40"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="42"/>
       <c r="Q19" t="s">
         <v>20</v>
       </c>
@@ -3136,29 +3166,24 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="H41" t="s">
-        <v>137</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="M19:O19"/>
     <mergeCell ref="B2:K2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:F35">
-    <cfRule type="cellIs" dxfId="2" priority="14" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="14" operator="between">
       <formula>0</formula>
       <formula>$N$22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G36">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>$N$16</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H35">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>$N$10/1000*$N$11</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3186,14 +3211,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B3" s="26" t="s">
@@ -3789,43 +3814,47 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FD2DCF-3994-4A7C-BD62-D1225B43EB25}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="1.6328125" customWidth="1"/>
+    <col min="4" max="4" width="1.6328125" customWidth="1"/>
+    <col min="5" max="5" width="1.81640625" customWidth="1"/>
     <col min="6" max="6" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="1.6328125" customWidth="1"/>
+    <col min="7" max="7" width="4.90625" customWidth="1"/>
+    <col min="8" max="10" width="1.6328125" customWidth="1"/>
     <col min="11" max="11" width="13.81640625" customWidth="1"/>
-    <col min="12" max="12" width="1.6328125" customWidth="1"/>
-    <col min="13" max="13" width="9.1796875" customWidth="1"/>
+    <col min="12" max="12" width="15.6328125" customWidth="1"/>
+    <col min="13" max="13" width="8.6328125" customWidth="1"/>
     <col min="14" max="14" width="16.36328125" customWidth="1"/>
     <col min="15" max="15" width="13.08984375" customWidth="1"/>
     <col min="16" max="16" width="12.453125" customWidth="1"/>
     <col min="17" max="17" width="11.90625" customWidth="1"/>
     <col min="18" max="18" width="12.26953125" customWidth="1"/>
-    <col min="19" max="20" width="1.6328125" customWidth="1"/>
-    <col min="21" max="21" width="13.36328125" customWidth="1"/>
+    <col min="19" max="21" width="6.1796875" customWidth="1"/>
     <col min="22" max="22" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13" customWidth="1"/>
-    <col min="24" max="24" width="1.6328125" customWidth="1"/>
+    <col min="24" max="24" width="7.81640625" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="8.26953125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="12.90625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="11" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.7265625" customWidth="1"/>
+    <col min="33" max="33" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>108</v>
       </c>
       <c r="B1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" t="s">
         <v>132</v>
-      </c>
-      <c r="C1" t="s">
-        <v>133</v>
       </c>
       <c r="D1" t="s">
         <v>109</v>
@@ -3834,7 +3863,7 @@
         <v>110</v>
       </c>
       <c r="F1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G1" t="s">
         <v>111</v>
@@ -3849,7 +3878,7 @@
         <v>112</v>
       </c>
       <c r="K1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L1" t="s">
         <v>115</v>
@@ -3858,55 +3887,67 @@
         <v>116</v>
       </c>
       <c r="N1" t="s">
+        <v>136</v>
+      </c>
+      <c r="O1" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>119</v>
+      </c>
+      <c r="R1" t="s">
+        <v>122</v>
+      </c>
+      <c r="S1" t="s">
+        <v>124</v>
+      </c>
+      <c r="T1" t="s">
+        <v>125</v>
+      </c>
+      <c r="U1" t="s">
+        <v>126</v>
+      </c>
+      <c r="V1" t="s">
         <v>117</v>
       </c>
-      <c r="O1" t="s">
-        <v>122</v>
-      </c>
-      <c r="P1" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="W1" t="s">
         <v>120</v>
       </c>
-      <c r="R1" t="s">
-        <v>123</v>
-      </c>
-      <c r="S1" t="s">
-        <v>125</v>
-      </c>
-      <c r="T1" t="s">
-        <v>126</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="X1" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA1" t="s">
         <v>127</v>
       </c>
-      <c r="V1" t="s">
-        <v>118</v>
-      </c>
-      <c r="W1" t="s">
-        <v>121</v>
-      </c>
-      <c r="X1" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>128</v>
-      </c>
       <c r="AB1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC1" t="s">
         <v>134</v>
       </c>
-      <c r="AC1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>10</v>
       </c>
@@ -3959,25 +4000,25 @@
       <c r="P2" s="32">
         <v>300</v>
       </c>
-      <c r="Q2" s="45">
+      <c r="Q2" s="38">
         <f>P2/M2</f>
         <v>1.2592916484477481</v>
       </c>
       <c r="R2" s="1">
         <v>128</v>
       </c>
-      <c r="S2" s="46">
+      <c r="S2" s="39">
         <f>1/R2/1000*(1-K2/100)*1000000</f>
         <v>0.39062500000000033</v>
       </c>
       <c r="T2" s="1">
         <v>2</v>
       </c>
-      <c r="U2" s="46">
+      <c r="U2" s="39">
         <f>S2/T2</f>
         <v>0.19531250000000017</v>
       </c>
-      <c r="V2" s="46">
+      <c r="V2" s="39">
         <f>A2-B2-Q2-Tableau1[[#This Row],[Vr,100mA (V)]]</f>
         <v>7.9307083515522514</v>
       </c>
@@ -3991,31 +4032,45 @@
       <c r="Y2" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Z2" s="46">
+      <c r="Z2" s="39">
         <f>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0, 1/(1/Tableau1[[#This Row],[Rfint (Ω)]]+1/Tableau1[[#This Row],[Rfext (Ω)]]), Tableau1[[#This Row],[Rfint (Ω)]])</f>
         <v>4.1221804511278188</v>
       </c>
-      <c r="AA2" s="46">
+      <c r="AA2" s="39">
         <f>(V2-W2)*EXP(-U2*10^-6/Tableau1[[#This Row],[Rf (Ω)]]/(P2*10^-9))+W2</f>
         <v>8.114685536921213</v>
       </c>
-      <c r="AB2" s="45">
+      <c r="AB2" s="38">
         <f>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0,Tableau1[[#This Row],[Vdd (V)]]/Tableau1[[#This Row],[Rfext (Ω)]],0)</f>
         <v>1.9607843137254903</v>
       </c>
-      <c r="AC2" s="46">
+      <c r="AC2" s="39">
         <f>IF(Tableau1[[#This Row],[Imaxext (A)]]&gt;0,3*Tableau1[[#This Row],[Rf (Ω)]]*Tableau1[[#This Row],[Cboot (nF)]]*10^-3,0)</f>
         <v>3.7099624060150371</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD2" s="39">
+        <v>128</v>
+      </c>
+      <c r="AE2" s="39">
+        <f>(G2*10^-9+H2/L2*10^-6+(I2+J2)/L2*10^-6*K2/100)/10^-9</f>
+        <v>238.22916666666666</v>
+      </c>
+      <c r="AF2" s="39">
+        <v>2</v>
+      </c>
+      <c r="AG2" s="39">
+        <f>Tableau1[[#This Row],[Qfreq_max (nC)]]*Tableau1[[#This Row],[Max Fsw (kHz)]]*0.001</f>
+        <v>30.493333333333332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>10</v>
       </c>
       <c r="B3" s="1">
         <v>0.3</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="1">
         <f>Tableau1[[#This Row],[Rfext (Ω)]]*0.1</f>
         <v>0.51</v>
       </c>
@@ -4025,7 +4080,7 @@
       <c r="E3" s="1">
         <v>0.27</v>
       </c>
-      <c r="F3" s="47">
+      <c r="F3" s="1">
         <f>A3-B3-D3-E3-Tableau1[[#This Row],[Vr,100mA (V)]]</f>
         <v>2.919999999999999</v>
       </c>
@@ -4045,46 +4100,46 @@
         <v>95</v>
       </c>
       <c r="L3" s="1">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M3" s="32">
         <f>(G3*10^-9+H3/L3*10^-6+(I3+J3)/L3*10^-6*K3/100)/10^-9</f>
-        <v>403.74999999999994</v>
+        <v>238.22916666666666</v>
       </c>
       <c r="N3" s="32">
         <f>M3/F3</f>
-        <v>138.27054794520549</v>
+        <v>81.585331050228334</v>
       </c>
       <c r="O3" s="1">
         <v>3</v>
       </c>
       <c r="P3" s="32">
         <f>N3*O3</f>
-        <v>414.81164383561645</v>
-      </c>
-      <c r="Q3" s="45">
+        <v>244.75599315068501</v>
+      </c>
+      <c r="Q3" s="38">
         <f>P3/M3</f>
-        <v>1.0273972602739727</v>
+        <v>1.0273972602739729</v>
       </c>
       <c r="R3" s="1">
         <v>128</v>
       </c>
-      <c r="S3" s="46">
+      <c r="S3" s="39">
         <f>1/R3/1000*(1-K3/100)*1000000</f>
         <v>0.39062500000000033</v>
       </c>
       <c r="T3" s="1">
         <v>2</v>
       </c>
-      <c r="U3" s="46">
+      <c r="U3" s="39">
         <f>S3/T3</f>
         <v>0.19531250000000017</v>
       </c>
-      <c r="V3" s="46">
+      <c r="V3" s="39">
         <f>A3-B3-Q3-Tableau1[[#This Row],[Vr,100mA (V)]]</f>
-        <v>8.1626027397260277</v>
-      </c>
-      <c r="W3" s="47">
+        <v>8.1626027397260259</v>
+      </c>
+      <c r="W3" s="1">
         <f>A3-B3-Tableau1[[#This Row],[Vr,100mA (V)]]</f>
         <v>9.19</v>
       </c>
@@ -4094,21 +4149,35 @@
       <c r="Y3" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Z3" s="46">
+      <c r="Z3" s="39">
         <f>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0, 1/(1/Tableau1[[#This Row],[Rfint (Ω)]]+1/Tableau1[[#This Row],[Rfext (Ω)]]), Tableau1[[#This Row],[Rfint (Ω)]])</f>
         <v>4.1221804511278188</v>
       </c>
-      <c r="AA3" s="46">
+      <c r="AA3" s="39">
         <f>(V3-W3)*EXP(-U3*10^-6/Tableau1[[#This Row],[Rf (Ω)]]/(P3*10^-9))+W3</f>
-        <v>8.2735006704566629</v>
-      </c>
-      <c r="AB3" s="45">
+        <v>8.3434241159982783</v>
+      </c>
+      <c r="AB3" s="38">
         <f>IF(Tableau1[[#This Row],[Rfext (Ω)]]&gt;0,Tableau1[[#This Row],[Vdd (V)]]/Tableau1[[#This Row],[Rfext (Ω)]],0)</f>
         <v>1.9607843137254903</v>
       </c>
-      <c r="AC3" s="46">
+      <c r="AC3" s="39">
         <f>IF(Tableau1[[#This Row],[Imaxext (A)]]&gt;0,3*Tableau1[[#This Row],[Rf (Ω)]]*Tableau1[[#This Row],[Cboot (nF)]]*10^-3,0)</f>
-        <v>5.129785347358121</v>
+        <v>3.0267851107863843</v>
+      </c>
+      <c r="AD3" s="39">
+        <v>128</v>
+      </c>
+      <c r="AE3" s="39">
+        <f>(G3*10^-9+H3/L3*10^-6+(I3+J3)/L3*10^-6*K3/100)/10^-9</f>
+        <v>238.22916666666666</v>
+      </c>
+      <c r="AF3" s="39">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="39">
+        <f>Tableau1[[#This Row],[Qfreq_max (nC)]]*Tableau1[[#This Row],[Max Fsw (kHz)]]*0.001</f>
+        <v>30.493333333333332</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Kururugi-ESC-calculs.xlsx
+++ b/resources/Kururugi-ESC-calculs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\binon\Desktop\Kururugi-ESC-Dev-Board\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A54ED9-CDC6-4C22-9B90-6ED0D557FDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096987B4-CBB1-49F6-A0B8-41FDA1FBFEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
   </bookViews>
@@ -28,7 +28,6 @@
     <definedName name="Radc">INPUTS!$H$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -71,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="288">
   <si>
     <t>R1 (kOhm)</t>
   </si>
@@ -1176,6 +1175,9 @@
   </si>
   <si>
     <t>Cbootmin,safe (nF)</t>
+  </si>
+  <si>
+    <t>Max current off (A)</t>
   </si>
 </sst>
 </file>
@@ -1604,7 +1606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1788,6 +1790,33 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1806,37 +1835,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1871,15 +1872,13 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1891,13 +1890,8 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="167" formatCode="0.0"/>
@@ -1983,6 +1977,13 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2487,75 +2488,75 @@
     <tableColumn id="11" xr3:uid="{1CBF1355-D31F-456C-80BE-6CC8C444F650}" name="Fsw min (kHz)" dataDxfId="35">
       <calculatedColumnFormula>_xlfn.XLOOKUP(INPUTS!A3, DB_limits[Name],DB_limits[Fmin (kHz)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{BE60760C-B4C3-4724-A105-5DF37CE7A319}" name="Consomation (nC/period)" dataDxfId="5">
+    <tableColumn id="39" xr3:uid="{BE60760C-B4C3-4724-A105-5DF37CE7A319}" name="Consomation (nC/period)" dataDxfId="34">
       <calculatedColumnFormula>CAL_HB[[#This Row],[Qt,on (nC)]]-CAL_HB[[#This Row],[Qg (nC)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{1E038DBA-495F-43B9-B606-822FB74520D5}" name="Qt,on (nC)" dataDxfId="34">
+    <tableColumn id="12" xr3:uid="{1E038DBA-495F-43B9-B606-822FB74520D5}" name="Qt,on (nC)" dataDxfId="33">
       <calculatedColumnFormula>(   I2*10^-9 + J2/N2*10^-6 + (K2+L2)/N2*10^-6*M2/100   )/10^-9</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{8AC582AB-F2DC-4941-822A-45B9871B889A}" name="Qt,off (nC)" dataDxfId="33">
+    <tableColumn id="35" xr3:uid="{8AC582AB-F2DC-4941-822A-45B9871B889A}" name="Qt,off (nC)" dataDxfId="32">
       <calculatedColumnFormula>(   I2*10^-9 - J2/N2*10^-6 - (K2+L2)/N2*10^-6*(1-M2/100)   )/10^-9</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{706960C6-D4AA-40BF-A7C4-F0C4473DA5E5}" name="Column1" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{C79274CC-E2A1-41D2-A761-D54CC7A29829}" name="Cbootmin (nF)" dataDxfId="32">
+    <tableColumn id="38" xr3:uid="{706960C6-D4AA-40BF-A7C4-F0C4473DA5E5}" name="Column1" dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{C79274CC-E2A1-41D2-A761-D54CC7A29829}" name="Cbootmin (nF)" dataDxfId="30">
       <calculatedColumnFormula>P2/H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FA3E1CDB-C23D-4FB1-B19E-9DA04D3955EB}" name="C secu (NU)" dataDxfId="31">
+    <tableColumn id="14" xr3:uid="{FA3E1CDB-C23D-4FB1-B19E-9DA04D3955EB}" name="C secu (NU)" dataDxfId="29">
       <calculatedColumnFormula>INPUTS!N10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{F2329A40-7530-43DD-9A8D-D9481FE6DDA8}" name="Cbootmin,safe (nF)" dataDxfId="30">
+    <tableColumn id="15" xr3:uid="{F2329A40-7530-43DD-9A8D-D9481FE6DDA8}" name="Cbootmin,safe (nF)" dataDxfId="28">
       <calculatedColumnFormula>INPUTS!N15</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{E7529637-516C-4BAC-9F9C-F3BCAD77EB6C}" name="ΔVboot (V)" dataDxfId="29">
+    <tableColumn id="16" xr3:uid="{E7529637-516C-4BAC-9F9C-F3BCAD77EB6C}" name="ΔVboot (V)" dataDxfId="27">
       <calculatedColumnFormula>U2/P2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{A1106862-E575-4A15-BDC9-291F1DC16EA8}" name="Fmax (kHz)" dataDxfId="28">
+    <tableColumn id="17" xr3:uid="{A1106862-E575-4A15-BDC9-291F1DC16EA8}" name="Fmax (kHz)" dataDxfId="26">
       <calculatedColumnFormula>INPUTS!B6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{ED56DF9B-39E7-4337-92AA-A19107C957F6}" name="Toff (µs)" dataDxfId="27">
+    <tableColumn id="18" xr3:uid="{ED56DF9B-39E7-4337-92AA-A19107C957F6}" name="Toff (µs)" dataDxfId="25">
       <calculatedColumnFormula>1/W2/1000*(1-M2/100)*1000000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{5EF5F032-1924-4722-B113-497A8A53F9F9}" name="Toff,charge (µs)" dataDxfId="26">
+    <tableColumn id="19" xr3:uid="{5EF5F032-1924-4722-B113-497A8A53F9F9}" name="Toff,charge (µs)" dataDxfId="24">
       <calculatedColumnFormula>CAL_HB[[#This Row],[Toff (µs)]]-INPUTS!B18/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{317078D3-172D-4084-B914-D44E27AF4622}" name="Tcharge (µs)" dataDxfId="25">
+    <tableColumn id="20" xr3:uid="{317078D3-172D-4084-B914-D44E27AF4622}" name="Tcharge (µs)" dataDxfId="23">
       <calculatedColumnFormula>CAL_HB[[#This Row],[Toff,charge (µs)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{C74CCBDA-ECD0-48F4-BDD1-B7B52CDCD12C}" name="Vboot0 (V)" dataDxfId="24">
+    <tableColumn id="21" xr3:uid="{C74CCBDA-ECD0-48F4-BDD1-B7B52CDCD12C}" name="Vboot0 (V)" dataDxfId="22">
       <calculatedColumnFormula>A2-V2-CAL_HB[[#This Row],[Vfext,100mA (V)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{24CB70CF-920B-4509-9638-5D3F89476E1B}" name="Vbootinf (V)" dataDxfId="23">
+    <tableColumn id="22" xr3:uid="{24CB70CF-920B-4509-9638-5D3F89476E1B}" name="Vbootinf (V)" dataDxfId="21">
       <calculatedColumnFormula>A2-CAL_HB[[#This Row],[Vfext,100mA (V)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{D571851B-D502-4394-822B-26D2605F0715}" name="Rf (Ω)" dataDxfId="22">
+    <tableColumn id="26" xr3:uid="{D571851B-D502-4394-822B-26D2605F0715}" name="Rf (Ω)" dataDxfId="20">
       <calculatedColumnFormula>IF(CAL_HB[[#This Row],[Rboot,ext (Ω)]]&gt;0, 1/(1/CAL_HB[[#This Row],[Rboot,int (Ω)]]+1/CAL_HB[[#This Row],[Rboot,ext (Ω)]]), CAL_HB[[#This Row],[Rboot,int (Ω)]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{C72492AB-BD7B-405B-867F-5ADF45417C24}" name="Vbootfinal (V)" dataDxfId="21">
+    <tableColumn id="24" xr3:uid="{C72492AB-BD7B-405B-867F-5ADF45417C24}" name="Vbootfinal (V)" dataDxfId="19">
       <calculatedColumnFormula>(AA2-AB2)*EXP(-Z2*10^-6/CAL_HB[[#This Row],[Rf (Ω)]]/(U2*10^-9))+AB2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{4A2A1E44-66D8-4309-9DC7-637AF6F8770A}" name="Imaxext (A)" dataDxfId="20">
+    <tableColumn id="30" xr3:uid="{4A2A1E44-66D8-4309-9DC7-637AF6F8770A}" name="Imaxext (A)" dataDxfId="18">
       <calculatedColumnFormula>IF(CAL_HB[[#This Row],[Rboot,ext (Ω)]]&gt;0,CAL_HB[[#This Row],[Vdd (V)]]/CAL_HB[[#This Row],[Rboot,ext (Ω)]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{B3DB0F25-7B1B-46E1-B7A4-6C280BA75465}" name="Tau Cboot (µs)" dataDxfId="19">
+    <tableColumn id="31" xr3:uid="{B3DB0F25-7B1B-46E1-B7A4-6C280BA75465}" name="Tau Cboot (µs)" dataDxfId="17">
       <calculatedColumnFormula>IF(CAL_HB[[#This Row],[Imaxext (A)]]&gt;0,CAL_HB[[#This Row],[Rf (Ω)]]*CAL_HB[[#This Row],[Cbootmin,safe (nF)]]*10^-3,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{35D08FA4-5098-49A1-96BF-78D1CE0C53DF}" name="Max Fsw (kHz)" dataDxfId="18">
+    <tableColumn id="27" xr3:uid="{35D08FA4-5098-49A1-96BF-78D1CE0C53DF}" name="Max Fsw (kHz)" dataDxfId="16">
       <calculatedColumnFormula>INPUTS!B6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{3AF36601-E787-45F8-A32B-D5DA2AC7BD86}" name="Qfreq_max (nC)" dataDxfId="17">
+    <tableColumn id="29" xr3:uid="{3AF36601-E787-45F8-A32B-D5DA2AC7BD86}" name="Qfreq_max (nC)" dataDxfId="15">
       <calculatedColumnFormula>(I2*10^-9+J2/CAL_HB[[#This Row],[Max Fsw (kHz)]]*10^-6+(K2+L2)/CAL_HB[[#This Row],[Max Fsw (kHz)]]*10^-6*M2/100)/10^-9</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{35C9A496-3EC8-43C9-89D9-26990B92E82D}" name="Safety (NU)" dataDxfId="16"/>
-    <tableColumn id="33" xr3:uid="{44D3BF9C-C6B6-41CA-BB2A-43E2DA8DB723}" name="Imaxmeqn (mA)" dataDxfId="15">
+    <tableColumn id="32" xr3:uid="{35C9A496-3EC8-43C9-89D9-26990B92E82D}" name="Safety (NU)" dataDxfId="14"/>
+    <tableColumn id="33" xr3:uid="{44D3BF9C-C6B6-41CA-BB2A-43E2DA8DB723}" name="Imaxmeqn (mA)" dataDxfId="13">
       <calculatedColumnFormula>CAL_HB[[#This Row],[Qfreq_max (nC)]]*CAL_HB[[#This Row],[Max Fsw (kHz)]]*0.001</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{4A87F850-550F-4B9F-9C8B-7714375CA89B}" name="Dissipated in Rg hs pu (W)" dataDxfId="14">
+    <tableColumn id="36" xr3:uid="{4A87F850-550F-4B9F-9C8B-7714375CA89B}" name="Dissipated in Rg hs pu (W)" dataDxfId="12">
       <calculatedColumnFormula>INPUTS!N34*INPUTS!N21/(INPUTS!N21+INPUTS!N5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{6EB2A3EE-5FFD-49F0-A8BB-7F58373BC0C5}" name="Tau Qg,on (µs)" dataDxfId="13">
+    <tableColumn id="37" xr3:uid="{6EB2A3EE-5FFD-49F0-A8BB-7F58373BC0C5}" name="Tau Qg,on (µs)" dataDxfId="11">
       <calculatedColumnFormula>INPUTS!N15*((INPUTS!N5+INPUTS!N6)/2+INPUTS!N21)/1000*INPUTS!N28</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{E8EC5DFA-18F4-473D-9D9E-E906C667A938}" name="Tau Qg,off (ns)" dataDxfId="4">
+    <tableColumn id="34" xr3:uid="{E8EC5DFA-18F4-473D-9D9E-E906C667A938}" name="Tau Qg,off (ns)" dataDxfId="10">
       <calculatedColumnFormula>CAL_HB[[#This Row],[Cbootmin,safe (nF)]]*(1/(1/INPUTS!N21+1/INPUTS!N20) + (INPUTS!N8+INPUTS!N7)/2)/1000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2618,7 +2619,7 @@
     <tableColumn id="4" xr3:uid="{2B471E9B-6758-4DEE-9999-F8CDA58ED934}" name="Vinadc = Vdd (V)"/>
     <tableColumn id="5" xr3:uid="{4A4F57B9-E128-4533-9E88-3DEB5AC39471}" name="Cadc,max (pF)"/>
     <tableColumn id="6" xr3:uid="{024B3B03-8354-4E20-8FDB-FEE3DD0DAC7D}" name="Fsamp,max (MHz)"/>
-    <tableColumn id="7" xr3:uid="{71EAE56C-7786-4272-AB14-E79BB1020D87}" name="Vin,max@vin (V)" dataDxfId="12">
+    <tableColumn id="7" xr3:uid="{71EAE56C-7786-4272-AB14-E79BB1020D87}" name="Vin,max@vin (V)" dataDxfId="6">
       <calculatedColumnFormula>DB_ADC[[#This Row],[Vinadc = Vdd (V)]]+0.3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2653,12 +2654,12 @@
     <tableColumn id="17" xr3:uid="{8828BB6B-7ABC-4BA6-9E1B-5C5BE5105F08}" name="Iph typ (A)"/>
     <tableColumn id="18" xr3:uid="{1F68324A-F399-4C91-BE2D-EFEF49ED6790}" name="ToF Iph typ (%)"/>
     <tableColumn id="15" xr3:uid="{5ED528D3-58D8-4741-86F9-6B25ECFBAFAE}" name="Iph max (A@Xs)"/>
-    <tableColumn id="19" xr3:uid="{305A20A8-F4F6-4F6B-BAC2-2A71E7628C5B}" name="ToF Iph max (%)" dataDxfId="11">
+    <tableColumn id="19" xr3:uid="{305A20A8-F4F6-4F6B-BAC2-2A71E7628C5B}" name="ToF Iph max (%)" dataDxfId="5">
       <calculatedColumnFormula>100-DB_limits[[#This Row],[ToF Iph typ (%)]]-DB_limits[[#This Row],[ToF Iph spike (%)]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{4D711E23-0E80-41C8-A566-2B43E0C79E4C}" name="Iph spike (A@Xms)"/>
     <tableColumn id="20" xr3:uid="{0DE3AE78-D822-41D8-B4E1-38C2CE21BE19}" name="ToF Iph spike (%)"/>
-    <tableColumn id="21" xr3:uid="{0DD4A4A7-CFA4-4B62-89A9-A58896065868}" name="Iph mean (A)" dataDxfId="10">
+    <tableColumn id="21" xr3:uid="{0DD4A4A7-CFA4-4B62-89A9-A58896065868}" name="Iph mean (A)" dataDxfId="4">
       <calculatedColumnFormula>DB_limits[[#This Row],[Iph typ (A)]]*DB_limits[[#This Row],[ToF Iph typ (%)]]%+DB_limits[[#This Row],[Iph max (A@Xs)]]*DB_limits[[#This Row],[ToF Iph max (%)]]%+DB_limits[[#This Row],[Iph spike (A@Xms)]]*DB_limits[[#This Row],[ToF Iph spike (%)]]%</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3018,71 +3019,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="80" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="D1" s="90" t="s">
+      <c r="B1" s="80"/>
+      <c r="D1" s="80" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="90"/>
-      <c r="G1" s="88" t="s">
+      <c r="E1" s="80"/>
+      <c r="G1" s="84" t="s">
         <v>171</v>
       </c>
-      <c r="H1" s="89"/>
-      <c r="J1" s="88" t="s">
+      <c r="H1" s="85"/>
+      <c r="J1" s="84" t="s">
         <v>174</v>
       </c>
-      <c r="K1" s="89"/>
-      <c r="M1" s="90" t="s">
+      <c r="K1" s="85"/>
+      <c r="M1" s="80" t="s">
         <v>186</v>
       </c>
-      <c r="N1" s="90"/>
+      <c r="N1" s="80"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="87"/>
+      <c r="B2" s="81"/>
       <c r="C2" s="31"/>
-      <c r="D2" s="87" t="s">
+      <c r="D2" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="G2" s="85" t="s">
+      <c r="E2" s="81"/>
+      <c r="G2" s="82" t="s">
         <v>130</v>
       </c>
-      <c r="H2" s="86"/>
-      <c r="J2" s="85" t="s">
+      <c r="H2" s="83"/>
+      <c r="J2" s="82" t="s">
         <v>130</v>
       </c>
-      <c r="K2" s="86"/>
-      <c r="M2" s="87" t="s">
+      <c r="K2" s="83"/>
+      <c r="M2" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="N2" s="87"/>
+      <c r="N2" s="81"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="91" t="s">
+      <c r="A3" s="79" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="D3" s="91" t="s">
+      <c r="B3" s="79"/>
+      <c r="D3" s="79" t="s">
         <v>275</v>
       </c>
-      <c r="E3" s="91"/>
-      <c r="G3" s="92" t="s">
+      <c r="E3" s="79"/>
+      <c r="G3" s="86" t="s">
         <v>151</v>
       </c>
-      <c r="H3" s="93"/>
-      <c r="J3" s="92" t="s">
+      <c r="H3" s="87"/>
+      <c r="J3" s="86" t="s">
         <v>151</v>
       </c>
-      <c r="K3" s="93"/>
-      <c r="M3" s="91" t="s">
+      <c r="K3" s="87"/>
+      <c r="M3" s="79" t="s">
         <v>187</v>
       </c>
-      <c r="N3" s="91"/>
+      <c r="N3" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="38" t="str">
@@ -3269,14 +3270,14 @@
         <f>_xlfn.XLOOKUP(D3, DB_Mostfet[Part], DB_Mostfet[Rds,on@10V typ(mΩ)])</f>
         <v>1.8</v>
       </c>
-      <c r="G8" s="85" t="s">
+      <c r="G8" s="82" t="s">
         <v>150</v>
       </c>
-      <c r="H8" s="86"/>
-      <c r="J8" s="87" t="s">
+      <c r="H8" s="83"/>
+      <c r="J8" s="81" t="s">
         <v>150</v>
       </c>
-      <c r="K8" s="87"/>
+      <c r="K8" s="81"/>
       <c r="M8" s="38" t="str">
         <f>DB_GD[[#Headers],[Rpd,ls (Ω)]]</f>
         <v>Rpd,ls (Ω)</v>
@@ -3373,10 +3374,10 @@
         <f>_xlfn.XLOOKUP(D3, DB_Mostfet[Part], DB_Mostfet[Fall time (ns)])</f>
         <v>3</v>
       </c>
-      <c r="G11" s="85" t="s">
+      <c r="G11" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="H11" s="86"/>
+      <c r="H11" s="83"/>
       <c r="J11" s="58" t="s">
         <v>175</v>
       </c>
@@ -3414,14 +3415,14 @@
         <f>H9/H7*1000</f>
         <v>41.666666666666664</v>
       </c>
-      <c r="J12" s="85" t="s">
+      <c r="J12" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="K12" s="86"/>
-      <c r="M12" s="87" t="s">
+      <c r="K12" s="83"/>
+      <c r="M12" s="81" t="s">
         <v>149</v>
       </c>
-      <c r="N12" s="87"/>
+      <c r="N12" s="81"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="38" t="str">
@@ -3473,10 +3474,10 @@
         <f>_xlfn.XLOOKUP(D3, DB_Mostfet[Part], DB_Mostfet[Size (mm)])</f>
         <v>5x6</v>
       </c>
-      <c r="G14" s="88" t="s">
+      <c r="G14" s="84" t="s">
         <v>172</v>
       </c>
-      <c r="H14" s="89"/>
+      <c r="H14" s="85"/>
       <c r="M14" s="32" t="s">
         <v>193</v>
       </c>
@@ -3502,10 +3503,10 @@
         <f>_xlfn.XLOOKUP(D3, DB_Mostfet[Part], DB_Mostfet[JLCPBC stock])</f>
         <v>Yes</v>
       </c>
-      <c r="G15" s="85" t="s">
+      <c r="G15" s="82" t="s">
         <v>150</v>
       </c>
-      <c r="H15" s="86"/>
+      <c r="H15" s="83"/>
       <c r="J15" s="48" t="s">
         <v>176</v>
       </c>
@@ -3538,10 +3539,10 @@
       <c r="H16" s="2">
         <v>390</v>
       </c>
-      <c r="J16" s="85" t="s">
+      <c r="J16" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="K16" s="86"/>
+      <c r="K16" s="83"/>
       <c r="M16" s="32" t="str">
         <f>CAL_HB[[#Headers],[Qt,on (nC)]]</f>
         <v>Qt,on (nC)</v>
@@ -3605,10 +3606,10 @@
         <f>CAL_ISENSE!F9</f>
         <v>0.4</v>
       </c>
-      <c r="M18" s="88" t="s">
+      <c r="M18" s="84" t="s">
         <v>185</v>
       </c>
-      <c r="N18" s="89"/>
+      <c r="N18" s="85"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D19" s="32" t="s">
@@ -3631,10 +3632,10 @@
         <f>CAL_ISENSE!E9</f>
         <v>0.64</v>
       </c>
-      <c r="M19" s="85" t="s">
+      <c r="M19" s="82" t="s">
         <v>150</v>
       </c>
-      <c r="N19" s="86"/>
+      <c r="N19" s="83"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="48" t="s">
@@ -3665,7 +3666,7 @@
         <v>179</v>
       </c>
       <c r="N20" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
@@ -3697,7 +3698,7 @@
         <v>202</v>
       </c>
       <c r="N21" s="2">
-        <v>3</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -3714,10 +3715,10 @@
         <f>E17*B16*(E11+E10)*B6*10^-6/2</f>
         <v>0.14916115199999999</v>
       </c>
-      <c r="G22" s="85" t="s">
+      <c r="G22" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="H22" s="86"/>
+      <c r="H22" s="83"/>
       <c r="J22" s="32" t="s">
         <v>212</v>
       </c>
@@ -3773,10 +3774,10 @@
         <f t="array" ref="H24">CAL_Vsense[Iadc (mA)]</f>
         <v>8.0173431270355664</v>
       </c>
-      <c r="M24" s="85" t="s">
+      <c r="M24" s="82" t="s">
         <v>149</v>
       </c>
-      <c r="N24" s="86"/>
+      <c r="N24" s="83"/>
       <c r="O24" s="71"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
@@ -3905,15 +3906,26 @@
       </c>
       <c r="N31" s="6" cm="1">
         <f t="array" ref="N31">CAL_HB[Tau Qg,on (µs)]</f>
-        <v>3.7768298758040761</v>
+        <v>5.7596655606012161</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="M32" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="N32" s="6">
+        <f>N29/((N6+N5)/2+N21)</f>
+        <v>1.555737704918033</v>
+      </c>
       <c r="O32" s="71"/>
     </row>
     <row r="33" spans="13:16" x14ac:dyDescent="0.35">
-      <c r="M33" t="s">
-        <v>285</v>
+      <c r="M33" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="N33" s="6">
+        <f>N29/((N8+N7)/2+1/(1/N21+1/N20))</f>
+        <v>2.4957373623024344</v>
       </c>
     </row>
     <row r="34" spans="13:16" x14ac:dyDescent="0.35">
@@ -3933,7 +3945,7 @@
       </c>
       <c r="N35" s="6">
         <f xml:space="preserve"> N34   -    (N21+ 1/(1/N20+1/N21))/2   /   ((N21+ 1/(1/N20+1/N21))/2  +   (N8+N7+N6+N5)/4)*N34</f>
-        <v>4.5149015358649791E-2</v>
+        <v>2.7014225019478033E-2</v>
       </c>
     </row>
     <row r="36" spans="13:16" x14ac:dyDescent="0.35">
@@ -3942,7 +3954,7 @@
       </c>
       <c r="N36" s="5">
         <f>(N34-N35)*(0.5+N21/(N20+N21)/2)</f>
-        <v>0.10693187848101265</v>
+        <v>0.10749518847483036</v>
       </c>
     </row>
     <row r="37" spans="13:16" x14ac:dyDescent="0.35">
@@ -3951,7 +3963,7 @@
       </c>
       <c r="N37" s="6">
         <f>(N34-N35)*(1-(0.5+N21/(N20+N21)/2))</f>
-        <v>3.5643959493670885E-2</v>
+        <v>5.3215439839024936E-2</v>
       </c>
     </row>
     <row r="38" spans="13:16" x14ac:dyDescent="0.35">
@@ -3965,25 +3977,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="M2:N2"/>
     <mergeCell ref="M24:N24"/>
     <mergeCell ref="M12:N12"/>
     <mergeCell ref="M18:N18"/>
@@ -3992,6 +3985,25 @@
     <mergeCell ref="M19:N19"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="G22:H22"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J19" r:id="rId1" xr:uid="{6EA051B8-41A2-4DC1-B63C-EE1F61D6E0BA}"/>
@@ -4240,18 +4252,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="84"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="93"/>
       <c r="M2" s="8" t="str">
         <f>INPUTS!A12</f>
         <v>Vph spike (V) @ disarm</v>
@@ -5200,11 +5212,11 @@
         <f t="shared" si="2"/>
         <v>6.5488500000000016</v>
       </c>
-      <c r="M19" s="79" t="s">
+      <c r="M19" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="N19" s="80"/>
-      <c r="O19" s="81"/>
+      <c r="N19" s="89"/>
+      <c r="O19" s="90"/>
       <c r="Q19" t="s">
         <v>20</v>
       </c>
@@ -6789,15 +6801,15 @@
       </c>
       <c r="AK2" s="50">
         <f>INPUTS!N34*INPUTS!N21/(INPUTS!N21+INPUTS!N5)</f>
-        <v>0.14079364</v>
+        <v>0.15695028721311477</v>
       </c>
       <c r="AL2" s="37">
         <f>INPUTS!N15*((INPUTS!N5+INPUTS!N6)/2+INPUTS!N21)/1000*INPUTS!N28</f>
-        <v>3.7768298758040761</v>
+        <v>5.7596655606012161</v>
       </c>
       <c r="AM2" s="37">
         <f>CAL_HB[[#This Row],[Cbootmin,safe (nF)]]*(1/(1/INPUTS!N21+1/INPUTS!N20) + (INPUTS!N8+INPUTS!N7)/2)/1000</f>
-        <v>0.1924771663647343</v>
+        <v>0.38020324072407774</v>
       </c>
     </row>
   </sheetData>
@@ -7637,11 +7649,11 @@
         <v>3.5</v>
       </c>
       <c r="K2">
-        <f>H2*F2</f>
+        <f t="shared" ref="K2:K7" si="0">H2*F2</f>
         <v>25.200000000000003</v>
       </c>
       <c r="L2">
-        <f>J2*G2</f>
+        <f t="shared" ref="L2:L7" si="1">J2*G2</f>
         <v>14</v>
       </c>
       <c r="M2">
@@ -7712,11 +7724,11 @@
         <v>3.5</v>
       </c>
       <c r="K3">
-        <f>H3*F3</f>
+        <f t="shared" si="0"/>
         <v>25.200000000000003</v>
       </c>
       <c r="L3">
-        <f>J3*G3</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="M3">
@@ -7787,11 +7799,11 @@
         <v>3.5</v>
       </c>
       <c r="K4">
-        <f>H4*F4</f>
+        <f t="shared" si="0"/>
         <v>25.200000000000003</v>
       </c>
       <c r="L4">
-        <f>J4*G4</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="M4">
@@ -7862,11 +7874,11 @@
         <v>3.5</v>
       </c>
       <c r="K5">
-        <f>H5*F5</f>
+        <f t="shared" si="0"/>
         <v>25.200000000000003</v>
       </c>
       <c r="L5">
-        <f>J5*G5</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="M5">
@@ -7937,11 +7949,11 @@
         <v>3.25</v>
       </c>
       <c r="K6">
-        <f>H6*F6</f>
+        <f t="shared" si="0"/>
         <v>25.200000000000003</v>
       </c>
       <c r="L6">
-        <f>J6*G6</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="M6">
@@ -8012,11 +8024,11 @@
         <v>3.5</v>
       </c>
       <c r="K7">
-        <f>H7*F7</f>
+        <f t="shared" si="0"/>
         <v>25.200000000000003</v>
       </c>
       <c r="L7">
-        <f>J7*G7</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="M7">
@@ -8040,7 +8052,7 @@
       <c r="S7">
         <v>25</v>
       </c>
-      <c r="T7" s="95">
+      <c r="T7">
         <f>100-DB_limits[[#This Row],[ToF Iph typ (%)]]-DB_limits[[#This Row],[ToF Iph spike (%)]]</f>
         <v>14</v>
       </c>
@@ -8050,7 +8062,7 @@
       <c r="V7">
         <v>1</v>
       </c>
-      <c r="W7" s="95">
+      <c r="W7">
         <f>DB_limits[[#This Row],[Iph typ (A)]]*DB_limits[[#This Row],[ToF Iph typ (%)]]%+DB_limits[[#This Row],[Iph max (A@Xs)]]*DB_limits[[#This Row],[ToF Iph max (%)]]%+DB_limits[[#This Row],[Iph spike (A@Xms)]]*DB_limits[[#This Row],[ToF Iph spike (%)]]%</f>
         <v>14.625</v>
       </c>

--- a/resources/Kururugi-ESC-calculs.xlsx
+++ b/resources/Kururugi-ESC-calculs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\binon\Desktop\Kururugi-ESC-Dev-Board\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81053D7-8006-41F6-B153-F401B34ECE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381F6C64-3C13-487D-86FE-7704AF7E3525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5775" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="783" activeTab="8" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
+    <workbookView xWindow="5775" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="783" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
   </bookViews>
   <sheets>
     <sheet name="HMI" sheetId="6" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="326">
   <si>
     <t>R1 (kOhm)</t>
   </si>
@@ -965,40 +965,12 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Rv1 (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ω)</t>
-    </r>
-  </si>
-  <si>
     <t>Rv2 &amp; Rtrace</t>
   </si>
   <si>
     <t>Prv1,rv2 (mW)</t>
   </si>
   <si>
-    <r>
-      <t>Rv1,th (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ω)</t>
-    </r>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -1033,9 +1005,6 @@
   </si>
   <si>
     <t>Cadc,ext</t>
-  </si>
-  <si>
-    <t>1.1kΩ, 2012m</t>
   </si>
   <si>
     <t>Vdivider,spike (V)</t>
@@ -1141,6 +1110,9 @@
     <t>Charge factor (ext)</t>
   </si>
   <si>
+    <t>1kΩ, 2012m</t>
+  </si>
+  <si>
     <t>Tfillsam just give a rought too conservative approx</t>
   </si>
   <si>
@@ -1234,6 +1206,40 @@
   <si>
     <t>Ptot,max (mW)</t>
   </si>
+  <si>
+    <t>Pboot (mW)</t>
+  </si>
+  <si>
+    <t>Prboot (mW)</t>
+  </si>
+  <si>
+    <r>
+      <t>Rv1,th (k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ω)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Rv1 (k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ω)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1245,7 +1251,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1308,6 +1314,14 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1848,7 +1862,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2106,6 +2120,21 @@
     <xf numFmtId="167" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2145,12 +2174,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2283,6 +2306,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2712,9 +2748,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>215911</xdr:colOff>
+      <xdr:colOff>219086</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>69315</xdr:rowOff>
+      <xdr:rowOff>66140</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2988,7 +3024,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>558801</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>95398</xdr:rowOff>
+      <xdr:rowOff>104923</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3035,7 +3071,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>92505</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>95249</xdr:rowOff>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3134,7 +3170,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>486343</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>101601</xdr:rowOff>
+      <xdr:rowOff>104776</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3173,64 +3209,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>114026</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Picture 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EFD232E-AE10-CFA8-D7FE-C87290F89A41}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:srcRect t="12298"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12185650" y="4584700"/>
-          <a:ext cx="2317750" cy="234676"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>158750</xdr:colOff>
+      <xdr:colOff>177800</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>56817</xdr:rowOff>
+      <xdr:rowOff>50467</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
+      <xdr:colOff>273050</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>161335</xdr:rowOff>
+      <xdr:rowOff>151810</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3246,15 +3234,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12249150" y="2507917"/>
-          <a:ext cx="1778000" cy="479168"/>
+          <a:off x="8512175" y="4736767"/>
+          <a:ext cx="1771650" cy="475993"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3293,7 +3281,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3324,7 +3312,7 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>444500</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>65201</xdr:rowOff>
+      <xdr:rowOff>55676</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3340,7 +3328,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3387,7 +3375,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3412,7 +3400,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>133351</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>71492</xdr:rowOff>
+      <xdr:rowOff>68317</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
@@ -3434,6 +3422,53 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8467726" y="3621142"/>
+          <a:ext cx="1892300" cy="415396"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>76198</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>75453</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>730250</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114715</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51E5D9B0-E0E7-CCCF-B1BB-E05297CE0E69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
@@ -3441,15 +3476,105 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8489951" y="2522592"/>
-          <a:ext cx="1898650" cy="412221"/>
+          <a:off x="10772773" y="1380378"/>
+          <a:ext cx="2428877" cy="229762"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>107949</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>73148</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>134392</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AA81600-FE23-4F27-A0CC-5E9F86FF4C33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10804524" y="3273548"/>
+          <a:ext cx="2416176" cy="251744"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>438151</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>114162</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>324664</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>101738</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5258B494-FA3B-6143-8BD9-E71623EEA89C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11134726" y="4638537"/>
+          <a:ext cx="1658163" cy="359051"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -3654,9 +3779,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>2197100</xdr:colOff>
+      <xdr:colOff>2200275</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>161941</xdr:rowOff>
+      <xdr:rowOff>158766</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3698,7 +3823,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>1987619</xdr:colOff>
+      <xdr:colOff>1990794</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>158765</xdr:rowOff>
     </xdr:to>
@@ -3742,7 +3867,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>524014</xdr:colOff>
+      <xdr:colOff>520839</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>95267</xdr:rowOff>
     </xdr:to>
@@ -3781,14 +3906,14 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>92075</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>53975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>768467</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>130196</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>92096</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3811,7 +3936,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11029950" y="3663950"/>
+          <a:off x="11029950" y="987425"/>
           <a:ext cx="2276592" cy="419121"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3823,16 +3948,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>28576</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>962026</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>134342</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>482601</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>93067</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3855,7 +3980,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10810876" y="2171700"/>
+          <a:off x="10839451" y="1000125"/>
           <a:ext cx="2686050" cy="401042"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3868,15 +3993,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>46790</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>65840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>466814</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>131024</xdr:rowOff>
+      <xdr:colOff>447764</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>162774</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3904,8 +4029,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11258550" y="789740"/>
-          <a:ext cx="1739989" cy="274734"/>
+          <a:off x="11239500" y="4961690"/>
+          <a:ext cx="1743164" cy="277909"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3923,9 +4048,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>602099</xdr:colOff>
+      <xdr:colOff>598924</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3969,7 +4094,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>568325</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>25728</xdr:rowOff>
+      <xdr:rowOff>16203</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4011,9 +4136,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>336493</xdr:colOff>
+      <xdr:colOff>333318</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>98424</xdr:rowOff>
+      <xdr:rowOff>85724</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4055,9 +4180,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>412606</xdr:colOff>
+      <xdr:colOff>409431</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>102679</xdr:rowOff>
+      <xdr:rowOff>115379</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4097,94 +4222,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>549941</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>93746</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 52">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39C9680C-C43B-C0FE-B199-28A02974077C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13836650" y="809625"/>
-          <a:ext cx="1715166" cy="217571"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>436780</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>92075</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>534203</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>57294</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 53">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2592E347-8C43-55C8-8897-A510C3522265}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11219080" y="5359400"/>
-          <a:ext cx="1850023" cy="336694"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
       <xdr:row>26</xdr:row>
@@ -4192,7 +4229,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>387813</xdr:colOff>
+      <xdr:colOff>390988</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>181166</xdr:rowOff>
     </xdr:to>
@@ -4210,7 +4247,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4219,6 +4256,99 @@
         <a:xfrm>
           <a:off x="5819775" y="4953438"/>
           <a:ext cx="1626063" cy="676028"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>173188</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>100392</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>770546</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>112331</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3027E104-8EDF-7CFE-8639-599EB32EE6B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11050738" y="2548317"/>
+          <a:ext cx="2349958" cy="383414"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>50782</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>467185</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>111193</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2FB7DC0-F979-958A-705C-4E0E5061A6F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11296650" y="3803632"/>
+          <a:ext cx="1705435" cy="250911"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4290,7 +4420,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>275589</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>130176</xdr:rowOff>
+      <xdr:rowOff>123826</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4337,7 +4467,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>425451</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>160079</xdr:rowOff>
+      <xdr:rowOff>172779</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4384,7 +4514,7 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>387350</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>124693</xdr:rowOff>
+      <xdr:rowOff>131043</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4429,14 +4559,14 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>63501</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>97530</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>94355</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4475,14 +4605,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>114301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>425450</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>58127</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4506,8 +4636,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7054850" y="4425951"/>
-          <a:ext cx="1930400" cy="318476"/>
+          <a:off x="6610350" y="4419601"/>
+          <a:ext cx="1933575" cy="315301"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4582,7 +4712,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>1063625</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>103704</xdr:rowOff>
+      <xdr:rowOff>106879</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4979,7 +5109,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>1285701</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>82363</xdr:rowOff>
+      <xdr:rowOff>88713</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5024,7 +5154,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1137873</xdr:colOff>
+      <xdr:colOff>1131523</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>94549</xdr:rowOff>
     </xdr:to>
@@ -6034,87 +6164,87 @@
   <sheetData>
     <row r="1" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B2" s="153" t="s">
+      <c r="B2" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="154"/>
-      <c r="E2" s="153" t="s">
+      <c r="C2" s="157"/>
+      <c r="E2" s="156" t="s">
         <v>145</v>
       </c>
-      <c r="F2" s="154"/>
-      <c r="H2" s="153" t="s">
+      <c r="F2" s="157"/>
+      <c r="H2" s="156" t="s">
         <v>102</v>
       </c>
-      <c r="I2" s="154"/>
-      <c r="K2" s="153" t="s">
+      <c r="I2" s="157"/>
+      <c r="K2" s="156" t="s">
         <v>226</v>
       </c>
-      <c r="L2" s="154"/>
-      <c r="N2" s="153" t="s">
-        <v>257</v>
-      </c>
-      <c r="O2" s="154"/>
-      <c r="Q2" s="146"/>
-      <c r="R2" s="146"/>
-      <c r="T2" s="150"/>
-      <c r="U2" s="150"/>
+      <c r="L2" s="157"/>
+      <c r="N2" s="156" t="s">
+        <v>256</v>
+      </c>
+      <c r="O2" s="157"/>
+      <c r="Q2" s="149"/>
+      <c r="R2" s="149"/>
+      <c r="T2" s="153"/>
+      <c r="U2" s="153"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B3" s="155" t="s">
+      <c r="B3" s="158" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="156"/>
-      <c r="D3" s="149"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="152"/>
       <c r="E3" s="101" t="s">
         <v>204</v>
       </c>
       <c r="F3" s="102"/>
-      <c r="H3" s="155" t="s">
+      <c r="H3" s="158" t="s">
         <v>202</v>
       </c>
-      <c r="I3" s="156"/>
-      <c r="K3" s="155" t="s">
+      <c r="I3" s="159"/>
+      <c r="K3" s="158" t="s">
         <v>131</v>
       </c>
-      <c r="L3" s="156"/>
-      <c r="N3" s="155" t="s">
+      <c r="L3" s="159"/>
+      <c r="N3" s="158" t="s">
         <v>131</v>
       </c>
-      <c r="O3" s="156"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
-      <c r="T3" s="148"/>
-      <c r="U3" s="148"/>
+      <c r="O3" s="159"/>
+      <c r="Q3" s="148"/>
+      <c r="R3" s="148"/>
+      <c r="T3" s="151"/>
+      <c r="U3" s="151"/>
     </row>
     <row r="4" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="157" t="s">
+      <c r="B4" s="160" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="158"/>
-      <c r="E4" s="155" t="s">
+      <c r="C4" s="161"/>
+      <c r="E4" s="158" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="156"/>
-      <c r="H4" s="157" t="s">
+      <c r="F4" s="159"/>
+      <c r="H4" s="160" t="s">
         <v>203</v>
       </c>
-      <c r="I4" s="158"/>
-      <c r="K4" s="162" t="s">
+      <c r="I4" s="161"/>
+      <c r="K4" s="165" t="s">
         <v>243</v>
       </c>
-      <c r="L4" s="163">
+      <c r="L4" s="166">
         <v>850</v>
       </c>
-      <c r="N4" s="161" t="s">
-        <v>267</v>
+      <c r="N4" s="164" t="s">
+        <v>265</v>
       </c>
       <c r="O4" s="61" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q4" s="151"/>
-      <c r="R4" s="151"/>
-      <c r="T4" s="152"/>
-      <c r="U4" s="152"/>
+        <v>297</v>
+      </c>
+      <c r="Q4" s="154"/>
+      <c r="R4" s="154"/>
+      <c r="T4" s="155"/>
+      <c r="U4" s="155"/>
     </row>
     <row r="5" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B5" s="70" t="str">
@@ -6125,11 +6255,11 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Frame size (")])</f>
         <v>6</v>
       </c>
-      <c r="E5" s="162" t="s">
+      <c r="E5" s="165" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="163">
-        <v>10</v>
+      <c r="F5" s="166">
+        <v>10.5</v>
       </c>
       <c r="H5" s="70" t="str">
         <f>DB_Mostfet[[#Headers],[Vds (V)]]</f>
@@ -6149,8 +6279,8 @@
         <f>_xlfn.XLOOKUP(O4, DB_R[Description], DB_R[Prated@70°C (W)])</f>
         <v>0.25</v>
       </c>
-      <c r="R5" s="144"/>
-      <c r="U5" s="144"/>
+      <c r="R5" s="147"/>
+      <c r="U5" s="147"/>
     </row>
     <row r="6" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="70" t="str">
@@ -6165,22 +6295,22 @@
         <f>DB_Mostfet[[#Headers],[Qg,typ @ 10V (nC)]]</f>
         <v>Qg,typ @ 10V (nC)</v>
       </c>
-      <c r="I6" s="164">
+      <c r="I6" s="167">
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Qg,typ @ 10V (nC)])</f>
         <v>41</v>
       </c>
-      <c r="K6" s="166" t="s">
+      <c r="K6" s="169" t="s">
         <v>140</v>
       </c>
-      <c r="L6" s="167"/>
-      <c r="N6" s="161" t="s">
-        <v>288</v>
+      <c r="L6" s="170"/>
+      <c r="N6" s="164" t="s">
+        <v>285</v>
       </c>
       <c r="O6" s="61" t="s">
-        <v>281</v>
-      </c>
-      <c r="R6" s="144"/>
-      <c r="U6" s="144"/>
+        <v>278</v>
+      </c>
+      <c r="R6" s="147"/>
+      <c r="U6" s="147"/>
     </row>
     <row r="7" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="70" t="str">
@@ -6191,10 +6321,10 @@
         <f>_xlfn.XLOOKUP(B4,DB_limits[Name],DB_limits[Fmax (kHz)])</f>
         <v>64</v>
       </c>
-      <c r="E7" s="153" t="s">
+      <c r="E7" s="156" t="s">
         <v>225</v>
       </c>
-      <c r="F7" s="154"/>
+      <c r="F7" s="157"/>
       <c r="H7" s="70" t="str">
         <f>DB_Mostfet[[#Headers],[Qg,typ,sync @ 10V (nC)]] &amp;  " (not used)"</f>
         <v>Qg,typ,sync @ 10V (nC) (not used)</v>
@@ -6203,20 +6333,20 @@
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Qg,typ,sync @ 10V (nC)])</f>
         <v>X</v>
       </c>
-      <c r="K7" s="159" t="s">
+      <c r="K7" s="162" t="s">
         <v>113</v>
       </c>
-      <c r="L7" s="160"/>
-      <c r="N7" s="165" t="str">
+      <c r="L7" s="163"/>
+      <c r="N7" s="168" t="str">
         <f>N5</f>
         <v>Prated@70°C (W)</v>
       </c>
-      <c r="O7" s="163">
+      <c r="O7" s="166">
         <f>_xlfn.XLOOKUP(O4, DB_R[Description], DB_R[Prated@70°C (W)])</f>
         <v>0.25</v>
       </c>
-      <c r="R7" s="144"/>
-      <c r="U7" s="144"/>
+      <c r="R7" s="147"/>
+      <c r="U7" s="147"/>
     </row>
     <row r="8" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="70" t="str">
@@ -6239,14 +6369,14 @@
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Rds,on@10V typ(mΩ)])</f>
         <v>1.8</v>
       </c>
-      <c r="K8" s="157" t="s">
+      <c r="K8" s="160" t="s">
         <v>132</v>
       </c>
-      <c r="L8" s="158"/>
+      <c r="L8" s="161"/>
       <c r="N8" s="104"/>
       <c r="O8" s="104"/>
-      <c r="R8" s="144"/>
-      <c r="U8" s="144"/>
+      <c r="R8" s="147"/>
+      <c r="U8" s="147"/>
     </row>
     <row r="9" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="70" t="str">
@@ -6261,7 +6391,7 @@
         <f>DB_Mostfet[[#Headers],[Rds,on@10V max (mΩ)]]</f>
         <v>Rds,on@10V max (mΩ)</v>
       </c>
-      <c r="I9" s="164">
+      <c r="I9" s="167">
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Rds,on@10V max (mΩ)])</f>
         <v>2.2000000000000002</v>
       </c>
@@ -6273,14 +6403,14 @@
         <f>_xlfn.XLOOKUP($K$8, DB_ADC[Name], DB_ADC[Vmax (V)])</f>
         <v>3.5999999999999996</v>
       </c>
-      <c r="N9" s="166" t="s">
+      <c r="N9" s="169" t="s">
         <v>254</v>
       </c>
-      <c r="O9" s="167"/>
-      <c r="Q9" s="145"/>
-      <c r="R9" s="145"/>
-      <c r="T9" s="145"/>
-      <c r="U9" s="145"/>
+      <c r="O9" s="170"/>
+      <c r="Q9" s="148"/>
+      <c r="R9" s="148"/>
+      <c r="T9" s="148"/>
+      <c r="U9" s="148"/>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B10" s="70" t="str">
@@ -6291,10 +6421,10 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Vbat spike (V) @ run])</f>
         <v>32</v>
       </c>
-      <c r="E10" s="166" t="s">
+      <c r="E10" s="169" t="s">
         <v>216</v>
       </c>
-      <c r="F10" s="167"/>
+      <c r="F10" s="170"/>
       <c r="H10" s="70" t="str">
         <f>DB_Mostfet[[#Headers],[Id @ Tc&gt;70°C (A)]]</f>
         <v>Id @ Tc&gt;70°C (A)</v>
@@ -6303,16 +6433,16 @@
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Id @ Tc&gt;70°C (A)])</f>
         <v>100</v>
       </c>
-      <c r="K10" s="159" t="s">
+      <c r="K10" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="L10" s="160"/>
-      <c r="N10" s="159" t="s">
+      <c r="L10" s="163"/>
+      <c r="N10" s="162" t="s">
         <v>113</v>
       </c>
-      <c r="O10" s="160"/>
-      <c r="R10" s="144"/>
-      <c r="U10" s="144"/>
+      <c r="O10" s="163"/>
+      <c r="R10" s="147"/>
+      <c r="U10" s="147"/>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B11" s="70" t="str">
@@ -6323,19 +6453,19 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Vbat spike (V) @ disarm])</f>
         <v>45</v>
       </c>
-      <c r="E11" s="159" t="s">
+      <c r="E11" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="F11" s="160"/>
+      <c r="F11" s="163"/>
       <c r="H11" s="70" t="str">
         <f>DB_Mostfet[[#Headers],[Id @ Ta&gt;70°C (A)]]</f>
         <v>Id @ Ta&gt;70°C (A)</v>
       </c>
-      <c r="I11" s="164" t="str">
+      <c r="I11" s="167" t="str">
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Id @ Ta&gt;70°C (A)])</f>
         <v>(est ~21A)</v>
       </c>
-      <c r="K11" s="161" t="s">
+      <c r="K11" s="164" t="s">
         <v>127</v>
       </c>
       <c r="L11" s="61">
@@ -6345,8 +6475,8 @@
         <v>132</v>
       </c>
       <c r="O11" s="102"/>
-      <c r="R11" s="144"/>
-      <c r="U11" s="144"/>
+      <c r="R11" s="147"/>
+      <c r="U11" s="147"/>
     </row>
     <row r="12" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="70" t="str">
@@ -6357,10 +6487,10 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Vph spike (V) @ run])</f>
         <v>35</v>
       </c>
-      <c r="E12" s="162" t="s">
+      <c r="E12" s="165" t="s">
         <v>228</v>
       </c>
-      <c r="F12" s="163">
+      <c r="F12" s="166">
         <v>10</v>
       </c>
       <c r="H12" s="70" t="str">
@@ -6371,8 +6501,8 @@
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Size (mm)])</f>
         <v>5x6</v>
       </c>
-      <c r="K12" s="161" t="s">
-        <v>286</v>
+      <c r="K12" s="164" t="s">
+        <v>283</v>
       </c>
       <c r="L12" s="61">
         <v>2.5</v>
@@ -6385,9 +6515,9 @@
         <f>_xlfn.XLOOKUP($N$11, DB_ADC[Name], DB_ADC[Csamp (pF)])</f>
         <v>5</v>
       </c>
-      <c r="R12" s="144"/>
-      <c r="T12" s="145"/>
-      <c r="U12" s="145"/>
+      <c r="R12" s="147"/>
+      <c r="T12" s="148"/>
+      <c r="U12" s="148"/>
     </row>
     <row r="13" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="70" t="str">
@@ -6398,7 +6528,7 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Vph spike (V) @ disarm])</f>
         <v>28</v>
       </c>
-      <c r="F13" s="143"/>
+      <c r="F13" s="146"/>
       <c r="H13" s="70" t="str">
         <f>DB_Mostfet[[#Headers],[JLCPBC stock]]</f>
         <v>JLCPBC stock</v>
@@ -6407,7 +6537,7 @@
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[JLCPBC stock])</f>
         <v>Yes</v>
       </c>
-      <c r="K13" s="161" t="s">
+      <c r="K13" s="164" t="s">
         <v>141</v>
       </c>
       <c r="L13" s="61">
@@ -6421,9 +6551,9 @@
         <f>_xlfn.XLOOKUP($N$11, DB_ADC[Name], DB_ADC[Cpad (pF)])</f>
         <v>5</v>
       </c>
-      <c r="Q13" s="145"/>
-      <c r="R13" s="145"/>
-      <c r="U13" s="141"/>
+      <c r="Q13" s="148"/>
+      <c r="R13" s="148"/>
+      <c r="U13" s="144"/>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B14" s="70" t="str">
@@ -6434,23 +6564,23 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Iph typ (A)])</f>
         <v>12.5</v>
       </c>
-      <c r="E14" s="166" t="s">
+      <c r="E14" s="169" t="s">
         <v>253</v>
       </c>
-      <c r="F14" s="167"/>
-      <c r="H14" s="155" t="s">
+      <c r="F14" s="170"/>
+      <c r="H14" s="158" t="s">
         <v>130</v>
       </c>
-      <c r="I14" s="156"/>
-      <c r="K14" s="159" t="s">
+      <c r="I14" s="159"/>
+      <c r="K14" s="162" t="s">
         <v>130</v>
       </c>
-      <c r="L14" s="160"/>
-      <c r="N14" s="159" t="s">
+      <c r="L14" s="163"/>
+      <c r="N14" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="O14" s="160"/>
-      <c r="R14" s="141"/>
+      <c r="O14" s="163"/>
+      <c r="R14" s="144"/>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B15" s="70" t="str">
@@ -6461,33 +6591,33 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Iph max (A@Xs)])</f>
         <v>20</v>
       </c>
-      <c r="E15" s="159" t="s">
+      <c r="E15" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="F15" s="160"/>
-      <c r="H15" s="178" t="str">
+      <c r="F15" s="163"/>
+      <c r="H15" s="181" t="str">
         <f>CAL_Fets!G28</f>
         <v>Ptot,typ (mW)</v>
       </c>
-      <c r="I15" s="179">
+      <c r="I15" s="182">
         <f>CAL_Fets!H28</f>
-        <v>1586.7291130000003</v>
+        <v>1667.2220807894741</v>
       </c>
       <c r="K15" s="73" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L15" s="78">
         <f>(L11+L12+0.5)*_xlfn.XLOOKUP(K8,DB_ADC[Name],DB_ADC[Tadc,clock (ns)])</f>
         <v>250.00000000000003</v>
       </c>
-      <c r="N15" s="161" t="s">
+      <c r="N15" s="164" t="s">
         <v>127</v>
       </c>
       <c r="O15" s="61">
         <v>8</v>
       </c>
-      <c r="T15" s="146"/>
-      <c r="U15" s="146"/>
+      <c r="T15" s="149"/>
+      <c r="U15" s="149"/>
     </row>
     <row r="16" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="70" t="str">
@@ -6498,38 +6628,38 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Iph spike (A@Xms)])</f>
         <v>50</v>
       </c>
-      <c r="E16" s="161" t="s">
+      <c r="E16" s="184" t="s">
         <v>214</v>
       </c>
-      <c r="F16" s="61">
-        <v>40</v>
-      </c>
-      <c r="H16" s="170" t="str">
+      <c r="F16" s="186">
+        <v>60</v>
+      </c>
+      <c r="H16" s="173" t="str">
         <f>CAL_Fets!G29</f>
         <v>Ptot,max (mW)</v>
       </c>
-      <c r="I16" s="171">
+      <c r="I16" s="174">
         <f>CAL_Fets!H29</f>
-        <v>3021.0160000000005</v>
-      </c>
-      <c r="K16" s="168" t="str">
+        <v>3145.7629473684219</v>
+      </c>
+      <c r="K16" s="171" t="str">
         <f>CAL_Rshunt!G22</f>
         <v>Vshunt,amp,spike (V)</v>
       </c>
-      <c r="L16" s="172">
+      <c r="L16" s="175">
         <f>CAL_Rshunt!H22</f>
         <v>2.72</v>
       </c>
-      <c r="N16" s="161" t="s">
-        <v>286</v>
+      <c r="N16" s="164" t="s">
+        <v>283</v>
       </c>
       <c r="O16" s="61">
         <v>2.5</v>
       </c>
-      <c r="Q16" s="147"/>
-      <c r="R16" s="147"/>
-      <c r="T16" s="145"/>
-      <c r="U16" s="145"/>
+      <c r="Q16" s="150"/>
+      <c r="R16" s="150"/>
+      <c r="T16" s="148"/>
+      <c r="U16" s="148"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B17" s="70" t="str">
@@ -6540,130 +6670,130 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Iph mean (A)])</f>
         <v>12.905000000000001</v>
       </c>
-      <c r="E17" s="161" t="s">
+      <c r="E17" s="184" t="s">
         <v>239</v>
       </c>
-      <c r="F17" s="78">
+      <c r="F17" s="185">
         <v>3</v>
       </c>
-      <c r="K17" s="168" t="str">
+      <c r="K17" s="171" t="str">
         <f>CAL_Rshunt!J6</f>
         <v>ΔIlsb (mA/bit)</v>
       </c>
-      <c r="L17" s="172">
+      <c r="L17" s="175">
         <f>CAL_Rshunt!K6</f>
         <v>14.813617754794226</v>
       </c>
-      <c r="N17" s="174" t="s">
-        <v>292</v>
-      </c>
-      <c r="O17" s="175">
+      <c r="N17" s="177" t="s">
+        <v>289</v>
+      </c>
+      <c r="O17" s="178">
         <v>5</v>
       </c>
-      <c r="Q17" s="145"/>
-      <c r="R17" s="145"/>
-      <c r="U17" s="144"/>
+      <c r="Q17" s="148"/>
+      <c r="R17" s="148"/>
+      <c r="U17" s="147"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B18" s="159" t="s">
+      <c r="B18" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="160"/>
-      <c r="E18" s="161" t="s">
+      <c r="C18" s="163"/>
+      <c r="E18" s="164" t="s">
         <v>146</v>
       </c>
       <c r="F18" s="61">
-        <v>5.0999999999999996</v>
+        <v>3.3</v>
       </c>
       <c r="K18" s="73" t="str">
-        <f>CAL_Rshunt!J15</f>
+        <f>CAL_Rshunt!J14</f>
         <v>Pshunt,mean (mW)</v>
       </c>
       <c r="L18" s="78">
-        <f>CAL_Rshunt!K15</f>
+        <f>CAL_Rshunt!K14</f>
         <v>84.934902750000006</v>
       </c>
-      <c r="N18" s="159" t="s">
+      <c r="N18" s="162" t="s">
         <v>130</v>
       </c>
-      <c r="O18" s="160"/>
-      <c r="R18" s="143"/>
-      <c r="U18" s="144"/>
+      <c r="O18" s="163"/>
+      <c r="R18" s="146"/>
+      <c r="U18" s="147"/>
     </row>
     <row r="19" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="161" t="s">
+      <c r="B19" s="164" t="s">
         <v>139</v>
       </c>
       <c r="C19" s="61">
         <v>480</v>
       </c>
-      <c r="E19" s="159" t="s">
+      <c r="E19" s="162" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="160"/>
-      <c r="K19" s="170" t="str">
-        <f>CAL_Rshunt!J23</f>
+      <c r="F19" s="163"/>
+      <c r="K19" s="173" t="str">
+        <f>CAL_Rshunt!J22</f>
         <v>Pshunt,max (mW@Xs)</v>
       </c>
-      <c r="L19" s="173">
-        <f>CAL_Rshunt!K23</f>
+      <c r="L19" s="176">
+        <f>CAL_Rshunt!K22</f>
         <v>204</v>
       </c>
       <c r="N19" s="73" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="O19" s="78">
         <f>(O15+O16+0.5)*_xlfn.XLOOKUP(N11,DB_ADC[Name],DB_ADC[Tadc,clock (ns)])</f>
         <v>183.33333333333334</v>
       </c>
-      <c r="R19" s="142"/>
-      <c r="U19" s="144"/>
+      <c r="R19" s="145"/>
+      <c r="U19" s="147"/>
     </row>
     <row r="20" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="162" t="s">
+      <c r="B20" s="165" t="s">
         <v>224</v>
       </c>
-      <c r="C20" s="163">
+      <c r="C20" s="166">
         <v>300</v>
       </c>
-      <c r="E20" s="168" t="str">
+      <c r="E20" s="171" t="str">
         <f>CAL_Cboot!G12</f>
         <v>Vboot,min (V)</v>
       </c>
-      <c r="F20" s="169">
+      <c r="F20" s="172">
         <f>CAL_Cboot!H12</f>
         <v>6.74</v>
       </c>
       <c r="N20" s="73" t="str">
         <f>'CAL_Rv1-2'!G5</f>
-        <v>Rv1,th (Ω)</v>
-      </c>
-      <c r="O20" s="85">
+        <v>Rv1,th (kΩ)</v>
+      </c>
+      <c r="O20" s="74">
         <f>'CAL_Rv1-2'!H5</f>
-        <v>10566.666666666668</v>
-      </c>
-      <c r="R20" s="142"/>
-      <c r="U20" s="144"/>
+        <v>9.6060606060606073</v>
+      </c>
+      <c r="R20" s="145"/>
+      <c r="U20" s="147"/>
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E21" s="168" t="str">
+      <c r="E21" s="171" t="str">
         <f>CAL_Cboot!G18</f>
         <v>Vboot,max (V)</v>
       </c>
-      <c r="F21" s="169">
+      <c r="F21" s="172">
         <f>CAL_Cboot!H18</f>
-        <v>9.76</v>
+        <v>10.26</v>
       </c>
       <c r="N21" s="73" t="str">
         <f>'CAL_Rv1-2'!G6</f>
-        <v>Rv1 (Ω)</v>
-      </c>
-      <c r="O21" s="85">
+        <v>Rv1 (kΩ)</v>
+      </c>
+      <c r="O21" s="74">
         <f>'CAL_Rv1-2'!H6</f>
-        <v>11000</v>
-      </c>
-      <c r="R21" s="142"/>
-      <c r="U21" s="144"/>
+        <v>10</v>
+      </c>
+      <c r="R21" s="145"/>
+      <c r="U21" s="147"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.35">
       <c r="E22" s="73" t="str">
@@ -6672,7 +6802,7 @@
       </c>
       <c r="F22" s="85">
         <f>CAL_Cboot!N4</f>
-        <v>127.66967024539878</v>
+        <v>167.44099069148933</v>
       </c>
       <c r="N22" s="73" t="str">
         <f>'CAL_Rv1-2'!G24</f>
@@ -6680,10 +6810,10 @@
       </c>
       <c r="O22" s="74">
         <f>'CAL_Rv1-2'!H24</f>
-        <v>2.290909090909091</v>
-      </c>
-      <c r="R22" s="143"/>
-      <c r="U22" s="144"/>
+        <v>24.950495049504955</v>
+      </c>
+      <c r="R22" s="146"/>
+      <c r="U22" s="147"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.35">
       <c r="E23" s="73" t="str">
@@ -6692,7 +6822,7 @@
       </c>
       <c r="F23" s="85">
         <f>CAL_Cboot!N5</f>
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="N23" s="73" t="str">
         <f>'CAL_Rv1-2'!J5</f>
@@ -6700,144 +6830,144 @@
       </c>
       <c r="O23" s="74">
         <f>'CAL_Rv1-2'!K5</f>
-        <v>2.0826446280991737</v>
-      </c>
-      <c r="R23" s="142"/>
-      <c r="T23" s="148"/>
-      <c r="U23" s="148"/>
+        <v>24.950495049504951</v>
+      </c>
+      <c r="R23" s="145"/>
+      <c r="T23" s="151"/>
+      <c r="U23" s="151"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.35">
       <c r="E24" s="73" t="str">
+        <f>CAL_Cboot!P24</f>
+        <v>Prboot (mW)</v>
+      </c>
+      <c r="F24" s="85">
+        <f>CAL_Cboot!Q24</f>
+        <v>23.654290993548383</v>
+      </c>
+      <c r="N24" s="171" t="str">
+        <f>'CAL_Rv1-2'!J25</f>
+        <v>ΔVlsb,fullscale (mV/bit)</v>
+      </c>
+      <c r="O24" s="172">
+        <f>'CAL_Rv1-2'!K25</f>
+        <v>13.070588235294117</v>
+      </c>
+      <c r="Q24" s="152"/>
+      <c r="U24" s="146"/>
+    </row>
+    <row r="25" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E25" s="73" t="str">
         <f>CAL_Cboot!M13</f>
         <v>t_recharge (µs)</v>
       </c>
-      <c r="F24" s="78">
+      <c r="F25" s="78">
         <f>CAL_Cboot!N13</f>
         <v>1.2624999999999995</v>
       </c>
-      <c r="N24" s="168" t="str">
-        <f>'CAL_Rv1-2'!J25</f>
-        <v>ΔVlsb,fullscale (mV/bit)</v>
-      </c>
-      <c r="O24" s="169">
-        <f>'CAL_Rv1-2'!K25</f>
-        <v>142.35294117647058</v>
-      </c>
-      <c r="Q24" s="149"/>
-      <c r="U24" s="143"/>
-    </row>
-    <row r="25" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E25" s="170" t="str">
-        <f>CAL_Cboot!P7</f>
-        <v>Vboot,max@Dmax (V)</v>
-      </c>
-      <c r="F25" s="171">
-        <f>CAL_Cboot!Q7</f>
-        <v>9.3680193623712888</v>
-      </c>
-      <c r="N25" s="170" t="str">
+      <c r="N25" s="173" t="str">
         <f>'CAL_Rv1-2'!G14</f>
         <v>Prv1,rv2 (mW)</v>
       </c>
-      <c r="O25" s="176">
+      <c r="O25" s="179">
         <f>'CAL_Rv1-2'!H14</f>
-        <v>101.2396694214876</v>
-      </c>
-      <c r="U25" s="143"/>
+        <v>1212.8712871287128</v>
+      </c>
+      <c r="U25" s="146"/>
     </row>
     <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="U26" s="143"/>
-    </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E27" s="166" t="s">
+      <c r="E26" s="173" t="str">
+        <f>CAL_Cboot!P8</f>
+        <v>Vboot,max@Dmax (V)</v>
+      </c>
+      <c r="F26" s="174">
+        <f>CAL_Cboot!Q8</f>
+        <v>10.255157760457088</v>
+      </c>
+      <c r="U26" s="146"/>
+    </row>
+    <row r="27" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N27" s="169" t="s">
+        <v>269</v>
+      </c>
+      <c r="O27" s="170"/>
+      <c r="U27" s="146"/>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="E28" s="169" t="s">
         <v>230</v>
       </c>
-      <c r="F27" s="167"/>
-      <c r="N27" s="166" t="s">
-        <v>271</v>
-      </c>
-      <c r="O27" s="167"/>
-      <c r="U27" s="143"/>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E28" s="159" t="s">
+      <c r="F28" s="170"/>
+      <c r="N28" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="F28" s="160"/>
-      <c r="N28" s="159" t="s">
+      <c r="O28" s="163"/>
+      <c r="U28" s="144"/>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="E29" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="O28" s="160"/>
-      <c r="U28" s="141"/>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E29" s="161" t="s">
-        <v>142</v>
-      </c>
-      <c r="F29" s="61">
-        <v>3.3</v>
-      </c>
-      <c r="N29" s="161" t="s">
-        <v>270</v>
-      </c>
-      <c r="O29" s="61">
+      <c r="F29" s="163"/>
+      <c r="N29" s="164" t="s">
+        <v>268</v>
+      </c>
+      <c r="O29" s="187">
         <v>100</v>
       </c>
-      <c r="U29" s="142"/>
+      <c r="U29" s="145"/>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E30" s="161" t="s">
+      <c r="E30" s="164" t="s">
         <v>149</v>
       </c>
       <c r="F30" s="61">
         <v>3.3</v>
       </c>
-      <c r="N30" s="161" t="s">
+      <c r="N30" s="184" t="s">
         <v>214</v>
       </c>
-      <c r="O30" s="61">
+      <c r="O30" s="186">
         <v>40</v>
       </c>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E31" s="161" t="s">
+      <c r="E31" s="164" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" s="61">
+        <v>10</v>
+      </c>
+      <c r="N31" s="184" t="s">
+        <v>295</v>
+      </c>
+      <c r="O31" s="186">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="E32" s="184" t="s">
         <v>240</v>
       </c>
-      <c r="F31" s="78">
-        <v>3</v>
-      </c>
-      <c r="N31" s="161" t="s">
-        <v>298</v>
-      </c>
-      <c r="O31" s="61">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E32" s="159" t="s">
+      <c r="F32" s="185">
+        <v>1.5</v>
+      </c>
+      <c r="N32" s="184" t="s">
+        <v>296</v>
+      </c>
+      <c r="O32" s="186">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="5:15" x14ac:dyDescent="0.35">
+      <c r="E33" s="162" t="s">
         <v>130</v>
       </c>
-      <c r="F32" s="160"/>
-      <c r="N32" s="161" t="s">
-        <v>299</v>
-      </c>
-      <c r="O32" s="61">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="5:15" x14ac:dyDescent="0.35">
-      <c r="E33" s="73" t="str">
-        <f>CAL_Rg!J4</f>
-        <v>Req,off (Ω)</v>
-      </c>
-      <c r="F33" s="78">
-        <f>CAL_Rg!K4</f>
-        <v>3.6749999999999998</v>
-      </c>
-      <c r="N33" s="159" t="s">
+      <c r="F33" s="163"/>
+      <c r="N33" s="162" t="s">
         <v>130</v>
       </c>
-      <c r="O33" s="160"/>
+      <c r="O33" s="163"/>
     </row>
     <row r="34" spans="5:15" x14ac:dyDescent="0.35">
       <c r="E34" s="73" t="str">
@@ -6846,7 +6976,7 @@
       </c>
       <c r="F34" s="78">
         <f>CAL_Rg!K5</f>
-        <v>1.6542372881355931</v>
+        <v>1.7389830508474575</v>
       </c>
       <c r="N34" s="73" t="str">
         <f>'CAL_Rv1-2'!M22</f>
@@ -6864,93 +6994,96 @@
       </c>
       <c r="F35" s="78">
         <f>CAL_Rg!K6</f>
-        <v>2.6557823129251701</v>
-      </c>
-      <c r="N35" s="168" t="str">
+        <v>2.2768614691527969</v>
+      </c>
+      <c r="N35" s="171" t="str">
         <f>'CAL_Rv1-2'!M30</f>
         <v>Tfill,adc,ext (ns)</v>
       </c>
-      <c r="O35" s="177">
+      <c r="O35" s="180">
         <f>'CAL_Rv1-2'!N30</f>
-        <v>309.90000000000003</v>
+        <v>12.870297029702972</v>
       </c>
     </row>
     <row r="36" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E36" s="73" t="str">
+      <c r="E36" s="171" t="str">
         <f>CAL_Rg!J25</f>
         <v>t_rise (ns)</v>
       </c>
-      <c r="F36" s="78">
+      <c r="F36" s="175">
         <f>CAL_Rg!K25</f>
         <v>9.8825000000000003</v>
       </c>
-      <c r="N36" s="170" t="str">
+      <c r="N36" s="173" t="str">
         <f>'CAL_Rv1-2'!P13</f>
         <v>Tfill,samp (ns)</v>
       </c>
-      <c r="O36" s="176">
+      <c r="O36" s="179">
         <f>'CAL_Rv1-2'!Q13</f>
-        <v>185.94</v>
+        <v>7.7221782178217833</v>
       </c>
     </row>
     <row r="37" spans="5:15" x14ac:dyDescent="0.35">
-      <c r="E37" s="73" t="str">
+      <c r="E37" s="171" t="str">
         <f>CAL_Rg!J26</f>
         <v>t_fall (ns)</v>
       </c>
-      <c r="F37" s="78">
+      <c r="F37" s="175">
         <f>CAL_Rg!K26</f>
-        <v>6.1556249999999997</v>
+        <v>7.5478900375939855</v>
       </c>
       <c r="N37" s="67" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="5:15" x14ac:dyDescent="0.35">
-      <c r="E38" s="168" t="str">
+      <c r="E38" s="181" t="str">
         <f>CAL_Rg!M11</f>
         <v>Pg,loss (mW)</v>
       </c>
-      <c r="F38" s="172">
+      <c r="F38" s="183">
         <f>CAL_Rg!N11</f>
-        <v>76.830719999999985</v>
+        <v>40.383359999999996</v>
       </c>
       <c r="N38" s="67" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="5:15" x14ac:dyDescent="0.35">
-      <c r="E39" s="73" t="str">
-        <f>CAL_Rg!P28</f>
+      <c r="E39" s="171" t="str">
+        <f>CAL_Rg!P13</f>
+        <v>Prg,on+off (mW)</v>
+      </c>
+      <c r="F39" s="175">
+        <f>CAL_Rg!Q13</f>
+        <v>27.360304480749178</v>
+      </c>
+    </row>
+    <row r="40" spans="5:15" x14ac:dyDescent="0.35">
+      <c r="E40" s="171" t="str">
+        <f>CAL_Rg!P20</f>
         <v>Prg,off (mW)</v>
       </c>
-      <c r="F39" s="78">
-        <f>CAL_Rg!Q28</f>
-        <v>0.59071565223789047</v>
-      </c>
-    </row>
-    <row r="40" spans="5:15" x14ac:dyDescent="0.35">
-      <c r="E40" s="73" t="str">
-        <f>CAL_Rg!S4</f>
-        <v>Prg,on+off (mW)</v>
-      </c>
-      <c r="F40" s="78">
-        <f>CAL_Rg!T4</f>
-        <v>58.480849571551182</v>
+      <c r="F40" s="175">
+        <f>CAL_Rg!Q20</f>
+        <v>3.8750645831104009</v>
       </c>
     </row>
     <row r="41" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E41" s="87" t="str">
-        <f>CAL_Rg!P4</f>
+        <f>CAL_Rg!P26</f>
         <v>Prgdint,mean (mW)</v>
       </c>
       <c r="F41" s="89">
-        <f>CAL_Rg!Q4</f>
-        <v>17.759154776210913</v>
+        <f>CAL_Rg!Q26</f>
+        <v>9.1479909361404168</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E33:F33"/>
     <mergeCell ref="N18:O18"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K10:L10"/>
@@ -6985,9 +7118,6 @@
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="N14:O14"/>
     <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E27:F27"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="E14:F14"/>
@@ -7190,7 +7320,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B1" t="s">
         <v>211</v>
@@ -7199,19 +7329,19 @@
         <v>227</v>
       </c>
       <c r="D1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F1" t="s">
         <v>261</v>
-      </c>
-      <c r="E1" t="s">
-        <v>262</v>
-      </c>
-      <c r="F1" t="s">
-        <v>263</v>
       </c>
       <c r="G1" t="s">
         <v>103</v>
       </c>
       <c r="H1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -7230,13 +7360,13 @@
         <v>0.25</v>
       </c>
       <c r="E2" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F2" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -7255,13 +7385,13 @@
         <v>0.25</v>
       </c>
       <c r="E3" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F3" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -7280,13 +7410,13 @@
         <v>0.25</v>
       </c>
       <c r="E4" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F4" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -7305,13 +7435,13 @@
         <v>0.25</v>
       </c>
       <c r="E5" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F5" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -7330,13 +7460,13 @@
         <v>0.25</v>
       </c>
       <c r="E6" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F6" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -7355,13 +7485,13 @@
         <v>0.25</v>
       </c>
       <c r="E7" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F7" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -7380,13 +7510,13 @@
         <v>0.25</v>
       </c>
       <c r="E8" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F8" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -7405,13 +7535,13 @@
         <v>0.25</v>
       </c>
       <c r="E9" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F9" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -7430,13 +7560,13 @@
         <v>0.25</v>
       </c>
       <c r="E10" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F10" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -7455,13 +7585,13 @@
         <v>0.25</v>
       </c>
       <c r="E11" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F11" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -7480,13 +7610,13 @@
         <v>0.25</v>
       </c>
       <c r="E12" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F12" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -7505,13 +7635,13 @@
         <v>0.25</v>
       </c>
       <c r="E13" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F13" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -7530,13 +7660,13 @@
         <v>0.25</v>
       </c>
       <c r="E14" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F14" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -7555,24 +7685,24 @@
         <v>0.25</v>
       </c>
       <c r="E15" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F15" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H15" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="140" t="str">
+      <c r="A16" s="143" t="str">
         <f>IF(B16&gt;=1000,C16&amp; "kΩ, ",B16&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>51Ω, 2012m</v>
       </c>
       <c r="B16">
         <v>51</v>
       </c>
-      <c r="C16" s="140">
+      <c r="C16" s="143">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>5.0999999999999997E-2</v>
       </c>
@@ -7580,24 +7710,24 @@
         <v>0.25</v>
       </c>
       <c r="E16" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F16" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H16" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="140" t="str">
+      <c r="A17" s="143" t="str">
         <f>IF(B17&gt;=1000,C17&amp; "kΩ, ",B17&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>56Ω, 2012m</v>
       </c>
       <c r="B17">
         <v>56</v>
       </c>
-      <c r="C17" s="140">
+      <c r="C17" s="143">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>5.6000000000000001E-2</v>
       </c>
@@ -7605,24 +7735,24 @@
         <v>0.25</v>
       </c>
       <c r="E17" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F17" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H17" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="140" t="str">
+      <c r="A18" s="143" t="str">
         <f>IF(B18&gt;=1000,C18&amp; "kΩ, ",B18&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>62Ω, 2012m</v>
       </c>
       <c r="B18">
         <v>62</v>
       </c>
-      <c r="C18" s="140">
+      <c r="C18" s="143">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>6.2E-2</v>
       </c>
@@ -7630,24 +7760,24 @@
         <v>0.25</v>
       </c>
       <c r="E18" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F18" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H18" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="140" t="str">
+      <c r="A19" s="143" t="str">
         <f>IF(B19&gt;=1000,C19&amp; "kΩ, ",B19&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>68Ω, 2012m</v>
       </c>
       <c r="B19">
         <v>68</v>
       </c>
-      <c r="C19" s="140">
+      <c r="C19" s="143">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>6.8000000000000005E-2</v>
       </c>
@@ -7655,24 +7785,24 @@
         <v>0.25</v>
       </c>
       <c r="E19" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F19" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H19" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="140" t="str">
+      <c r="A20" s="143" t="str">
         <f>IF(B20&gt;=1000,C20&amp; "kΩ, ",B20&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>75Ω, 2012m</v>
       </c>
       <c r="B20">
         <v>75</v>
       </c>
-      <c r="C20" s="140">
+      <c r="C20" s="143">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>7.4999999999999997E-2</v>
       </c>
@@ -7680,24 +7810,24 @@
         <v>0.25</v>
       </c>
       <c r="E20" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F20" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="140" t="str">
+      <c r="A21" s="143" t="str">
         <f>IF(B21&gt;=1000,C21&amp; "kΩ, ",B21&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>82Ω, 2012m</v>
       </c>
       <c r="B21">
         <v>82</v>
       </c>
-      <c r="C21" s="140">
+      <c r="C21" s="143">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>8.2000000000000003E-2</v>
       </c>
@@ -7705,24 +7835,24 @@
         <v>0.25</v>
       </c>
       <c r="E21" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F21" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H21" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="140" t="str">
+      <c r="A22" s="143" t="str">
         <f>IF(B22&gt;=1000,C22&amp; "kΩ, ",B22&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>91Ω, 2012m</v>
       </c>
       <c r="B22">
         <v>91</v>
       </c>
-      <c r="C22" s="140">
+      <c r="C22" s="143">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>9.0999999999999998E-2</v>
       </c>
@@ -7730,13 +7860,13 @@
         <v>0.25</v>
       </c>
       <c r="E22" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F22" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H22" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -7755,13 +7885,13 @@
         <v>0.25</v>
       </c>
       <c r="E23" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F23" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H23" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -7780,13 +7910,13 @@
         <v>0.25</v>
       </c>
       <c r="E24" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F24" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H24" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -7805,13 +7935,13 @@
         <v>0.25</v>
       </c>
       <c r="E25" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F25" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H25" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -7830,13 +7960,13 @@
         <v>0.25</v>
       </c>
       <c r="E26" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F26" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H26" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -7855,13 +7985,13 @@
         <v>0.25</v>
       </c>
       <c r="E27" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F27" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H27" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -7880,13 +8010,13 @@
         <v>0.25</v>
       </c>
       <c r="E28" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F28" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H28" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -7905,13 +8035,13 @@
         <v>0.25</v>
       </c>
       <c r="E29" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F29" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H29" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -7930,13 +8060,13 @@
         <v>0.25</v>
       </c>
       <c r="E30" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F30" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H30" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -7955,13 +8085,13 @@
         <v>0.25</v>
       </c>
       <c r="E31" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F31" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H31" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -7980,13 +8110,13 @@
         <v>0.25</v>
       </c>
       <c r="E32" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F32" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.35">
@@ -8005,13 +8135,13 @@
         <v>0.25</v>
       </c>
       <c r="E33" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F33" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H33" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.35">
@@ -8030,13 +8160,13 @@
         <v>0.25</v>
       </c>
       <c r="E34" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F34" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H34" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.35">
@@ -8055,13 +8185,13 @@
         <v>0.25</v>
       </c>
       <c r="E35" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F35" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H35" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.35">
@@ -8080,13 +8210,13 @@
         <v>0.25</v>
       </c>
       <c r="E36" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F36" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H36" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.35">
@@ -8105,13 +8235,13 @@
         <v>0.25</v>
       </c>
       <c r="E37" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F37" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H37" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.35">
@@ -8130,13 +8260,13 @@
         <v>0.25</v>
       </c>
       <c r="E38" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F38" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H38" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.35">
@@ -8155,13 +8285,13 @@
         <v>0.25</v>
       </c>
       <c r="E39" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F39" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H39" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.35">
@@ -8180,13 +8310,13 @@
         <v>0.25</v>
       </c>
       <c r="E40" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F40" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H40" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.35">
@@ -8205,13 +8335,13 @@
         <v>0.25</v>
       </c>
       <c r="E41" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F41" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H41" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.35">
@@ -8230,13 +8360,13 @@
         <v>0.25</v>
       </c>
       <c r="E42" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F42" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H42" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R42" s="60"/>
       <c r="S42" s="60"/>
@@ -8257,13 +8387,13 @@
         <v>0.25</v>
       </c>
       <c r="E43" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F43" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H43" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R43" s="60"/>
       <c r="S43" s="60"/>
@@ -8284,13 +8414,13 @@
         <v>0.25</v>
       </c>
       <c r="E44" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F44" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H44" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R44" s="60"/>
       <c r="S44" s="60"/>
@@ -8311,13 +8441,13 @@
         <v>0.25</v>
       </c>
       <c r="E45" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F45" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H45" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R45" s="60"/>
       <c r="S45" s="60"/>
@@ -8338,13 +8468,13 @@
         <v>0.25</v>
       </c>
       <c r="E46" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F46" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H46" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R46" s="60"/>
       <c r="S46" s="60"/>
@@ -8365,13 +8495,13 @@
         <v>0.25</v>
       </c>
       <c r="E47" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F47" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H47" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R47" s="60"/>
       <c r="S47" s="60"/>
@@ -8392,13 +8522,13 @@
         <v>0.25</v>
       </c>
       <c r="E48" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F48" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H48" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R48" s="60"/>
       <c r="S48" s="60"/>
@@ -8419,13 +8549,13 @@
         <v>0.25</v>
       </c>
       <c r="E49" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F49" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H49" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R49" s="60"/>
       <c r="S49" s="60"/>
@@ -8446,13 +8576,13 @@
         <v>0.25</v>
       </c>
       <c r="E50" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F50" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H50" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R50" s="60"/>
       <c r="S50" s="60"/>
@@ -8473,13 +8603,13 @@
         <v>0.25</v>
       </c>
       <c r="E51" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F51" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H51" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R51" s="60"/>
       <c r="S51" s="60"/>
@@ -8500,13 +8630,13 @@
         <v>0.25</v>
       </c>
       <c r="E52" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F52" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H52" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R52" s="60"/>
       <c r="S52" s="60"/>
@@ -8527,13 +8657,13 @@
         <v>0.25</v>
       </c>
       <c r="E53" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F53" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H53" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R53" s="60"/>
       <c r="S53" s="60"/>
@@ -8554,13 +8684,13 @@
         <v>0.25</v>
       </c>
       <c r="E54" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F54" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H54" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.35">
@@ -8579,13 +8709,13 @@
         <v>0.25</v>
       </c>
       <c r="E55" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F55" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H55" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.35">
@@ -8604,13 +8734,13 @@
         <v>0.25</v>
       </c>
       <c r="E56" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F56" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H56" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.35">
@@ -8629,13 +8759,13 @@
         <v>0.25</v>
       </c>
       <c r="E57" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F57" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H57" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.35">
@@ -8654,13 +8784,13 @@
         <v>0.25</v>
       </c>
       <c r="E58" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F58" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H58" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.35">
@@ -8679,13 +8809,13 @@
         <v>0.25</v>
       </c>
       <c r="E59" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F59" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H59" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.35">
@@ -8704,13 +8834,13 @@
         <v>0.25</v>
       </c>
       <c r="E60" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F60" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H60" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.35">
@@ -8729,13 +8859,13 @@
         <v>0.25</v>
       </c>
       <c r="E61" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F61" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H61" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.35">
@@ -8754,13 +8884,13 @@
         <v>0.25</v>
       </c>
       <c r="E62" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F62" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H62" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.35">
@@ -8779,13 +8909,13 @@
         <v>0.25</v>
       </c>
       <c r="E63" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F63" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H63" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.35">
@@ -8804,13 +8934,13 @@
         <v>0.25</v>
       </c>
       <c r="E64" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F64" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H64" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
@@ -8829,13 +8959,13 @@
         <v>0.25</v>
       </c>
       <c r="E65" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F65" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H65" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
@@ -8854,13 +8984,13 @@
         <v>0.25</v>
       </c>
       <c r="E66" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F66" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H66" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
@@ -8879,13 +9009,13 @@
         <v>0.25</v>
       </c>
       <c r="E67" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F67" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H67" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
@@ -8904,13 +9034,13 @@
         <v>0.25</v>
       </c>
       <c r="E68" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F68" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H68" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
@@ -8929,13 +9059,13 @@
         <v>0.25</v>
       </c>
       <c r="E69" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F69" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H69" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
@@ -8954,13 +9084,13 @@
         <v>0.25</v>
       </c>
       <c r="E70" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F70" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H70" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
@@ -8979,13 +9109,13 @@
         <v>0.25</v>
       </c>
       <c r="E71" s="62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F71" s="60" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H71" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
@@ -9499,13 +9629,13 @@
         <v>171</v>
       </c>
       <c r="Q1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="R1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="S1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="T1" t="s">
         <v>164</v>
@@ -9971,22 +10101,22 @@
         <v>103</v>
       </c>
       <c r="B1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C1" t="s">
         <v>247</v>
       </c>
       <c r="D1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H1" t="s">
         <v>133</v>
@@ -10220,7 +10350,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="3.1796875" style="67" customWidth="1"/>
-    <col min="3" max="3" width="20" style="67" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" style="67" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.1796875" style="67" customWidth="1"/>
     <col min="5" max="6" width="3.1796875" style="67" customWidth="1"/>
     <col min="7" max="7" width="23.453125" style="67" customWidth="1"/>
@@ -10252,7 +10382,7 @@
       </c>
       <c r="H2" s="84">
         <f>D13</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J2" s="68" t="str">
         <f>C29</f>
@@ -10276,7 +10406,7 @@
       </c>
       <c r="Q2" s="90">
         <f>H18</f>
-        <v>9.76</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
@@ -10285,7 +10415,7 @@
         <v>117</v>
       </c>
       <c r="D3" s="92"/>
-      <c r="E3" s="119"/>
+      <c r="E3" s="124"/>
       <c r="G3" s="70" t="str">
         <f>C11</f>
         <v>Vhbr (V)</v>
@@ -10308,7 +10438,7 @@
       </c>
       <c r="N3" s="61">
         <f>D18</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P3" s="70" t="str">
         <f>G12</f>
@@ -10328,7 +10458,7 @@
         <f>HMI!B4</f>
         <v>V1.0</v>
       </c>
-      <c r="E4" s="120"/>
+      <c r="E4" s="125"/>
       <c r="G4" s="70" t="str">
         <f>C12</f>
         <v>Vhbh,max (V)</v>
@@ -10346,11 +10476,11 @@
         <v>1.25</v>
       </c>
       <c r="M4" s="73" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N4" s="85">
         <f>K15/(1-N3%)*N2</f>
-        <v>127.66967024539878</v>
+        <v>167.44099069148933</v>
       </c>
       <c r="P4" s="70" t="str">
         <f>M13</f>
@@ -10371,7 +10501,7 @@
         <f>_xlfn.XLOOKUP(D4, DB_limits[Name], DB_limits[Dmax (%)])</f>
         <v>90</v>
       </c>
-      <c r="E5" s="120"/>
+      <c r="E5" s="125"/>
       <c r="G5" s="70" t="s">
         <v>208</v>
       </c>
@@ -10385,14 +10515,14 @@
       </c>
       <c r="K5" s="78">
         <f>H24</f>
-        <v>0.97599999999999998</v>
+        <v>1.026</v>
       </c>
       <c r="M5" s="87" t="s">
         <v>215</v>
       </c>
       <c r="N5" s="88">
         <f>_xlfn.MINIFS(J21:J32,J21:J32,"&gt;="&amp;N4)</f>
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="P5" s="70" t="str">
         <f>M20</f>
@@ -10400,7 +10530,7 @@
       </c>
       <c r="Q5" s="78">
         <f>N20</f>
-        <v>4.1221804511278188</v>
+        <v>2.8608870967741935</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10413,13 +10543,13 @@
         <f>_xlfn.XLOOKUP(D4,DB_limits[Name],DB_limits[Fmax (kHz)])</f>
         <v>64</v>
       </c>
-      <c r="E6" s="120"/>
+      <c r="E6" s="125"/>
       <c r="G6" s="87" t="s">
         <v>219</v>
       </c>
       <c r="H6" s="89">
         <f>H2-H3-H4-H5</f>
-        <v>3.26</v>
+        <v>3.76</v>
       </c>
       <c r="J6" s="70" t="str">
         <f>C5</f>
@@ -10436,11 +10566,11 @@
         <v>Cboot (nF)</v>
       </c>
       <c r="Q6" s="85">
-        <f>N5</f>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <f>N4</f>
+        <v>167.44099069148933</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B7" s="63"/>
       <c r="C7" s="36" t="str">
         <f>HMI!B20</f>
@@ -10450,7 +10580,7 @@
         <f>HMI!C20</f>
         <v>300</v>
       </c>
-      <c r="E7" s="120"/>
+      <c r="E7" s="125"/>
       <c r="G7" s="81"/>
       <c r="H7" s="82"/>
       <c r="J7" s="70" t="str">
@@ -10463,12 +10593,13 @@
       </c>
       <c r="M7" s="71"/>
       <c r="N7" s="72"/>
-      <c r="P7" s="87" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q7" s="118">
-        <f>Q2-(Q2-Q3)*EXP(-Q4/Q5/Q6*10^3)</f>
-        <v>9.3680193623712888</v>
+      <c r="P7" s="70" t="str">
+        <f>C18</f>
+        <v>Expected derating (%)</v>
+      </c>
+      <c r="Q7" s="85">
+        <f>D18</f>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10477,7 +10608,7 @@
         <v>205</v>
       </c>
       <c r="D8" s="92"/>
-      <c r="E8" s="119"/>
+      <c r="E8" s="124"/>
       <c r="G8" s="75"/>
       <c r="H8" s="76"/>
       <c r="J8" s="87" t="s">
@@ -10485,12 +10616,17 @@
       </c>
       <c r="K8" s="88">
         <f>K2+(K3+(K4+K5)*K6%)/K7*10^3</f>
-        <v>83.240624999999994</v>
+        <v>83.943749999999994</v>
       </c>
       <c r="M8" s="75"/>
       <c r="N8" s="76"/>
-      <c r="P8" s="81"/>
-      <c r="Q8" s="82"/>
+      <c r="P8" s="87" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q8" s="123">
+        <f>Q2-(Q2-Q3)*EXP(-Q4/Q5/Q6/(1-Q7%)*10^3)</f>
+        <v>10.255157760457088</v>
+      </c>
     </row>
     <row r="9" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="63"/>
@@ -10501,13 +10637,13 @@
         <f>HMI!E3</f>
         <v>Infineon 2EDL8024</v>
       </c>
-      <c r="E9" s="120"/>
+      <c r="E9" s="125"/>
       <c r="J9" s="81"/>
       <c r="K9" s="82"/>
-      <c r="P9" s="75"/>
-      <c r="Q9" s="109"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="P9" s="81"/>
+      <c r="Q9" s="82"/>
+    </row>
+    <row r="10" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="63"/>
       <c r="C10" s="36" t="s">
         <v>148</v>
@@ -10516,14 +10652,14 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Vfint,100mA (V)])</f>
         <v>2.15</v>
       </c>
-      <c r="E10" s="121"/>
+      <c r="E10" s="126"/>
       <c r="G10" s="68" t="str">
         <f>G2</f>
         <v>Vdd (V)</v>
       </c>
       <c r="H10" s="69">
         <f>H2</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J10" s="71"/>
       <c r="K10" s="72"/>
@@ -10535,6 +10671,8 @@
         <f>K6</f>
         <v>90</v>
       </c>
+      <c r="P10" s="75"/>
+      <c r="Q10" s="114"/>
     </row>
     <row r="11" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="63"/>
@@ -10545,14 +10683,14 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Vhbr (V)])</f>
         <v>6</v>
       </c>
-      <c r="E11" s="120"/>
+      <c r="E11" s="125"/>
       <c r="G11" s="70" t="str">
         <f>G6</f>
         <v>ΔVboot,max (V)</v>
       </c>
       <c r="H11" s="61">
         <f>H6</f>
-        <v>3.26</v>
+        <v>3.76</v>
       </c>
       <c r="J11" s="75"/>
       <c r="K11" s="76"/>
@@ -10575,7 +10713,7 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Vhbh,max (V)])</f>
         <v>0.5</v>
       </c>
-      <c r="E12" s="120"/>
+      <c r="E12" s="125"/>
       <c r="G12" s="87" t="s">
         <v>220</v>
       </c>
@@ -10590,6 +10728,14 @@
       <c r="N12" s="61">
         <f>D7</f>
         <v>300</v>
+      </c>
+      <c r="P12" s="68" t="str">
+        <f>M5</f>
+        <v>Cboot (nF)</v>
+      </c>
+      <c r="Q12" s="69">
+        <f>N5</f>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10600,9 +10746,9 @@
       </c>
       <c r="D13" s="2">
         <f>HMI!F5</f>
-        <v>10</v>
-      </c>
-      <c r="E13" s="120"/>
+        <v>10.5</v>
+      </c>
+      <c r="E13" s="125"/>
       <c r="G13" s="81"/>
       <c r="H13" s="82"/>
       <c r="J13" s="68" t="str">
@@ -10611,14 +10757,22 @@
       </c>
       <c r="K13" s="69">
         <f>K8</f>
-        <v>83.240624999999994</v>
+        <v>83.943749999999994</v>
       </c>
       <c r="M13" s="87" t="s">
         <v>217</v>
       </c>
-      <c r="N13" s="118">
+      <c r="N13" s="123">
         <f>((1-N10%)/N11)*1000-N12/1000</f>
         <v>1.2624999999999995</v>
+      </c>
+      <c r="P13" s="70" t="str">
+        <f>P7</f>
+        <v>Expected derating (%)</v>
+      </c>
+      <c r="Q13" s="85">
+        <f>Q7</f>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10631,7 +10785,7 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Ihb (mA)])</f>
         <v>0.7</v>
       </c>
-      <c r="E14" s="120"/>
+      <c r="E14" s="125"/>
       <c r="G14" s="75"/>
       <c r="H14" s="76"/>
       <c r="J14" s="70" t="str">
@@ -10640,10 +10794,18 @@
       </c>
       <c r="K14" s="61">
         <f>H6</f>
-        <v>3.26</v>
+        <v>3.76</v>
       </c>
       <c r="M14" s="81"/>
       <c r="N14" s="82"/>
+      <c r="P14" s="70" t="str">
+        <f>G18</f>
+        <v>Vboot,max (V)</v>
+      </c>
+      <c r="Q14" s="78">
+        <f>H18</f>
+        <v>10.26</v>
+      </c>
     </row>
     <row r="15" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B15" s="63"/>
@@ -10655,16 +10817,24 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Ihbs (mA)])</f>
         <v>1.25</v>
       </c>
-      <c r="E15" s="120"/>
+      <c r="E15" s="125"/>
       <c r="J15" s="87" t="s">
         <v>147</v>
       </c>
       <c r="K15" s="88">
         <f>K13/K14</f>
-        <v>25.533934049079754</v>
+        <v>22.325465425531913</v>
       </c>
       <c r="M15" s="71"/>
       <c r="N15" s="72"/>
+      <c r="P15" s="70" t="str">
+        <f>G6</f>
+        <v>ΔVboot,max (V)</v>
+      </c>
+      <c r="Q15" s="85">
+        <f>H6</f>
+        <v>3.76</v>
+      </c>
     </row>
     <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="63"/>
@@ -10676,27 +10846,35 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Rboot,int (Ω)])</f>
         <v>21.5</v>
       </c>
-      <c r="E16" s="120"/>
+      <c r="E16" s="125"/>
       <c r="G16" s="68" t="str">
         <f>G2</f>
         <v>Vdd (V)</v>
       </c>
       <c r="H16" s="69">
         <f>H2</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J16" s="81"/>
       <c r="K16" s="82"/>
       <c r="M16" s="75"/>
       <c r="N16" s="76"/>
-    </row>
-    <row r="17" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P16" s="70" t="str">
+        <f>C6</f>
+        <v>Fmax (kHz)</v>
+      </c>
+      <c r="Q16" s="85">
+        <f>D6</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="63"/>
       <c r="C17" s="91" t="s">
         <v>213</v>
       </c>
       <c r="D17" s="92"/>
-      <c r="E17" s="119"/>
+      <c r="E17" s="124"/>
       <c r="G17" s="70" t="str">
         <f>G5</f>
         <v>Vf (V)</v>
@@ -10707,8 +10885,15 @@
       </c>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
-    </row>
-    <row r="18" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P17" s="87" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q17" s="88">
+        <f>Q12*10^-6*(1-Q13%)*Q14*Q15*Q16*10^3</f>
+        <v>177.76558079999998</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="63"/>
       <c r="C18" s="36" t="str">
         <f>HMI!E16</f>
@@ -10716,15 +10901,15 @@
       </c>
       <c r="D18" s="2">
         <f>HMI!F16</f>
-        <v>40</v>
-      </c>
-      <c r="E18" s="120"/>
+        <v>60</v>
+      </c>
+      <c r="E18" s="125"/>
       <c r="G18" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="H18" s="118">
+      <c r="H18" s="123">
         <f>H16-H17</f>
-        <v>9.76</v>
+        <v>10.26</v>
       </c>
       <c r="J18" s="75"/>
       <c r="K18" s="76"/>
@@ -10734,10 +10919,12 @@
       </c>
       <c r="N18" s="69">
         <f>D26</f>
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>3.3</v>
+      </c>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="82"/>
+    </row>
+    <row r="19" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="63"/>
       <c r="C19" s="36" t="str">
         <f>HMI!E17</f>
@@ -10747,7 +10934,7 @@
         <f>HMI!F17</f>
         <v>3</v>
       </c>
-      <c r="E19" s="120"/>
+      <c r="E19" s="125"/>
       <c r="G19" s="81"/>
       <c r="H19" s="82"/>
       <c r="M19" s="70" t="str">
@@ -10758,29 +10945,31 @@
         <f>D16</f>
         <v>21.5</v>
       </c>
-    </row>
-    <row r="20" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P19" s="75"/>
+      <c r="Q19" s="114"/>
+    </row>
+    <row r="20" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="63"/>
       <c r="C20" s="91" t="s">
         <v>210</v>
       </c>
       <c r="D20" s="92"/>
-      <c r="E20" s="119"/>
+      <c r="E20" s="124"/>
       <c r="G20" s="75"/>
       <c r="H20" s="76"/>
-      <c r="J20" s="122" t="s">
+      <c r="J20" s="127" t="s">
         <v>229</v>
       </c>
-      <c r="K20" s="123"/>
+      <c r="K20" s="128"/>
       <c r="M20" s="87" t="s">
         <v>222</v>
       </c>
       <c r="N20" s="88">
         <f>N19*N18/(N18+N19)</f>
-        <v>4.1221804511278188</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>2.8608870967741935</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="63"/>
       <c r="C21" s="36" t="s">
         <v>206</v>
@@ -10789,15 +10978,23 @@
         <f>HMI!E8</f>
         <v>Rohm RB161QS-40</v>
       </c>
-      <c r="E21" s="120"/>
+      <c r="E21" s="125"/>
       <c r="J21" s="101">
         <v>47</v>
       </c>
       <c r="K21" s="102"/>
       <c r="M21" s="81"/>
       <c r="N21" s="82"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="P21" s="68" t="str">
+        <f>C26</f>
+        <v>Rboot,ext (Ω)</v>
+      </c>
+      <c r="Q21" s="84">
+        <f>D26</f>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B22" s="63"/>
       <c r="C22" s="36" t="str">
         <f>DB_diode[[#Headers],[Vf@100mA (V)]]</f>
@@ -10807,29 +11004,37 @@
         <f>_xlfn.XLOOKUP(D21, DB_diode[Ref], DB_diode[Vf@100mA (V)])</f>
         <v>0.24</v>
       </c>
-      <c r="E22" s="120"/>
+      <c r="E22" s="125"/>
       <c r="G22" s="68" t="str">
         <f>G18</f>
         <v>Vboot,max (V)</v>
       </c>
       <c r="H22" s="77">
         <f>H18</f>
-        <v>9.76</v>
+        <v>10.26</v>
       </c>
       <c r="J22" s="101">
         <v>56</v>
       </c>
       <c r="K22" s="102"/>
-      <c r="M22" s="112"/>
-      <c r="N22" s="113"/>
-    </row>
-    <row r="23" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M22" s="117"/>
+      <c r="N22" s="118"/>
+      <c r="P22" s="70" t="str">
+        <f>C16</f>
+        <v>Rboot,int (Ω)</v>
+      </c>
+      <c r="Q22" s="61">
+        <f>D16</f>
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="63"/>
       <c r="C23" s="91" t="s">
         <v>216</v>
       </c>
       <c r="D23" s="92"/>
-      <c r="E23" s="119"/>
+      <c r="E23" s="124"/>
       <c r="G23" s="70" t="str">
         <f>C24</f>
         <v>Rpd,gate (kΩ)</v>
@@ -10844,8 +11049,16 @@
       <c r="K23" s="102"/>
       <c r="M23" s="75"/>
       <c r="N23" s="76"/>
-    </row>
-    <row r="24" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P23" s="70" t="str">
+        <f>P17</f>
+        <v>Pboot (mW)</v>
+      </c>
+      <c r="Q23" s="85">
+        <f>Q17</f>
+        <v>177.76558079999998</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="63"/>
       <c r="C24" s="36" t="str">
         <f>HMI!E12</f>
@@ -10855,34 +11068,43 @@
         <f>HMI!F12</f>
         <v>10</v>
       </c>
-      <c r="E24" s="120"/>
+      <c r="E24" s="125"/>
       <c r="G24" s="87" t="s">
         <v>212</v>
       </c>
-      <c r="H24" s="118">
+      <c r="H24" s="123">
         <f>H22/H23</f>
-        <v>0.97599999999999998</v>
+        <v>1.026</v>
       </c>
       <c r="J24" s="101">
         <v>82</v>
       </c>
       <c r="K24" s="102"/>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="P24" s="87" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q24" s="88">
+        <f>Q21/(Q22+Q21)*Q23</f>
+        <v>23.654290993548383</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B25" s="63"/>
       <c r="C25" s="91" t="s">
         <v>226</v>
       </c>
       <c r="D25" s="92"/>
-      <c r="E25" s="119"/>
+      <c r="E25" s="124"/>
       <c r="G25" s="81"/>
       <c r="H25" s="82"/>
       <c r="J25" s="101">
         <v>100</v>
       </c>
       <c r="K25" s="102"/>
-    </row>
-    <row r="26" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P25" s="81"/>
+      <c r="Q25" s="82"/>
+    </row>
+    <row r="26" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="63"/>
       <c r="C26" s="36" t="str">
         <f>HMI!E18</f>
@@ -10890,29 +11112,33 @@
       </c>
       <c r="D26" s="2">
         <f>HMI!F18</f>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E26" s="120"/>
+        <v>3.3</v>
+      </c>
+      <c r="E26" s="125"/>
       <c r="G26" s="75"/>
       <c r="H26" s="76"/>
       <c r="J26" s="101">
         <v>120</v>
       </c>
       <c r="K26" s="102"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="P26" s="71"/>
+      <c r="Q26" s="72"/>
+    </row>
+    <row r="27" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="63"/>
       <c r="C27" s="91" t="s">
         <v>102</v>
       </c>
       <c r="D27" s="92"/>
-      <c r="E27" s="119"/>
+      <c r="E27" s="124"/>
       <c r="J27" s="101">
         <v>150</v>
       </c>
       <c r="K27" s="102"/>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="P27" s="75"/>
+      <c r="Q27" s="76"/>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B28" s="63"/>
       <c r="C28" s="36" t="s">
         <v>206</v>
@@ -10921,13 +11147,13 @@
         <f>HMI!H4</f>
         <v>TI CSD18540Q5B</v>
       </c>
-      <c r="E28" s="120"/>
+      <c r="E28" s="125"/>
       <c r="J28" s="101">
         <v>180</v>
       </c>
       <c r="K28" s="102"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B29" s="63"/>
       <c r="C29" s="36" t="str">
         <f>HMI!H6</f>
@@ -10937,13 +11163,13 @@
         <f>_xlfn.XLOOKUP(D28, DB_Mostfet[Part],DB_Mostfet[Qg,typ @ 10V (nC)])</f>
         <v>41</v>
       </c>
-      <c r="E29" s="120"/>
+      <c r="E29" s="125"/>
       <c r="J29" s="101">
         <v>220</v>
       </c>
       <c r="K29" s="102"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B30" s="63"/>
       <c r="C30" s="63"/>
       <c r="D30" s="63"/>
@@ -10953,13 +11179,13 @@
       </c>
       <c r="K30" s="102"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
       <c r="J31" s="101">
         <v>680</v>
       </c>
       <c r="K31" s="102"/>
     </row>
-    <row r="32" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J32" s="99">
         <v>1000</v>
       </c>
@@ -11099,7 +11325,7 @@
       </c>
       <c r="E6" s="65"/>
       <c r="G6" s="73" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H6" s="85">
         <f>H2^2*H4*H5%</f>
@@ -11118,7 +11344,7 @@
       </c>
       <c r="E7" s="65"/>
       <c r="G7" s="87" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H7" s="88">
         <f>H3^2*H4*H5%</f>
@@ -11219,7 +11445,7 @@
     <row r="14" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B14" s="63"/>
       <c r="C14" s="91" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D14" s="92"/>
       <c r="E14" s="65"/>
@@ -11260,7 +11486,7 @@
       </c>
       <c r="D16" s="7">
         <f>HMI!F37</f>
-        <v>6.1556249999999997</v>
+        <v>7.5478900375939855</v>
       </c>
       <c r="E16" s="64"/>
       <c r="G16" s="70" t="str">
@@ -11283,25 +11509,25 @@
       </c>
       <c r="H17" s="78">
         <f>D16</f>
-        <v>6.1556249999999997</v>
+        <v>7.5478900375939855</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="G18" s="73" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H18" s="85">
         <f>0.5*H12*H13*H15*(H16+H17)*10^-3</f>
-        <v>231.80864350000004</v>
+        <v>251.9318854473685</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G19" s="73" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H19" s="85">
         <f>0.5*H12*H14*H15*(H16+H17)*10^-3</f>
-        <v>359.25400000000002</v>
+        <v>390.44073684210537</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.35">
@@ -11344,7 +11570,7 @@
       </c>
       <c r="H26" s="85">
         <f>H18</f>
-        <v>231.80864350000004</v>
+        <v>251.9318854473685</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.35">
@@ -11354,25 +11580,25 @@
       </c>
       <c r="H27" s="85">
         <f>H19</f>
-        <v>359.25400000000002</v>
+        <v>390.44073684210537</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.35">
       <c r="G28" s="73" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H28" s="85">
         <f>2*H24+4*H26</f>
-        <v>1586.7291130000003</v>
+        <v>1667.2220807894741</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G29" s="73" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H29" s="88">
         <f>2*H25+4*H27</f>
-        <v>3021.0160000000005</v>
+        <v>3145.7629473684219</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.35">
@@ -11403,11 +11629,11 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="B1:T31"/>
+  <dimension ref="B1:Q31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="3.1796875" style="67" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.08984375" style="67" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.26953125" style="67" customWidth="1"/>
     <col min="5" max="6" width="3.1796875" style="67" customWidth="1"/>
     <col min="7" max="7" width="18.7265625" style="67" customWidth="1"/>
@@ -11426,21 +11652,21 @@
     <col min="20" max="16384" width="8.7265625" style="67"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E1" s="125"/>
-    </row>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E1" s="130"/>
+    </row>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B2" s="63"/>
       <c r="C2" s="63"/>
       <c r="D2" s="63"/>
-      <c r="E2" s="120"/>
+      <c r="E2" s="125"/>
       <c r="G2" s="68" t="str">
         <f>C8</f>
         <v>Rg,off (Ω)</v>
       </c>
-      <c r="H2" s="69">
+      <c r="H2" s="90">
         <f>D8</f>
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="J2" s="68" t="str">
         <f>C16</f>
@@ -11448,7 +11674,7 @@
       </c>
       <c r="K2" s="69">
         <f>D16</f>
-        <v>9.76</v>
+        <v>10.26</v>
       </c>
       <c r="M2" s="68" t="str">
         <f>C21</f>
@@ -11459,29 +11685,21 @@
         <v>41</v>
       </c>
       <c r="P2" s="68" t="str">
-        <f>M11</f>
-        <v>Pg,loss (mW)</v>
-      </c>
-      <c r="Q2" s="69">
-        <f>N11</f>
-        <v>76.830719999999985</v>
-      </c>
-      <c r="S2" s="68" t="str">
-        <f>P19</f>
-        <v>Prg,mean (mW)</v>
-      </c>
-      <c r="T2" s="69">
-        <f>Q19</f>
-        <v>59.071565223789072</v>
-      </c>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.35">
+        <f>M28</f>
+        <v>Rg,mean (Ω)</v>
+      </c>
+      <c r="Q2" s="77">
+        <f>N28</f>
+        <v>1.6090601503759396</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B3" s="63"/>
       <c r="C3" s="91" t="s">
         <v>117</v>
       </c>
       <c r="D3" s="92"/>
-      <c r="E3" s="120"/>
+      <c r="E3" s="125"/>
       <c r="G3" s="70" t="str">
         <f>C9</f>
         <v>Rg,on+off (Ω)</v>
@@ -11504,26 +11722,18 @@
       </c>
       <c r="N3" s="61">
         <f>D16</f>
-        <v>9.76</v>
+        <v>10.26</v>
       </c>
       <c r="P3" s="70" t="str">
-        <f>P19</f>
-        <v>Prg,mean (mW)</v>
-      </c>
-      <c r="Q3" s="85">
-        <f>Q19</f>
-        <v>59.071565223789072</v>
-      </c>
-      <c r="S3" s="70" t="str">
-        <f>P28</f>
-        <v>Prg,off (mW)</v>
-      </c>
-      <c r="T3" s="85">
-        <f>Q28</f>
-        <v>0.59071565223789047</v>
-      </c>
-    </row>
-    <row r="4" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <f>M20</f>
+        <v>Rgatedriver,mean (Ω)</v>
+      </c>
+      <c r="Q3" s="74">
+        <f>N20</f>
+        <v>0.47125</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="63"/>
       <c r="C4" s="36" t="s">
         <v>103</v>
@@ -11532,13 +11742,13 @@
         <f>HMI!B4</f>
         <v>V1.0</v>
       </c>
-      <c r="E4" s="120"/>
+      <c r="E4" s="125"/>
       <c r="G4" s="79" t="s">
         <v>236</v>
       </c>
       <c r="H4" s="83">
         <f>H2*H3/(H3+H2)</f>
-        <v>1.65</v>
+        <v>2.481203007518797</v>
       </c>
       <c r="J4" s="70" t="str">
         <f>G22</f>
@@ -11546,7 +11756,7 @@
       </c>
       <c r="K4" s="78">
         <f>H22</f>
-        <v>3.6749999999999998</v>
+        <v>4.5062030075187973</v>
       </c>
       <c r="M4" s="70" t="str">
         <f>C6</f>
@@ -11556,22 +11766,16 @@
         <f>D6</f>
         <v>64</v>
       </c>
-      <c r="P4" s="87" t="s">
-        <v>314</v>
-      </c>
-      <c r="Q4" s="88">
-        <f>Q2-Q3</f>
-        <v>17.759154776210913</v>
-      </c>
-      <c r="S4" s="79" t="s">
-        <v>316</v>
-      </c>
-      <c r="T4" s="89">
-        <f>T2-T3</f>
-        <v>58.480849571551182</v>
-      </c>
-    </row>
-    <row r="5" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P4" s="70" t="str">
+        <f>M11</f>
+        <v>Pg,loss (mW)</v>
+      </c>
+      <c r="Q4" s="78">
+        <f>N11</f>
+        <v>40.383359999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B5" s="63"/>
       <c r="C5" s="36" t="str">
         <f>HMI!B6</f>
@@ -11582,28 +11786,31 @@
         <v>90</v>
       </c>
       <c r="E5" s="63"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="129"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="132"/>
       <c r="J5" s="73" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="K5" s="74">
         <f>K2/K3</f>
-        <v>1.6542372881355931</v>
+        <v>1.7389830508474575</v>
       </c>
       <c r="M5" s="87" t="s">
         <v>241</v>
       </c>
       <c r="N5" s="89">
         <f>N2*N3*N4*10^-3</f>
-        <v>25.610239999999997</v>
-      </c>
-      <c r="P5" s="128"/>
-      <c r="Q5" s="129"/>
-      <c r="S5" s="128"/>
-      <c r="T5" s="129"/>
-    </row>
-    <row r="6" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>26.922239999999999</v>
+      </c>
+      <c r="P5" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q5" s="86">
+        <f>Q4*Q2/(Q2+Q3)</f>
+        <v>31.235369063859579</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="63"/>
       <c r="C6" s="36" t="str">
         <f>HMI!B7</f>
@@ -11613,60 +11820,54 @@
         <f>HMI!C7</f>
         <v>64</v>
       </c>
-      <c r="E6" s="119"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="131"/>
+      <c r="E6" s="124"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="134"/>
       <c r="J6" s="87" t="s">
-        <v>305</v>
-      </c>
-      <c r="K6" s="118">
+        <v>303</v>
+      </c>
+      <c r="K6" s="123">
         <f>K2/K4</f>
-        <v>2.6557823129251701</v>
-      </c>
-      <c r="M6" s="128"/>
-      <c r="N6" s="129"/>
-      <c r="P6" s="132"/>
-      <c r="Q6" s="133"/>
-      <c r="S6" s="132"/>
-      <c r="T6" s="133"/>
-    </row>
-    <row r="7" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>2.2768614691527969</v>
+      </c>
+      <c r="M6" s="131"/>
+      <c r="N6" s="132"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="110"/>
+    </row>
+    <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="63"/>
       <c r="C7" s="91" t="s">
         <v>231</v>
       </c>
       <c r="D7" s="92"/>
-      <c r="E7" s="120"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="133"/>
+      <c r="E7" s="125"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="136"/>
       <c r="J7" s="71"/>
       <c r="K7" s="72"/>
-      <c r="M7" s="132"/>
-      <c r="N7" s="133"/>
-    </row>
-    <row r="8" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M7" s="135"/>
+      <c r="N7" s="136"/>
+      <c r="P7" s="111"/>
+      <c r="Q7" s="112"/>
+    </row>
+    <row r="8" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="63"/>
       <c r="C8" s="36" t="str">
-        <f>HMI!E29</f>
+        <f>HMI!E31</f>
         <v>Rg,off (Ω)</v>
       </c>
       <c r="D8" s="2">
-        <f>HMI!F29</f>
-        <v>3.3</v>
-      </c>
-      <c r="E8" s="120"/>
+        <f>HMI!F31</f>
+        <v>10</v>
+      </c>
+      <c r="E8" s="125"/>
       <c r="J8" s="71"/>
       <c r="K8" s="72"/>
-      <c r="P8" s="68" t="str">
-        <f>M15</f>
-        <v>Dmax (%)</v>
-      </c>
-      <c r="Q8" s="84">
-        <f>N15</f>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="P8" s="113"/>
+      <c r="Q8" s="114"/>
+    </row>
+    <row r="9" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="63"/>
       <c r="C9" s="36" t="str">
         <f>HMI!E30</f>
@@ -11693,24 +11894,16 @@
       </c>
       <c r="N9" s="69">
         <f>N5</f>
-        <v>25.610239999999997</v>
-      </c>
-      <c r="P9" s="70" t="str">
-        <f>G3</f>
-        <v>Rg,on+off (Ω)</v>
-      </c>
-      <c r="Q9" s="61">
-        <f>H3</f>
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="10" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>26.922239999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="63"/>
       <c r="C10" s="91" t="s">
         <v>232</v>
       </c>
       <c r="D10" s="92"/>
-      <c r="E10" s="119"/>
+      <c r="E10" s="124"/>
       <c r="G10" s="70" t="str">
         <f>C13</f>
         <v>Rpu,ls (Ω)</v>
@@ -11727,18 +11920,18 @@
       </c>
       <c r="N10" s="61">
         <f>D18</f>
-        <v>3</v>
-      </c>
-      <c r="P10" s="70" t="str">
-        <f>G4</f>
-        <v>Rg,eq,off</v>
-      </c>
-      <c r="Q10" s="78">
-        <f>H4</f>
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="11" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>1.5</v>
+      </c>
+      <c r="P10" s="68" t="str">
+        <f>C8</f>
+        <v>Rg,off (Ω)</v>
+      </c>
+      <c r="Q10" s="84">
+        <f>D8</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="63"/>
       <c r="C11" s="36" t="s">
         <v>206</v>
@@ -11747,7 +11940,7 @@
         <f>HMI!E3</f>
         <v>Infineon 2EDL8024</v>
       </c>
-      <c r="E11" s="120"/>
+      <c r="E11" s="125"/>
       <c r="G11" s="70" t="str">
         <f>C9</f>
         <v>Rg,on+off (Ω)</v>
@@ -11761,17 +11954,18 @@
       </c>
       <c r="N11" s="88">
         <f>N9*N10</f>
-        <v>76.830719999999985</v>
-      </c>
-      <c r="P11" s="87" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q11" s="89">
-        <f>(Q8%*Q9+(1-Q8%)*Q10)/2</f>
-        <v>1.5674999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
+        <v>40.383359999999996</v>
+      </c>
+      <c r="P11" s="70" t="str">
+        <f>C9</f>
+        <v>Rg,on+off (Ω)</v>
+      </c>
+      <c r="Q11" s="61">
+        <f>D9</f>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B12" s="63"/>
       <c r="C12" s="36" t="str">
         <f>DB_GD[[#Headers],[Rpu,hs (Ω)]]</f>
@@ -11781,7 +11975,7 @@
         <f>_xlfn.XLOOKUP(D11, DB_GD[Part], DB_GD[Rpu,hs (Ω)])</f>
         <v>1</v>
       </c>
-      <c r="E12" s="120"/>
+      <c r="E12" s="125"/>
       <c r="G12" s="70" t="str">
         <f>C24</f>
         <v>Rg,int,max (Ω)</v>
@@ -11798,12 +11992,18 @@
         <f>D23</f>
         <v>4</v>
       </c>
-      <c r="M12" s="114"/>
-      <c r="N12" s="115"/>
-      <c r="P12" s="128"/>
-      <c r="Q12" s="129"/>
-    </row>
-    <row r="13" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M12" s="119"/>
+      <c r="N12" s="120"/>
+      <c r="P12" s="70" t="str">
+        <f>P5</f>
+        <v>Prg,mean (mW)</v>
+      </c>
+      <c r="Q12" s="85">
+        <f>Q5</f>
+        <v>31.235369063859579</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="63"/>
       <c r="C13" s="36" t="str">
         <f>DB_GD[[#Headers],[Rpu,ls (Ω)]]</f>
@@ -11813,7 +12013,7 @@
         <f>_xlfn.XLOOKUP(D11, DB_GD[Part], DB_GD[Rpu,ls (Ω)])</f>
         <v>1</v>
       </c>
-      <c r="E13" s="120"/>
+      <c r="E13" s="125"/>
       <c r="G13" s="79" t="s">
         <v>233</v>
       </c>
@@ -11829,12 +12029,17 @@
         <f>H13</f>
         <v>5.9</v>
       </c>
-      <c r="M13" s="116"/>
-      <c r="N13" s="117"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="131"/>
-    </row>
-    <row r="14" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M13" s="121"/>
+      <c r="N13" s="122"/>
+      <c r="P13" s="79" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q13" s="83">
+        <f>0.5*(1+Q10/(Q10+Q11))*Q12</f>
+        <v>27.360304480749178</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="63"/>
       <c r="C14" s="36" t="str">
         <f>DB_GD[[#Headers],[Rpd,hs (Ω)]]</f>
@@ -11844,21 +12049,21 @@
         <f>_xlfn.XLOOKUP(D11, DB_GD[Part], DB_GD[Rpd,hs (Ω)])</f>
         <v>0.5</v>
       </c>
-      <c r="E14" s="120"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="135"/>
+      <c r="E14" s="125"/>
+      <c r="G14" s="137"/>
+      <c r="H14" s="138"/>
       <c r="J14" s="70" t="str">
         <f>G22</f>
         <v>Req,off (Ω)</v>
       </c>
       <c r="K14" s="78">
         <f>H22</f>
-        <v>3.6749999999999998</v>
-      </c>
-      <c r="P14" s="132"/>
-      <c r="Q14" s="133"/>
-    </row>
-    <row r="15" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>4.5062030075187973</v>
+      </c>
+      <c r="P14" s="137"/>
+      <c r="Q14" s="138"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B15" s="63"/>
       <c r="C15" s="36" t="str">
         <f>DB_GD[[#Headers],[Rpd,ls (Ω)]]</f>
@@ -11868,11 +12073,11 @@
         <f>_xlfn.XLOOKUP(D11, DB_GD[Part], DB_GD[Rpd,ls (Ω)])</f>
         <v>0.35</v>
       </c>
-      <c r="E15" s="120"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="137"/>
+      <c r="E15" s="125"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="140"/>
       <c r="J15" s="73" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K15" s="74">
         <f>K12/K13</f>
@@ -11886,8 +12091,10 @@
         <f>D5</f>
         <v>90</v>
       </c>
-    </row>
-    <row r="16" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P15" s="139"/>
+      <c r="Q15" s="140"/>
+    </row>
+    <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="63"/>
       <c r="C16" s="36" t="str">
         <f>HMI!E21</f>
@@ -11895,17 +12102,17 @@
       </c>
       <c r="D16" s="2">
         <f>HMI!F21</f>
-        <v>9.76</v>
-      </c>
-      <c r="E16" s="120"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="139"/>
+        <v>10.26</v>
+      </c>
+      <c r="E16" s="125"/>
+      <c r="G16" s="141"/>
+      <c r="H16" s="142"/>
       <c r="J16" s="87" t="s">
-        <v>308</v>
-      </c>
-      <c r="K16" s="118">
+        <v>306</v>
+      </c>
+      <c r="K16" s="123">
         <f>K12/K14</f>
-        <v>1.08843537414966</v>
+        <v>0.8876652901180494</v>
       </c>
       <c r="M16" s="70" t="str">
         <f>G9</f>
@@ -11915,14 +12122,8 @@
         <f>H9</f>
         <v>1</v>
       </c>
-      <c r="P16" s="68" t="str">
-        <f>P11</f>
-        <v>Rg,mean (Ω)</v>
-      </c>
-      <c r="Q16" s="77">
-        <f>Q11</f>
-        <v>1.5674999999999999</v>
-      </c>
+      <c r="P16" s="141"/>
+      <c r="Q16" s="142"/>
     </row>
     <row r="17" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="63"/>
@@ -11932,9 +12133,9 @@
       </c>
       <c r="D17" s="2">
         <f>HMI!F23</f>
-        <v>150</v>
-      </c>
-      <c r="E17" s="120"/>
+        <v>180</v>
+      </c>
+      <c r="E17" s="125"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
       <c r="M17" s="70" t="str">
@@ -11945,26 +12146,18 @@
         <f>H10</f>
         <v>1</v>
       </c>
-      <c r="P17" s="70" t="str">
-        <f>M20</f>
-        <v>Rgatedriver,mean (Ω)</v>
-      </c>
-      <c r="Q17" s="74">
-        <f>N20</f>
-        <v>0.47125</v>
-      </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B18" s="63"/>
       <c r="C18" s="36" t="str">
-        <f>HMI!E31</f>
+        <f>HMI!E32</f>
         <v>Safety margin on losses</v>
       </c>
       <c r="D18" s="7">
-        <f>HMI!F31</f>
-        <v>3</v>
-      </c>
-      <c r="E18" s="121"/>
+        <f>HMI!F32</f>
+        <v>1.5</v>
+      </c>
+      <c r="E18" s="126"/>
       <c r="G18" s="68" t="str">
         <f>C14</f>
         <v>Rpd,hs (Ω)</v>
@@ -11983,16 +12176,16 @@
         <f>H18</f>
         <v>0.5</v>
       </c>
-      <c r="P18" s="70" t="str">
-        <f>M11</f>
-        <v>Pg,loss (mW)</v>
-      </c>
-      <c r="Q18" s="78">
-        <f>N11</f>
-        <v>76.830719999999985</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P18" s="68" t="str">
+        <f>P5</f>
+        <v>Prg,mean (mW)</v>
+      </c>
+      <c r="Q18" s="69">
+        <f>Q5</f>
+        <v>31.235369063859579</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" s="63"/>
       <c r="C19" s="91" t="s">
         <v>102</v>
@@ -12017,12 +12210,13 @@
         <f>H19</f>
         <v>0.35</v>
       </c>
-      <c r="P19" s="79" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q19" s="86">
-        <f>Q18*Q16/(Q16+Q17)</f>
-        <v>59.071565223789072</v>
+      <c r="P19" s="70" t="str">
+        <f>P13</f>
+        <v>Prg,on+off (mW)</v>
+      </c>
+      <c r="Q19" s="85">
+        <f>Q13</f>
+        <v>27.360304480749178</v>
       </c>
     </row>
     <row r="20" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -12034,26 +12228,31 @@
         <f>HMI!H4</f>
         <v>TI CSD18540Q5B</v>
       </c>
-      <c r="E20" s="119"/>
+      <c r="E20" s="124"/>
       <c r="G20" s="70" t="str">
         <f>G4</f>
         <v>Rg,eq,off</v>
       </c>
       <c r="H20" s="78">
         <f>H4</f>
-        <v>1.65</v>
+        <v>2.481203007518797</v>
       </c>
       <c r="J20" s="75"/>
       <c r="K20" s="76"/>
       <c r="M20" s="87" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="N20" s="89">
         <f>(N15%*(N17+N16)+(1-N15%)*(N18+N19))/4</f>
         <v>0.47125</v>
       </c>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="115"/>
+      <c r="P20" s="79" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q20" s="89">
+        <f>Q18-Q19</f>
+        <v>3.8750645831104009</v>
+      </c>
     </row>
     <row r="21" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="63"/>
@@ -12065,7 +12264,7 @@
         <f>_xlfn.XLOOKUP(D20, DB_Mostfet[Part],DB_Mostfet[Qg,typ @ 10V (nC)])</f>
         <v>41</v>
       </c>
-      <c r="E21" s="120"/>
+      <c r="E21" s="125"/>
       <c r="G21" s="70" t="str">
         <f>C24</f>
         <v>Rg,int,max (Ω)</v>
@@ -12074,10 +12273,10 @@
         <f>D24</f>
         <v>1.6</v>
       </c>
-      <c r="M21" s="128"/>
-      <c r="N21" s="129"/>
-      <c r="P21" s="126"/>
-      <c r="Q21" s="127"/>
+      <c r="M21" s="131"/>
+      <c r="N21" s="132"/>
+      <c r="P21" s="137"/>
+      <c r="Q21" s="138"/>
     </row>
     <row r="22" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="63"/>
@@ -12089,13 +12288,13 @@
         <f>_xlfn.XLOOKUP(D20, DB_Mostfet[Part],DB_Mostfet[Qgd,typ (nC)])</f>
         <v>6.7</v>
       </c>
-      <c r="E22" s="119"/>
+      <c r="E22" s="124"/>
       <c r="G22" s="79" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H22" s="83">
         <f>(H18+H19)/2+H20+H21</f>
-        <v>3.6749999999999998</v>
+        <v>4.5062030075187973</v>
       </c>
       <c r="J22" s="68" t="str">
         <f>C22</f>
@@ -12105,10 +12304,10 @@
         <f>D22</f>
         <v>6.7</v>
       </c>
-      <c r="M22" s="130"/>
-      <c r="N22" s="131"/>
-      <c r="P22" s="116"/>
-      <c r="Q22" s="117"/>
+      <c r="M22" s="133"/>
+      <c r="N22" s="134"/>
+      <c r="P22" s="141"/>
+      <c r="Q22" s="142"/>
     </row>
     <row r="23" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="63"/>
@@ -12120,9 +12319,9 @@
         <f>_xlfn.XLOOKUP(D20, DB_Mostfet[Part],DB_Mostfet[Vmiller (V)])</f>
         <v>4</v>
       </c>
-      <c r="E23" s="119"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="135"/>
+      <c r="E23" s="124"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="138"/>
       <c r="J23" s="70" t="str">
         <f>J15</f>
         <v>Imiller,on (A)</v>
@@ -12131,10 +12330,10 @@
         <f>K15</f>
         <v>0.67796610169491522</v>
       </c>
-      <c r="M23" s="132"/>
-      <c r="N23" s="133"/>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="M23" s="135"/>
+      <c r="N23" s="136"/>
+    </row>
+    <row r="24" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="63"/>
       <c r="C24" s="36" t="str">
         <f>DB_Mostfet[[#Headers],[Rg,int,max (Ω)]]</f>
@@ -12144,113 +12343,128 @@
         <f>_xlfn.XLOOKUP(D20, DB_Mostfet[Part],DB_Mostfet[Rg,int,max (Ω)])</f>
         <v>1.6</v>
       </c>
-      <c r="E24" s="120"/>
-      <c r="G24" s="136"/>
-      <c r="H24" s="137"/>
+      <c r="E24" s="125"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="140"/>
       <c r="J24" s="70" t="str">
         <f>J16</f>
         <v>Imiller,off (A)</v>
       </c>
       <c r="K24" s="74">
         <f>K16</f>
-        <v>1.08843537414966</v>
+        <v>0.8876652901180494</v>
       </c>
       <c r="P24" s="68" t="str">
-        <f>C8</f>
-        <v>Rg,off (Ω)</v>
-      </c>
-      <c r="Q24" s="84">
-        <f>D8</f>
-        <v>3.3</v>
+        <f>M11</f>
+        <v>Pg,loss (mW)</v>
+      </c>
+      <c r="Q24" s="69">
+        <f>N11</f>
+        <v>40.383359999999996</v>
       </c>
     </row>
     <row r="25" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="63"/>
       <c r="C25" s="63"/>
       <c r="D25" s="63"/>
-      <c r="E25" s="120"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="139"/>
+      <c r="E25" s="125"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="142"/>
       <c r="J25" s="73" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="K25" s="74">
         <f>K22/K23</f>
         <v>9.8825000000000003</v>
       </c>
+      <c r="M25" s="68" t="str">
+        <f>M15</f>
+        <v>Dmax (%)</v>
+      </c>
+      <c r="N25" s="84">
+        <f>N15</f>
+        <v>90</v>
+      </c>
       <c r="P25" s="70" t="str">
-        <f>C9</f>
-        <v>Rg,on+off (Ω)</v>
-      </c>
-      <c r="Q25" s="61">
-        <f>D9</f>
-        <v>3.3</v>
+        <f>P5</f>
+        <v>Prg,mean (mW)</v>
+      </c>
+      <c r="Q25" s="85">
+        <f>Q5</f>
+        <v>31.235369063859579</v>
       </c>
     </row>
     <row r="26" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J26" s="87" t="s">
-        <v>310</v>
-      </c>
-      <c r="K26" s="118">
+        <v>308</v>
+      </c>
+      <c r="K26" s="123">
         <f>K22/K24</f>
-        <v>6.1556249999999997</v>
-      </c>
-      <c r="P26" s="70" t="str">
-        <f>C5</f>
-        <v>Dmax (%)</v>
-      </c>
-      <c r="Q26" s="85">
-        <f>D5</f>
-        <v>90</v>
+        <v>7.5478900375939855</v>
+      </c>
+      <c r="M26" s="70" t="str">
+        <f>G3</f>
+        <v>Rg,on+off (Ω)</v>
+      </c>
+      <c r="N26" s="61">
+        <f>H3</f>
+        <v>3.3</v>
+      </c>
+      <c r="P26" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q26" s="88">
+        <f>Q24-Q25</f>
+        <v>9.1479909361404168</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.35">
       <c r="J27" s="71"/>
       <c r="K27" s="72"/>
-      <c r="P27" s="70" t="str">
-        <f>P19</f>
-        <v>Prg,mean (mW)</v>
-      </c>
-      <c r="Q27" s="85">
-        <f>Q19</f>
-        <v>59.071565223789072</v>
-      </c>
+      <c r="M27" s="70" t="str">
+        <f>G4</f>
+        <v>Rg,eq,off</v>
+      </c>
+      <c r="N27" s="78">
+        <f>H4</f>
+        <v>2.481203007518797</v>
+      </c>
+      <c r="P27" s="137"/>
+      <c r="Q27" s="138"/>
     </row>
     <row r="28" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J28" s="71"/>
       <c r="K28" s="72"/>
-      <c r="P28" s="79" t="s">
-        <v>315</v>
-      </c>
-      <c r="Q28" s="83">
-        <f>Q24*(1-Q26%)^2*Q27/Q25</f>
-        <v>0.59071565223789047</v>
-      </c>
+      <c r="M28" s="87" t="s">
+        <v>237</v>
+      </c>
+      <c r="N28" s="89">
+        <f>(N25%*N26+(1-N25%)*N27)/2</f>
+        <v>1.6090601503759396</v>
+      </c>
+      <c r="P28" s="141"/>
+      <c r="Q28" s="142"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.35">
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
-      <c r="P29" s="134"/>
-      <c r="Q29" s="135"/>
+      <c r="M29" s="137"/>
+      <c r="N29" s="138"/>
     </row>
     <row r="30" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J30" s="75"/>
       <c r="K30" s="76"/>
-      <c r="P30" s="136"/>
-      <c r="Q30" s="137"/>
+      <c r="M30" s="139"/>
+      <c r="N30" s="140"/>
     </row>
     <row r="31" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="P31" s="138"/>
-      <c r="Q31" s="139"/>
+      <c r="M31" s="141"/>
+      <c r="N31" s="142"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="S5:T6"/>
-    <mergeCell ref="P5:Q6"/>
+  <mergeCells count="8">
     <mergeCell ref="G5:H7"/>
-    <mergeCell ref="P12:Q14"/>
     <mergeCell ref="M21:N23"/>
-    <mergeCell ref="P20:Q22"/>
     <mergeCell ref="M12:N13"/>
     <mergeCell ref="M6:N7"/>
     <mergeCell ref="C3:D3"/>
@@ -14085,7 +14299,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="B1:K26"/>
+  <dimension ref="B1:K25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.1796875" style="67" customWidth="1"/>
@@ -14213,7 +14427,7 @@
       <c r="G6" s="75"/>
       <c r="H6" s="76"/>
       <c r="J6" s="87" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K6" s="89">
         <f>K2/(2^K3-1)/K4/K5*10^9</f>
@@ -14231,8 +14445,8 @@
         <v>12.905000000000001</v>
       </c>
       <c r="E7" s="66"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="111"/>
+      <c r="J7" s="115"/>
+      <c r="K7" s="116"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B8" s="63"/>
@@ -14253,8 +14467,8 @@
         <f>H4</f>
         <v>10.625</v>
       </c>
-      <c r="J8" s="112"/>
-      <c r="K8" s="113"/>
+      <c r="J8" s="117"/>
+      <c r="K8" s="118"/>
     </row>
     <row r="9" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="63"/>
@@ -14293,7 +14507,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B11" s="63"/>
       <c r="C11" s="36" t="str">
         <f>HMI!K4</f>
@@ -14306,6 +14520,14 @@
       <c r="E11" s="64"/>
       <c r="G11" s="81"/>
       <c r="H11" s="82"/>
+      <c r="J11" s="68" t="str">
+        <f>C11</f>
+        <v>Rshunt (µΩ)</v>
+      </c>
+      <c r="K11" s="69">
+        <f>D11</f>
+        <v>850</v>
+      </c>
     </row>
     <row r="12" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="63"/>
@@ -14316,13 +14538,13 @@
       <c r="E12" s="64"/>
       <c r="G12" s="75"/>
       <c r="H12" s="76"/>
-      <c r="J12" s="68" t="str">
-        <f>C11</f>
-        <v>Rshunt (µΩ)</v>
-      </c>
-      <c r="K12" s="69">
-        <f>D11</f>
-        <v>850</v>
+      <c r="J12" s="70" t="str">
+        <f>C7</f>
+        <v>Iph mean (A)</v>
+      </c>
+      <c r="K12" s="61">
+        <f>D7</f>
+        <v>12.905000000000001</v>
       </c>
     </row>
     <row r="13" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -14337,15 +14559,15 @@
       </c>
       <c r="E13" s="64"/>
       <c r="J13" s="70" t="str">
-        <f>C7</f>
-        <v>Iph mean (A)</v>
+        <f>C9</f>
+        <v>Dmax (%)</v>
       </c>
       <c r="K13" s="61">
-        <f>D7</f>
-        <v>12.905000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
+        <f>D9</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="63"/>
       <c r="C14" s="36" t="str">
         <f>HMI!K11</f>
@@ -14364,16 +14586,15 @@
         <f>D8</f>
         <v>50</v>
       </c>
-      <c r="J14" s="70" t="str">
-        <f>C9</f>
-        <v>Dmax (%)</v>
-      </c>
-      <c r="K14" s="61">
-        <f>D9</f>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J14" s="79" t="s">
+        <v>250</v>
+      </c>
+      <c r="K14" s="86">
+        <f>K11/10^3*K12^2*K13%*2/3</f>
+        <v>84.934902750000006</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B15" s="63"/>
       <c r="C15" s="36" t="str">
         <f>HMI!K13</f>
@@ -14392,13 +14613,8 @@
         <f>D11</f>
         <v>850</v>
       </c>
-      <c r="J15" s="79" t="s">
-        <v>250</v>
-      </c>
-      <c r="K15" s="86">
-        <f>K12/10^3*K13^2*K14%*2/3</f>
-        <v>84.934902750000006</v>
-      </c>
+      <c r="J15" s="81"/>
+      <c r="K15" s="82"/>
     </row>
     <row r="16" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="63"/>
@@ -14418,30 +14634,36 @@
         <f>H15*H14/1000</f>
         <v>42.5</v>
       </c>
-      <c r="J16" s="81"/>
-      <c r="K16" s="82"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="J16" s="71"/>
+      <c r="K16" s="72"/>
+    </row>
+    <row r="17" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="63"/>
       <c r="C17" s="63"/>
       <c r="D17" s="63"/>
       <c r="E17" s="63"/>
       <c r="G17" s="81"/>
       <c r="H17" s="82"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="72"/>
+      <c r="J17" s="75"/>
+      <c r="K17" s="76"/>
     </row>
     <row r="18" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="64"/>
       <c r="E18" s="64"/>
       <c r="G18" s="75"/>
       <c r="H18" s="76"/>
-      <c r="J18" s="75"/>
-      <c r="K18" s="76"/>
     </row>
     <row r="19" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="64"/>
       <c r="E19" s="64"/>
+      <c r="J19" s="68" t="str">
+        <f>J11</f>
+        <v>Rshunt (µΩ)</v>
+      </c>
+      <c r="K19" s="69">
+        <f>K11</f>
+        <v>850</v>
+      </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B20" s="64"/>
@@ -14454,13 +14676,13 @@
         <f>H16</f>
         <v>42.5</v>
       </c>
-      <c r="J20" s="68" t="str">
-        <f>J12</f>
-        <v>Rshunt (µΩ)</v>
-      </c>
-      <c r="K20" s="69">
-        <f>K12</f>
-        <v>850</v>
+      <c r="J20" s="70" t="str">
+        <f>C6</f>
+        <v>Iph max (A@Xs) @ 4.9% ToF</v>
+      </c>
+      <c r="K20" s="61">
+        <f>D6</f>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.35">
@@ -14475,12 +14697,12 @@
         <v>64</v>
       </c>
       <c r="J21" s="70" t="str">
-        <f>C6</f>
-        <v>Iph max (A@Xs) @ 4.9% ToF</v>
+        <f>C9</f>
+        <v>Dmax (%)</v>
       </c>
       <c r="K21" s="61">
-        <f>D6</f>
-        <v>20</v>
+        <f>D9</f>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -14493,27 +14715,21 @@
         <f>H21*H20/1000</f>
         <v>2.72</v>
       </c>
-      <c r="J22" s="70" t="str">
-        <f>C9</f>
-        <v>Dmax (%)</v>
-      </c>
-      <c r="K22" s="61">
-        <f>D9</f>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J22" s="79" t="s">
+        <v>251</v>
+      </c>
+      <c r="K22" s="86">
+        <f>K19/10^3*K20^2*K21%*2/3</f>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B23" s="64"/>
       <c r="E23" s="64"/>
       <c r="G23" s="81"/>
       <c r="H23" s="82"/>
-      <c r="J23" s="79" t="s">
-        <v>251</v>
-      </c>
-      <c r="K23" s="86">
-        <f>K20/10^3*K21^2*K22%*2/3</f>
-        <v>204</v>
-      </c>
+      <c r="J23" s="81"/>
+      <c r="K23" s="82"/>
     </row>
     <row r="24" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="63"/>
@@ -14522,16 +14738,12 @@
       <c r="E24" s="63"/>
       <c r="G24" s="75"/>
       <c r="H24" s="76"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="82"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="J25" s="71"/>
-      <c r="K25" s="72"/>
-    </row>
-    <row r="26" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J26" s="75"/>
-      <c r="K26" s="76"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="72"/>
+    </row>
+    <row r="25" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J25" s="75"/>
+      <c r="K25" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -15037,7 +15249,7 @@
       </c>
       <c r="H2" s="84">
         <f>D18</f>
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="J2" s="68" t="str">
         <f>C6</f>
@@ -15049,11 +15261,11 @@
       </c>
       <c r="M2" s="68" t="str">
         <f>G6</f>
-        <v>Rv1 (Ω)</v>
+        <v>Rv1 (kΩ)</v>
       </c>
       <c r="N2" s="69">
         <f>H6</f>
-        <v>11000</v>
+        <v>10</v>
       </c>
       <c r="P2" s="68" t="str">
         <f t="shared" ref="P2:Q4" si="0">C13</f>
@@ -15081,11 +15293,11 @@
       </c>
       <c r="J3" s="70" t="str">
         <f>G6</f>
-        <v>Rv1 (Ω)</v>
+        <v>Rv1 (kΩ)</v>
       </c>
       <c r="K3" s="85">
         <f>H6</f>
-        <v>11000</v>
+        <v>10</v>
       </c>
       <c r="M3" s="70" t="str">
         <f>C18</f>
@@ -15093,7 +15305,7 @@
       </c>
       <c r="N3" s="61">
         <f>D18</f>
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="P3" s="70" t="str">
         <f t="shared" si="0"/>
@@ -15128,14 +15340,14 @@
       </c>
       <c r="K4" s="61">
         <f>D18</f>
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="M4" s="87" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="N4" s="88">
         <f>N2*N3/(N3+N2)</f>
-        <v>1000</v>
+        <v>9.9009900990099009</v>
       </c>
       <c r="P4" s="70" t="str">
         <f t="shared" si="0"/>
@@ -15158,23 +15370,23 @@
       </c>
       <c r="E5" s="65"/>
       <c r="G5" s="73" t="s">
-        <v>259</v>
-      </c>
-      <c r="H5" s="85">
-        <f>H2*(H3/H4-1)</f>
-        <v>10566.666666666668</v>
+        <v>324</v>
+      </c>
+      <c r="H5" s="74">
+        <f>H2*(H3/H4-1)/1000</f>
+        <v>9.6060606060606073</v>
       </c>
       <c r="J5" s="79" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="K5" s="80">
         <f>K2/(K3+K4)*10^3</f>
-        <v>2.0826446280991737</v>
+        <v>24.950495049504951</v>
       </c>
       <c r="M5" s="81"/>
       <c r="N5" s="82"/>
       <c r="P5" s="79" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q5" s="83">
         <f>Q4+Q3+Q2</f>
@@ -15193,11 +15405,11 @@
       </c>
       <c r="E6" s="65"/>
       <c r="G6" s="79" t="s">
-        <v>256</v>
-      </c>
-      <c r="H6" s="86">
+        <v>325</v>
+      </c>
+      <c r="H6" s="80">
         <f>_xlfn.MINIFS(DB_R[R (Ω)],DB_R[R (Ω)],"&gt;="&amp;H5)</f>
-        <v>11000</v>
+        <v>10</v>
       </c>
       <c r="J6" s="81"/>
       <c r="K6" s="82"/>
@@ -15281,7 +15493,7 @@
       </c>
       <c r="K10" s="77">
         <f>H23</f>
-        <v>3.1818181818181817</v>
+        <v>34.653465346534652</v>
       </c>
       <c r="M10" s="75"/>
       <c r="N10" s="76"/>
@@ -15291,7 +15503,7 @@
       </c>
       <c r="Q10" s="85">
         <f>N27</f>
-        <v>1000</v>
+        <v>9.9009900990099009</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15307,11 +15519,11 @@
       <c r="E11" s="65"/>
       <c r="G11" s="68" t="str">
         <f>G6</f>
-        <v>Rv1 (Ω)</v>
+        <v>Rv1 (kΩ)</v>
       </c>
       <c r="H11" s="69">
         <f>H6</f>
-        <v>11000</v>
+        <v>10</v>
       </c>
       <c r="J11" s="70" t="str">
         <f>G24</f>
@@ -15319,7 +15531,7 @@
       </c>
       <c r="K11" s="74">
         <f>H24</f>
-        <v>2.290909090909091</v>
+        <v>24.950495049504955</v>
       </c>
       <c r="P11" s="70" t="str">
         <f>M28</f>
@@ -15347,7 +15559,7 @@
       </c>
       <c r="H12" s="61">
         <f>D18</f>
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="J12" s="70" t="str">
         <f>C20</f>
@@ -15363,7 +15575,7 @@
       </c>
       <c r="N12" s="69">
         <f>N4</f>
-        <v>1000</v>
+        <v>9.9009900990099009</v>
       </c>
       <c r="P12" s="70" t="str">
         <f>P5</f>
@@ -15394,11 +15606,11 @@
         <v>35</v>
       </c>
       <c r="J13" s="73" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K13" s="85">
         <f>K10/K12*1000</f>
-        <v>96.418732782369133</v>
+        <v>1050.1050105010502</v>
       </c>
       <c r="M13" s="70" t="str">
         <f>C20</f>
@@ -15409,11 +15621,11 @@
         <v>33</v>
       </c>
       <c r="P13" s="79" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q13" s="83">
         <f>Q9*(Q10+Q11)*(Q12)*10^-3</f>
-        <v>185.94</v>
+        <v>7.7221782178217833</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15428,18 +15640,18 @@
       </c>
       <c r="E14" s="63"/>
       <c r="G14" s="79" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H14" s="86">
         <f>H13^2/(H11+H12)*1000</f>
-        <v>101.2396694214876</v>
+        <v>1212.8712871287128</v>
       </c>
       <c r="J14" s="79" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K14" s="86">
         <f>K11/K12*1000</f>
-        <v>69.421487603305778</v>
+        <v>756.07560756075623</v>
       </c>
       <c r="M14" s="70" t="str">
         <f>C22</f>
@@ -15468,11 +15680,11 @@
       <c r="J15" s="81"/>
       <c r="K15" s="82"/>
       <c r="M15" s="79" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="N15" s="83">
         <f>1/2/PI()/(N12+N13)/N14/10^-6</f>
-        <v>1.5407061286727528</v>
+        <v>37.098198135890676</v>
       </c>
       <c r="P15" s="71"/>
       <c r="Q15" s="72"/>
@@ -15502,7 +15714,7 @@
       </c>
       <c r="D17" s="2" t="str">
         <f>HMI!O4</f>
-        <v>1.1kΩ, 2012m</v>
+        <v>1kΩ, 2012m</v>
       </c>
       <c r="E17" s="65"/>
       <c r="G17" s="75"/>
@@ -15519,7 +15731,7 @@
       </c>
       <c r="D18" s="2">
         <f>_xlfn.XLOOKUP(D17, DB_R[Description], DB_R[R (Ω)])</f>
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E18" s="63"/>
       <c r="J18" s="71"/>
@@ -15550,11 +15762,11 @@
       <c r="E19" s="64"/>
       <c r="G19" s="68" t="str">
         <f>G6</f>
-        <v>Rv1 (Ω)</v>
+        <v>Rv1 (kΩ)</v>
       </c>
       <c r="H19" s="69">
         <f>H6</f>
-        <v>11000</v>
+        <v>10</v>
       </c>
       <c r="J19" s="75"/>
       <c r="K19" s="76"/>
@@ -15572,7 +15784,7 @@
     <row r="20" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="63"/>
       <c r="C20" s="36" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D20" s="2">
         <f>_xlfn.XLOOKUP(D19, DB_R[Description], DB_R[R (Ω)])</f>
@@ -15585,7 +15797,7 @@
       </c>
       <c r="H20" s="61">
         <f>D18</f>
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="M20" s="68" t="str">
         <f>C22</f>
@@ -15609,7 +15821,7 @@
     <row r="21" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B21" s="63"/>
       <c r="C21" s="91" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D21" s="92"/>
       <c r="E21" s="65"/>
@@ -15627,7 +15839,7 @@
       </c>
       <c r="K21" s="77">
         <f>H23</f>
-        <v>3.1818181818181817</v>
+        <v>34.653465346534652</v>
       </c>
       <c r="M21" s="70" t="str">
         <f>C23</f>
@@ -15676,7 +15888,7 @@
         <v>3.3</v>
       </c>
       <c r="M22" s="87" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N22" s="88">
         <f>N20*(1-N21%)</f>
@@ -15705,11 +15917,11 @@
       </c>
       <c r="E23" s="65"/>
       <c r="G23" s="73" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H23" s="74">
         <f>H20*H21/(H20+H19)</f>
-        <v>3.1818181818181817</v>
+        <v>34.653465346534652</v>
       </c>
       <c r="J23" s="70" t="str">
         <f>C10</f>
@@ -15744,11 +15956,11 @@
       </c>
       <c r="E24" s="65"/>
       <c r="G24" s="79" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H24" s="80">
         <f>H20*H22/(H20+H19)</f>
-        <v>2.290909090909091</v>
+        <v>24.950495049504955</v>
       </c>
       <c r="J24" s="70" t="str">
         <f>C5</f>
@@ -15785,11 +15997,11 @@
       <c r="G25" s="81"/>
       <c r="H25" s="82"/>
       <c r="J25" s="79" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K25" s="83">
         <f>K22/K21/(2^K23-1)*K24*1000</f>
-        <v>142.35294117647058</v>
+        <v>13.070588235294117</v>
       </c>
       <c r="T25" s="104"/>
       <c r="U25" s="104"/>
@@ -15832,8 +16044,8 @@
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B27" s="63"/>
-      <c r="C27" s="124"/>
-      <c r="D27" s="124"/>
+      <c r="C27" s="129"/>
+      <c r="D27" s="129"/>
       <c r="E27" s="63"/>
       <c r="G27" s="71"/>
       <c r="H27" s="72"/>
@@ -15845,7 +16057,7 @@
       </c>
       <c r="N27" s="85">
         <f>N12</f>
-        <v>1000</v>
+        <v>9.9009900990099009</v>
       </c>
       <c r="T27" s="104"/>
       <c r="U27" s="104"/>
@@ -15912,11 +16124,11 @@
       <c r="B30" s="63"/>
       <c r="E30" s="63"/>
       <c r="M30" s="79" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N30" s="83">
         <f>N26*(N27+N28)*N29*10^-3</f>
-        <v>309.90000000000003</v>
+        <v>12.870297029702972</v>
       </c>
       <c r="T30" s="104"/>
       <c r="U30" s="104"/>
@@ -16133,10 +16345,10 @@
         <v>125</v>
       </c>
       <c r="K1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="L1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M1" t="s">
         <v>193</v>

--- a/resources/Kururugi-ESC-calculs.xlsx
+++ b/resources/Kururugi-ESC-calculs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\binon\Desktop\Kururugi-ESC-Dev-Board\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381F6C64-3C13-487D-86FE-7704AF7E3525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12BFBB8-41B2-4D3F-997D-FD9DE4FA52C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5775" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="783" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
   </bookViews>
@@ -33,7 +33,6 @@
     <definedName name="Radc">HMI!$U$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -54,7 +53,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -76,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="331">
   <si>
     <t>R1 (kOhm)</t>
   </si>
@@ -1213,8 +1212,23 @@
     <t>Prboot (mW)</t>
   </si>
   <si>
+    <t>Expected derating max (%)</t>
+  </si>
+  <si>
+    <t>Expected derating min (%)</t>
+  </si>
+  <si>
+    <t>Termistors</t>
+  </si>
+  <si>
+    <t>3 (one at each FET)</t>
+  </si>
+  <si>
+    <t>1 (at a FET)</t>
+  </si>
+  <si>
     <r>
-      <t>Rv1,th (k</t>
+      <t>Rv1 (</t>
     </r>
     <r>
       <rPr>
@@ -1228,7 +1242,7 @@
   </si>
   <si>
     <r>
-      <t>Rv1 (k</t>
+      <t>Rv1,th (</t>
     </r>
     <r>
       <rPr>
@@ -1862,7 +1876,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2074,50 +2088,16 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2142,38 +2122,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2194,71 +2146,8 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2304,13 +2193,6 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2318,7 +2200,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2355,6 +2352,9 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="167" formatCode="0.0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -2380,9 +2380,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2748,9 +2745,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>219086</xdr:colOff>
+      <xdr:colOff>215910</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>66140</xdr:rowOff>
+      <xdr:rowOff>69314</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3022,9 +3019,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>558801</xdr:colOff>
+      <xdr:colOff>561976</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>104923</xdr:rowOff>
+      <xdr:rowOff>101748</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3071,7 +3068,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>92505</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>104774</xdr:rowOff>
+      <xdr:rowOff>107949</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3168,9 +3165,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>486343</xdr:colOff>
+      <xdr:colOff>483168</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>104776</xdr:rowOff>
+      <xdr:rowOff>101601</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3216,7 +3213,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>273050</xdr:colOff>
+      <xdr:colOff>276225</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>151810</xdr:rowOff>
     </xdr:to>
@@ -3263,9 +3260,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>349250</xdr:colOff>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>124584</xdr:rowOff>
+      <xdr:rowOff>121409</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3310,7 +3307,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
+      <xdr:colOff>447675</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>55676</xdr:rowOff>
     </xdr:to>
@@ -3357,9 +3354,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>139700</xdr:colOff>
+      <xdr:colOff>142875</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>86411</xdr:rowOff>
+      <xdr:rowOff>83236</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3404,9 +3401,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>349251</xdr:colOff>
+      <xdr:colOff>352426</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>102713</xdr:rowOff>
+      <xdr:rowOff>105888</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3451,7 +3448,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>730250</xdr:colOff>
+      <xdr:colOff>733425</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>114715</xdr:rowOff>
     </xdr:to>
@@ -3489,22 +3486,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>107949</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>73148</xdr:rowOff>
+      <xdr:colOff>159800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>31749</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>134392</xdr:rowOff>
+      <xdr:colOff>615950</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>160120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 16">
+        <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AA81600-FE23-4F27-A0CC-5E9F86FF4C33}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F515383-F3AE-280A-2BD9-D0BAC00E6052}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3513,15 +3510,20 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10804524" y="3273548"/>
-          <a:ext cx="2416176" cy="251744"/>
+          <a:off x="10894475" y="3232149"/>
+          <a:ext cx="2230975" cy="322046"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3533,22 +3535,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>438151</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>114162</xdr:rowOff>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>46089</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>324664</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>101738</xdr:rowOff>
+      <xdr:colOff>712328</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>111339</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 21">
+        <xdr:cNvPr id="8" name="Picture 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5258B494-FA3B-6143-8BD9-E71623EEA89C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4329D55-4ACC-E6DB-7D60-DFECA17AD8B9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3557,20 +3559,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11134726" y="4638537"/>
-          <a:ext cx="1658163" cy="359051"/>
+          <a:off x="11115674" y="4570464"/>
+          <a:ext cx="2293479" cy="436725"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4762,7 +4759,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>263526</xdr:colOff>
+      <xdr:colOff>393141</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>96445</xdr:rowOff>
     </xdr:to>
@@ -4809,7 +4806,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>179978</xdr:colOff>
+      <xdr:colOff>183153</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>114665</xdr:rowOff>
     </xdr:to>
@@ -4861,7 +4858,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>158752</xdr:colOff>
+      <xdr:colOff>275667</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>117081</xdr:rowOff>
     </xdr:to>
@@ -4909,9 +4906,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>387350</xdr:colOff>
+      <xdr:colOff>390525</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>82667</xdr:rowOff>
+      <xdr:rowOff>85842</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4961,9 +4958,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>361951</xdr:colOff>
+      <xdr:colOff>488391</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>47508</xdr:rowOff>
+      <xdr:rowOff>50683</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5008,9 +5005,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>120650</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>50267</xdr:rowOff>
+      <xdr:rowOff>47092</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5055,7 +5052,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>56365</xdr:rowOff>
     </xdr:to>
@@ -5107,9 +5104,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1285701</xdr:colOff>
+      <xdr:colOff>1288876</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>88713</xdr:rowOff>
+      <xdr:rowOff>85538</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5154,7 +5151,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1131523</xdr:colOff>
+      <xdr:colOff>1134698</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>94549</xdr:rowOff>
     </xdr:to>
@@ -5202,9 +5199,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>869765</xdr:colOff>
+      <xdr:colOff>866590</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>162544</xdr:rowOff>
+      <xdr:rowOff>159369</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5248,7 +5245,7 @@
       <xdr:col>13</xdr:col>
       <xdr:colOff>669881</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>85352</xdr:rowOff>
+      <xdr:rowOff>88527</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5290,9 +5287,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>619551</xdr:colOff>
+      <xdr:colOff>616376</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>86472</xdr:rowOff>
+      <xdr:rowOff>83297</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5334,7 +5331,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>616884</xdr:colOff>
+      <xdr:colOff>620059</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>97437</xdr:rowOff>
     </xdr:to>
@@ -5427,9 +5424,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>1116294</xdr:colOff>
+      <xdr:colOff>1113119</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>107010</xdr:rowOff>
+      <xdr:rowOff>103835</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5699,15 +5696,15 @@
     <tableColumn id="17" xr3:uid="{8828BB6B-7ABC-4BA6-9E1B-5C5BE5105F08}" name="Iph typ (A)"/>
     <tableColumn id="18" xr3:uid="{1F68324A-F399-4C91-BE2D-EFEF49ED6790}" name="ToF Iph typ (%)"/>
     <tableColumn id="15" xr3:uid="{5ED528D3-58D8-4741-86F9-6B25ECFBAFAE}" name="Iph max (A@Xs)"/>
-    <tableColumn id="19" xr3:uid="{305A20A8-F4F6-4F6B-BAC2-2A71E7628C5B}" name="ToF Iph max (%)" dataDxfId="12">
+    <tableColumn id="19" xr3:uid="{305A20A8-F4F6-4F6B-BAC2-2A71E7628C5B}" name="ToF Iph max (%)" dataDxfId="14">
       <calculatedColumnFormula>100-DB_limits[[#This Row],[ToF Iph typ (%)]]-DB_limits[[#This Row],[ToF Iph spike (%)]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" xr3:uid="{4D711E23-0E80-41C8-A566-2B43E0C79E4C}" name="Iph spike (A@Xms)"/>
     <tableColumn id="20" xr3:uid="{0DE3AE78-D822-41D8-B4E1-38C2CE21BE19}" name="ToF Iph spike (%)"/>
-    <tableColumn id="21" xr3:uid="{0DD4A4A7-CFA4-4B62-89A9-A58896065868}" name="Iph mean (A)" dataDxfId="11">
+    <tableColumn id="21" xr3:uid="{0DD4A4A7-CFA4-4B62-89A9-A58896065868}" name="Iph mean (A)" dataDxfId="13">
       <calculatedColumnFormula>DB_limits[[#This Row],[Iph typ (A)]]*DB_limits[[#This Row],[ToF Iph typ (%)]]%+DB_limits[[#This Row],[Iph max (A@Xs)]]*DB_limits[[#This Row],[ToF Iph max (%)]]%+DB_limits[[#This Row],[Iph spike (A@Xms)]]*DB_limits[[#This Row],[ToF Iph spike (%)]]%</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{47619F70-8E0D-4CA7-A6D9-A367CF759D25}" name="t_blank@V_sw=0 (ns)"/>
+    <tableColumn id="24" xr3:uid="{47619F70-8E0D-4CA7-A6D9-A367CF759D25}" name="Termistors"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5738,16 +5735,16 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{63D060DC-1A0E-4C6B-B8ED-355A99E0726F}" name="DB_R" displayName="DB_R" ref="A1:H97" totalsRowShown="0">
   <autoFilter ref="A1:H97" xr:uid="{63D060DC-1A0E-4C6B-B8ED-355A99E0726F}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{DBB93FE2-51C5-454A-AC99-D8757287ABB9}" name="Description" dataDxfId="4">
+    <tableColumn id="1" xr3:uid="{DBB93FE2-51C5-454A-AC99-D8757287ABB9}" name="Description" dataDxfId="12">
       <calculatedColumnFormula>IF(B2&gt;=1000,C2&amp; "kΩ, ",B2&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{AF373A17-D484-41B5-BED8-19D683DD5125}" name="R (Ω)"/>
-    <tableColumn id="8" xr3:uid="{E1D5325B-C0E2-4318-8B8F-5A97FC83BDE8}" name="R (kΩ)" dataDxfId="10">
+    <tableColumn id="8" xr3:uid="{E1D5325B-C0E2-4318-8B8F-5A97FC83BDE8}" name="R (kΩ)" dataDxfId="11">
       <calculatedColumnFormula>DB_R[[#This Row],[R (Ω)]]/1000</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{1869FA9B-CD3D-4490-9D7D-AF79F51E8B42}" name="Prated@70°C (W)"/>
-    <tableColumn id="4" xr3:uid="{FFB77188-A967-4E66-B819-72B42AD6014E}" name="Package (inch)" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{E4155B5D-359A-41BB-92C6-28261E84BA95}" name="Package (m)" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{FFB77188-A967-4E66-B819-72B42AD6014E}" name="Package (inch)" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{E4155B5D-359A-41BB-92C6-28261E84BA95}" name="Package (m)" dataDxfId="9"/>
     <tableColumn id="6" xr3:uid="{36F66B56-514C-403F-A857-E620F0D85ADB}" name="Name"/>
     <tableColumn id="7" xr3:uid="{C45470D4-A248-41F0-8FEA-BCC9DDBB36BB}" name="Basic"/>
   </tableColumns>
@@ -5777,11 +5774,11 @@
     <tableColumn id="5" xr3:uid="{9E36CA0A-030E-45D6-80B5-44EACE4CF9C1}" name="Rds,on@10V max (mΩ)"/>
     <tableColumn id="3" xr3:uid="{B36DB100-BC6C-4604-AFA9-893484874261}" name="Qg,typ @ 10V (nC)"/>
     <tableColumn id="18" xr3:uid="{AE11D89E-7D09-439D-A957-B257CDAE4013}" name="Qg,max @ 10V (nC)"/>
-    <tableColumn id="19" xr3:uid="{55C0F480-C3C0-4174-A4E9-9924DC4E5206}" name="Qg,typ,sync @ 10V (nC)" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{55C0F480-C3C0-4174-A4E9-9924DC4E5206}" name="Qg,typ,sync @ 10V (nC)" dataDxfId="8"/>
     <tableColumn id="11" xr3:uid="{EFF1EF6B-1B94-4403-96A6-8F379D253341}" name="Id @ Tc=25°C (A)"/>
     <tableColumn id="12" xr3:uid="{2CF664C6-5A37-4198-A82C-CB83562A34CE}" name="Id @ Tc&gt;70°C (A)"/>
-    <tableColumn id="15" xr3:uid="{5F19FBAC-6ADA-4394-8342-979B1F1DEDE7}" name="Id @ Ta=25°C (A)" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{6F591E39-1B6D-4062-9BE0-8B0277C5FCF7}" name="Id @ Ta&gt;70°C (A)" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{5F19FBAC-6ADA-4394-8342-979B1F1DEDE7}" name="Id @ Ta=25°C (A)" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{6F591E39-1B6D-4062-9BE0-8B0277C5FCF7}" name="Id @ Ta&gt;70°C (A)" dataDxfId="6"/>
     <tableColumn id="13" xr3:uid="{C7A711FC-0D57-4B8A-BB26-68DC361E005C}" name="Id,pulsed (A)"/>
     <tableColumn id="6" xr3:uid="{444A3D52-40D0-416F-A1B0-B9B0EB9CB918}" name="Rise time (ns)"/>
     <tableColumn id="7" xr3:uid="{0FF757B6-A521-4328-92D2-DC9B4DD9039B}" name="Fall time (ns)"/>
@@ -5806,8 +5803,8 @@
     </tableColumn>
     <tableColumn id="6" xr3:uid="{024B3B03-8354-4E20-8FDB-FEE3DD0DAC7D}" name="Csamp (pF)"/>
     <tableColumn id="8" xr3:uid="{F84DCCD2-D0FF-4366-93FF-50FA1CA3EF44}" name="Cpad (pF)"/>
-    <tableColumn id="7" xr3:uid="{71EAE56C-7786-4272-AB14-E79BB1020D87}" name="Fadc,clock(MHz)" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{F391904B-0620-4A43-9BB6-C6F0F8B772B8}" name="Tadc,clock (ns)" dataDxfId="13">
+    <tableColumn id="7" xr3:uid="{71EAE56C-7786-4272-AB14-E79BB1020D87}" name="Fadc,clock(MHz)" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{F391904B-0620-4A43-9BB6-C6F0F8B772B8}" name="Tadc,clock (ns)" dataDxfId="4">
       <calculatedColumnFormula>1/DB_ADC[[#This Row],[Fadc,clock(MHz)]]*10^3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{8C0FDEEA-51B2-409A-B9CA-F54F7CAFA2AC}" name="Vin,max@vin (V)">
@@ -6138,14 +6135,14 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B1:U41"/>
+  <dimension ref="B1:U42"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.1796875" style="67" customWidth="1"/>
     <col min="2" max="2" width="28.6328125" style="67" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" style="67" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.1796875" style="67" customWidth="1"/>
-    <col min="5" max="5" width="20.453125" style="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.453125" style="67" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.90625" style="67" customWidth="1"/>
     <col min="7" max="7" width="3.1796875" style="67" customWidth="1"/>
     <col min="8" max="8" width="28.6328125" style="67" bestFit="1" customWidth="1"/>
@@ -6164,87 +6161,85 @@
   <sheetData>
     <row r="1" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B2" s="156" t="s">
+      <c r="B2" s="147" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="157"/>
-      <c r="E2" s="156" t="s">
+      <c r="C2" s="148"/>
+      <c r="E2" s="147" t="s">
         <v>145</v>
       </c>
-      <c r="F2" s="157"/>
-      <c r="H2" s="156" t="s">
+      <c r="F2" s="148"/>
+      <c r="H2" s="147" t="s">
         <v>102</v>
       </c>
-      <c r="I2" s="157"/>
-      <c r="K2" s="156" t="s">
+      <c r="I2" s="148"/>
+      <c r="K2" s="147" t="s">
         <v>226</v>
       </c>
-      <c r="L2" s="157"/>
-      <c r="N2" s="156" t="s">
+      <c r="L2" s="148"/>
+      <c r="N2" s="147" t="s">
         <v>256</v>
       </c>
-      <c r="O2" s="157"/>
-      <c r="Q2" s="149"/>
-      <c r="R2" s="149"/>
-      <c r="T2" s="153"/>
-      <c r="U2" s="153"/>
+      <c r="O2" s="148"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="T2" s="150"/>
+      <c r="U2" s="150"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B3" s="158" t="s">
+      <c r="B3" s="145" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="101" t="s">
+      <c r="C3" s="146"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="152" t="s">
         <v>204</v>
       </c>
-      <c r="F3" s="102"/>
-      <c r="H3" s="158" t="s">
+      <c r="F3" s="153"/>
+      <c r="H3" s="145" t="s">
         <v>202</v>
       </c>
-      <c r="I3" s="159"/>
-      <c r="K3" s="158" t="s">
+      <c r="I3" s="146"/>
+      <c r="K3" s="145" t="s">
         <v>131</v>
       </c>
-      <c r="L3" s="159"/>
-      <c r="N3" s="158" t="s">
+      <c r="L3" s="146"/>
+      <c r="N3" s="145" t="s">
         <v>131</v>
       </c>
-      <c r="O3" s="159"/>
-      <c r="Q3" s="148"/>
-      <c r="R3" s="148"/>
+      <c r="O3" s="146"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="115"/>
       <c r="T3" s="151"/>
       <c r="U3" s="151"/>
     </row>
     <row r="4" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="160" t="s">
+      <c r="B4" s="143" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="161"/>
-      <c r="E4" s="158" t="s">
+      <c r="C4" s="144"/>
+      <c r="E4" s="145" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="159"/>
-      <c r="H4" s="160" t="s">
+      <c r="F4" s="146"/>
+      <c r="H4" s="143" t="s">
         <v>203</v>
       </c>
-      <c r="I4" s="161"/>
-      <c r="K4" s="165" t="s">
+      <c r="I4" s="144"/>
+      <c r="K4" s="120" t="s">
         <v>243</v>
       </c>
-      <c r="L4" s="166">
+      <c r="L4" s="121">
         <v>850</v>
       </c>
-      <c r="N4" s="164" t="s">
+      <c r="N4" s="119" t="s">
         <v>265</v>
       </c>
       <c r="O4" s="61" t="s">
         <v>297</v>
       </c>
-      <c r="Q4" s="154"/>
-      <c r="R4" s="154"/>
-      <c r="T4" s="155"/>
-      <c r="U4" s="155"/>
+      <c r="T4" s="149"/>
+      <c r="U4" s="149"/>
     </row>
     <row r="5" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B5" s="70" t="str">
@@ -6255,10 +6250,10 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Frame size (")])</f>
         <v>6</v>
       </c>
-      <c r="E5" s="165" t="s">
+      <c r="E5" s="120" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="166">
+      <c r="F5" s="121">
         <v>10.5</v>
       </c>
       <c r="H5" s="70" t="str">
@@ -6269,8 +6264,6 @@
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Vds (V)])</f>
         <v>60</v>
       </c>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
       <c r="N5" s="70" t="str">
         <f>DB_R[[#Headers],[Prated@70°C (W)]]</f>
         <v>Prated@70°C (W)</v>
@@ -6279,8 +6272,8 @@
         <f>_xlfn.XLOOKUP(O4, DB_R[Description], DB_R[Prated@70°C (W)])</f>
         <v>0.25</v>
       </c>
-      <c r="R5" s="147"/>
-      <c r="U5" s="147"/>
+      <c r="R5" s="95"/>
+      <c r="U5" s="95"/>
     </row>
     <row r="6" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="70" t="str">
@@ -6295,22 +6288,22 @@
         <f>DB_Mostfet[[#Headers],[Qg,typ @ 10V (nC)]]</f>
         <v>Qg,typ @ 10V (nC)</v>
       </c>
-      <c r="I6" s="167">
+      <c r="I6" s="122">
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Qg,typ @ 10V (nC)])</f>
         <v>41</v>
       </c>
-      <c r="K6" s="169" t="s">
+      <c r="K6" s="139" t="s">
         <v>140</v>
       </c>
-      <c r="L6" s="170"/>
-      <c r="N6" s="164" t="s">
+      <c r="L6" s="140"/>
+      <c r="N6" s="119" t="s">
         <v>285</v>
       </c>
       <c r="O6" s="61" t="s">
         <v>278</v>
       </c>
-      <c r="R6" s="147"/>
-      <c r="U6" s="147"/>
+      <c r="R6" s="95"/>
+      <c r="U6" s="95"/>
     </row>
     <row r="7" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="70" t="str">
@@ -6321,10 +6314,10 @@
         <f>_xlfn.XLOOKUP(B4,DB_limits[Name],DB_limits[Fmax (kHz)])</f>
         <v>64</v>
       </c>
-      <c r="E7" s="156" t="s">
+      <c r="E7" s="147" t="s">
         <v>225</v>
       </c>
-      <c r="F7" s="157"/>
+      <c r="F7" s="148"/>
       <c r="H7" s="70" t="str">
         <f>DB_Mostfet[[#Headers],[Qg,typ,sync @ 10V (nC)]] &amp;  " (not used)"</f>
         <v>Qg,typ,sync @ 10V (nC) (not used)</v>
@@ -6333,20 +6326,20 @@
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Qg,typ,sync @ 10V (nC)])</f>
         <v>X</v>
       </c>
-      <c r="K7" s="162" t="s">
+      <c r="K7" s="141" t="s">
         <v>113</v>
       </c>
-      <c r="L7" s="163"/>
-      <c r="N7" s="168" t="str">
+      <c r="L7" s="142"/>
+      <c r="N7" s="123" t="str">
         <f>N5</f>
         <v>Prated@70°C (W)</v>
       </c>
-      <c r="O7" s="166">
+      <c r="O7" s="121">
         <f>_xlfn.XLOOKUP(O4, DB_R[Description], DB_R[Prated@70°C (W)])</f>
         <v>0.25</v>
       </c>
-      <c r="R7" s="147"/>
-      <c r="U7" s="147"/>
+      <c r="R7" s="95"/>
+      <c r="U7" s="95"/>
     </row>
     <row r="8" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="70" t="str">
@@ -6357,10 +6350,10 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Vbat,min (V)])</f>
         <v>14</v>
       </c>
-      <c r="E8" s="99" t="s">
+      <c r="E8" s="154" t="s">
         <v>207</v>
       </c>
-      <c r="F8" s="100"/>
+      <c r="F8" s="155"/>
       <c r="H8" s="70" t="str">
         <f>DB_Mostfet[[#Headers],[Rds,on@10V typ(mΩ)]] &amp;  " (not used)"</f>
         <v>Rds,on@10V typ(mΩ) (not used)</v>
@@ -6369,14 +6362,12 @@
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Rds,on@10V typ(mΩ)])</f>
         <v>1.8</v>
       </c>
-      <c r="K8" s="160" t="s">
+      <c r="K8" s="143" t="s">
         <v>132</v>
       </c>
-      <c r="L8" s="161"/>
-      <c r="N8" s="104"/>
-      <c r="O8" s="104"/>
-      <c r="R8" s="147"/>
-      <c r="U8" s="147"/>
+      <c r="L8" s="144"/>
+      <c r="R8" s="95"/>
+      <c r="U8" s="95"/>
     </row>
     <row r="9" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="70" t="str">
@@ -6391,7 +6382,7 @@
         <f>DB_Mostfet[[#Headers],[Rds,on@10V max (mΩ)]]</f>
         <v>Rds,on@10V max (mΩ)</v>
       </c>
-      <c r="I9" s="167">
+      <c r="I9" s="122">
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Rds,on@10V max (mΩ)])</f>
         <v>2.2000000000000002</v>
       </c>
@@ -6403,14 +6394,14 @@
         <f>_xlfn.XLOOKUP($K$8, DB_ADC[Name], DB_ADC[Vmax (V)])</f>
         <v>3.5999999999999996</v>
       </c>
-      <c r="N9" s="169" t="s">
+      <c r="N9" s="139" t="s">
         <v>254</v>
       </c>
-      <c r="O9" s="170"/>
-      <c r="Q9" s="148"/>
-      <c r="R9" s="148"/>
-      <c r="T9" s="148"/>
-      <c r="U9" s="148"/>
+      <c r="O9" s="140"/>
+      <c r="Q9" s="115"/>
+      <c r="R9" s="115"/>
+      <c r="T9" s="115"/>
+      <c r="U9" s="115"/>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B10" s="70" t="str">
@@ -6421,10 +6412,10 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Vbat spike (V) @ run])</f>
         <v>32</v>
       </c>
-      <c r="E10" s="169" t="s">
+      <c r="E10" s="139" t="s">
         <v>216</v>
       </c>
-      <c r="F10" s="170"/>
+      <c r="F10" s="140"/>
       <c r="H10" s="70" t="str">
         <f>DB_Mostfet[[#Headers],[Id @ Tc&gt;70°C (A)]]</f>
         <v>Id @ Tc&gt;70°C (A)</v>
@@ -6433,16 +6424,16 @@
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Id @ Tc&gt;70°C (A)])</f>
         <v>100</v>
       </c>
-      <c r="K10" s="162" t="s">
+      <c r="K10" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="L10" s="163"/>
-      <c r="N10" s="162" t="s">
+      <c r="L10" s="142"/>
+      <c r="N10" s="141" t="s">
         <v>113</v>
       </c>
-      <c r="O10" s="163"/>
-      <c r="R10" s="147"/>
-      <c r="U10" s="147"/>
+      <c r="O10" s="142"/>
+      <c r="R10" s="95"/>
+      <c r="U10" s="95"/>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B11" s="70" t="str">
@@ -6453,30 +6444,30 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Vbat spike (V) @ disarm])</f>
         <v>45</v>
       </c>
-      <c r="E11" s="162" t="s">
+      <c r="E11" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="F11" s="163"/>
+      <c r="F11" s="142"/>
       <c r="H11" s="70" t="str">
         <f>DB_Mostfet[[#Headers],[Id @ Ta&gt;70°C (A)]]</f>
         <v>Id @ Ta&gt;70°C (A)</v>
       </c>
-      <c r="I11" s="167" t="str">
+      <c r="I11" s="122" t="str">
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Id @ Ta&gt;70°C (A)])</f>
         <v>(est ~21A)</v>
       </c>
-      <c r="K11" s="164" t="s">
+      <c r="K11" s="119" t="s">
         <v>127</v>
       </c>
       <c r="L11" s="61">
         <v>12</v>
       </c>
-      <c r="N11" s="101" t="s">
+      <c r="N11" s="152" t="s">
         <v>132</v>
       </c>
-      <c r="O11" s="102"/>
-      <c r="R11" s="147"/>
-      <c r="U11" s="147"/>
+      <c r="O11" s="153"/>
+      <c r="R11" s="95"/>
+      <c r="U11" s="95"/>
     </row>
     <row r="12" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="70" t="str">
@@ -6487,10 +6478,10 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Vph spike (V) @ run])</f>
         <v>35</v>
       </c>
-      <c r="E12" s="165" t="s">
+      <c r="E12" s="120" t="s">
         <v>228</v>
       </c>
-      <c r="F12" s="166">
+      <c r="F12" s="121">
         <v>10</v>
       </c>
       <c r="H12" s="70" t="str">
@@ -6501,7 +6492,7 @@
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[Size (mm)])</f>
         <v>5x6</v>
       </c>
-      <c r="K12" s="164" t="s">
+      <c r="K12" s="119" t="s">
         <v>283</v>
       </c>
       <c r="L12" s="61">
@@ -6515,9 +6506,9 @@
         <f>_xlfn.XLOOKUP($N$11, DB_ADC[Name], DB_ADC[Csamp (pF)])</f>
         <v>5</v>
       </c>
-      <c r="R12" s="147"/>
-      <c r="T12" s="148"/>
-      <c r="U12" s="148"/>
+      <c r="R12" s="95"/>
+      <c r="T12" s="115"/>
+      <c r="U12" s="115"/>
     </row>
     <row r="13" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="70" t="str">
@@ -6528,7 +6519,7 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Vph spike (V) @ disarm])</f>
         <v>28</v>
       </c>
-      <c r="F13" s="146"/>
+      <c r="F13" s="94"/>
       <c r="H13" s="70" t="str">
         <f>DB_Mostfet[[#Headers],[JLCPBC stock]]</f>
         <v>JLCPBC stock</v>
@@ -6537,7 +6528,7 @@
         <f>_xlfn.XLOOKUP(H4, DB_Mostfet[Part], DB_Mostfet[JLCPBC stock])</f>
         <v>Yes</v>
       </c>
-      <c r="K13" s="164" t="s">
+      <c r="K13" s="119" t="s">
         <v>141</v>
       </c>
       <c r="L13" s="61">
@@ -6551,9 +6542,9 @@
         <f>_xlfn.XLOOKUP($N$11, DB_ADC[Name], DB_ADC[Cpad (pF)])</f>
         <v>5</v>
       </c>
-      <c r="Q13" s="148"/>
-      <c r="R13" s="148"/>
-      <c r="U13" s="144"/>
+      <c r="Q13" s="115"/>
+      <c r="R13" s="115"/>
+      <c r="U13" s="96"/>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B14" s="70" t="str">
@@ -6564,23 +6555,23 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Iph typ (A)])</f>
         <v>12.5</v>
       </c>
-      <c r="E14" s="169" t="s">
+      <c r="E14" s="139" t="s">
         <v>253</v>
       </c>
-      <c r="F14" s="170"/>
-      <c r="H14" s="158" t="s">
+      <c r="F14" s="140"/>
+      <c r="H14" s="145" t="s">
         <v>130</v>
       </c>
-      <c r="I14" s="159"/>
-      <c r="K14" s="162" t="s">
+      <c r="I14" s="146"/>
+      <c r="K14" s="141" t="s">
         <v>130</v>
       </c>
-      <c r="L14" s="163"/>
-      <c r="N14" s="162" t="s">
+      <c r="L14" s="142"/>
+      <c r="N14" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="O14" s="163"/>
-      <c r="R14" s="144"/>
+      <c r="O14" s="142"/>
+      <c r="R14" s="96"/>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B15" s="70" t="str">
@@ -6591,15 +6582,15 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Iph max (A@Xs)])</f>
         <v>20</v>
       </c>
-      <c r="E15" s="162" t="s">
+      <c r="E15" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="F15" s="163"/>
-      <c r="H15" s="181" t="str">
+      <c r="F15" s="142"/>
+      <c r="H15" s="73" t="str">
         <f>CAL_Fets!G28</f>
         <v>Ptot,typ (mW)</v>
       </c>
-      <c r="I15" s="182">
+      <c r="I15" s="74">
         <f>CAL_Fets!H28</f>
         <v>1667.2220807894741</v>
       </c>
@@ -6610,14 +6601,14 @@
         <f>(L11+L12+0.5)*_xlfn.XLOOKUP(K8,DB_ADC[Name],DB_ADC[Tadc,clock (ns)])</f>
         <v>250.00000000000003</v>
       </c>
-      <c r="N15" s="164" t="s">
+      <c r="N15" s="119" t="s">
         <v>127</v>
       </c>
       <c r="O15" s="61">
         <v>8</v>
       </c>
-      <c r="T15" s="149"/>
-      <c r="U15" s="149"/>
+      <c r="T15" s="116"/>
+      <c r="U15" s="116"/>
     </row>
     <row r="16" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="70" t="str">
@@ -6628,38 +6619,38 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Iph spike (A@Xms)])</f>
         <v>50</v>
       </c>
-      <c r="E16" s="184" t="s">
-        <v>214</v>
-      </c>
-      <c r="F16" s="186">
+      <c r="E16" s="136" t="s">
+        <v>324</v>
+      </c>
+      <c r="F16" s="138">
         <v>60</v>
       </c>
-      <c r="H16" s="173" t="str">
+      <c r="H16" s="128" t="str">
         <f>CAL_Fets!G29</f>
         <v>Ptot,max (mW)</v>
       </c>
-      <c r="I16" s="174">
+      <c r="I16" s="129">
         <f>CAL_Fets!H29</f>
         <v>3145.7629473684219</v>
       </c>
-      <c r="K16" s="171" t="str">
+      <c r="K16" s="126" t="str">
         <f>CAL_Rshunt!G22</f>
         <v>Vshunt,amp,spike (V)</v>
       </c>
-      <c r="L16" s="175">
+      <c r="L16" s="130">
         <f>CAL_Rshunt!H22</f>
         <v>2.72</v>
       </c>
-      <c r="N16" s="164" t="s">
+      <c r="N16" s="119" t="s">
         <v>283</v>
       </c>
       <c r="O16" s="61">
         <v>2.5</v>
       </c>
-      <c r="Q16" s="150"/>
-      <c r="R16" s="150"/>
-      <c r="T16" s="148"/>
-      <c r="U16" s="148"/>
+      <c r="Q16" s="108"/>
+      <c r="R16" s="108"/>
+      <c r="T16" s="115"/>
+      <c r="U16" s="115"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B17" s="70" t="str">
@@ -6670,40 +6661,44 @@
         <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Iph mean (A)])</f>
         <v>12.905000000000001</v>
       </c>
-      <c r="E17" s="184" t="s">
-        <v>239</v>
-      </c>
-      <c r="F17" s="185">
-        <v>3</v>
-      </c>
-      <c r="K17" s="171" t="str">
+      <c r="E17" s="136" t="s">
+        <v>325</v>
+      </c>
+      <c r="F17" s="138">
+        <v>30</v>
+      </c>
+      <c r="K17" s="126" t="str">
         <f>CAL_Rshunt!J6</f>
         <v>ΔIlsb (mA/bit)</v>
       </c>
-      <c r="L17" s="175">
+      <c r="L17" s="130">
         <f>CAL_Rshunt!K6</f>
         <v>14.813617754794226</v>
       </c>
-      <c r="N17" s="177" t="s">
+      <c r="N17" s="132" t="s">
         <v>289</v>
       </c>
-      <c r="O17" s="178">
+      <c r="O17" s="133">
         <v>5</v>
       </c>
-      <c r="Q17" s="148"/>
-      <c r="R17" s="148"/>
-      <c r="U17" s="147"/>
+      <c r="Q17" s="115"/>
+      <c r="R17" s="115"/>
+      <c r="U17" s="95"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B18" s="162" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="163"/>
-      <c r="E18" s="164" t="s">
-        <v>146</v>
-      </c>
-      <c r="F18" s="61">
-        <v>3.3</v>
+      <c r="B18" s="70" t="str">
+        <f>DB_limits[[#Headers],[Termistors]]</f>
+        <v>Termistors</v>
+      </c>
+      <c r="C18" s="78" t="str">
+        <f>_xlfn.XLOOKUP($B$4, DB_limits[Name], DB_limits[Termistors])</f>
+        <v>3 (one at each FET)</v>
+      </c>
+      <c r="E18" s="136" t="s">
+        <v>239</v>
+      </c>
+      <c r="F18" s="137">
+        <v>3</v>
       </c>
       <c r="K18" s="73" t="str">
         <f>CAL_Rshunt!J14</f>
@@ -6713,29 +6708,29 @@
         <f>CAL_Rshunt!K14</f>
         <v>84.934902750000006</v>
       </c>
-      <c r="N18" s="162" t="s">
+      <c r="N18" s="141" t="s">
         <v>130</v>
       </c>
-      <c r="O18" s="163"/>
-      <c r="R18" s="146"/>
-      <c r="U18" s="147"/>
+      <c r="O18" s="142"/>
+      <c r="R18" s="94"/>
+      <c r="U18" s="95"/>
     </row>
     <row r="19" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="164" t="s">
-        <v>139</v>
-      </c>
-      <c r="C19" s="61">
-        <v>480</v>
-      </c>
-      <c r="E19" s="162" t="s">
-        <v>130</v>
-      </c>
-      <c r="F19" s="163"/>
-      <c r="K19" s="173" t="str">
+      <c r="B19" s="141" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="142"/>
+      <c r="E19" s="119" t="s">
+        <v>146</v>
+      </c>
+      <c r="F19" s="61">
+        <v>3.3</v>
+      </c>
+      <c r="K19" s="128" t="str">
         <f>CAL_Rshunt!J22</f>
         <v>Pshunt,max (mW@Xs)</v>
       </c>
-      <c r="L19" s="176">
+      <c r="L19" s="131">
         <f>CAL_Rshunt!K22</f>
         <v>204</v>
       </c>
@@ -6746,63 +6741,65 @@
         <f>(O15+O16+0.5)*_xlfn.XLOOKUP(N11,DB_ADC[Name],DB_ADC[Tadc,clock (ns)])</f>
         <v>183.33333333333334</v>
       </c>
-      <c r="R19" s="145"/>
-      <c r="U19" s="147"/>
-    </row>
-    <row r="20" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="165" t="s">
+      <c r="R19" s="93"/>
+      <c r="U19" s="95"/>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B20" s="119" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" s="61">
+        <v>480</v>
+      </c>
+      <c r="E20" s="117" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" s="118"/>
+      <c r="N20" s="73" t="str">
+        <f>'CAL_Rv1-2'!G5</f>
+        <v>Rv1,th (Ω)</v>
+      </c>
+      <c r="O20" s="74">
+        <f>'CAL_Rv1-2'!H5</f>
+        <v>9606.0606060606078</v>
+      </c>
+      <c r="R20" s="93"/>
+      <c r="U20" s="95"/>
+    </row>
+    <row r="21" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="120" t="s">
         <v>224</v>
       </c>
-      <c r="C20" s="166">
+      <c r="C21" s="121">
         <v>300</v>
       </c>
-      <c r="E20" s="171" t="str">
+      <c r="E21" s="126" t="str">
         <f>CAL_Cboot!G12</f>
         <v>Vboot,min (V)</v>
       </c>
-      <c r="F20" s="172">
+      <c r="F21" s="127">
         <f>CAL_Cboot!H12</f>
         <v>6.74</v>
       </c>
-      <c r="N20" s="73" t="str">
-        <f>'CAL_Rv1-2'!G5</f>
-        <v>Rv1,th (kΩ)</v>
-      </c>
-      <c r="O20" s="74">
-        <f>'CAL_Rv1-2'!H5</f>
-        <v>9.6060606060606073</v>
-      </c>
-      <c r="R20" s="145"/>
-      <c r="U20" s="147"/>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E21" s="171" t="str">
+      <c r="N21" s="73" t="str">
+        <f>'CAL_Rv1-2'!G6</f>
+        <v>Rv1 (Ω)</v>
+      </c>
+      <c r="O21" s="74">
+        <f>'CAL_Rv1-2'!H6</f>
+        <v>10000</v>
+      </c>
+      <c r="R21" s="93"/>
+      <c r="U21" s="95"/>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="E22" s="126" t="str">
         <f>CAL_Cboot!G18</f>
         <v>Vboot,max (V)</v>
       </c>
-      <c r="F21" s="172">
+      <c r="F22" s="127">
         <f>CAL_Cboot!H18</f>
         <v>10.26</v>
-      </c>
-      <c r="N21" s="73" t="str">
-        <f>'CAL_Rv1-2'!G6</f>
-        <v>Rv1 (kΩ)</v>
-      </c>
-      <c r="O21" s="74">
-        <f>'CAL_Rv1-2'!H6</f>
-        <v>10</v>
-      </c>
-      <c r="R21" s="145"/>
-      <c r="U21" s="147"/>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E22" s="73" t="str">
-        <f>CAL_Cboot!M4</f>
-        <v>Cboot,th (nF)</v>
-      </c>
-      <c r="F22" s="85">
-        <f>CAL_Cboot!N4</f>
-        <v>167.44099069148933</v>
       </c>
       <c r="N22" s="73" t="str">
         <f>'CAL_Rv1-2'!G24</f>
@@ -6810,19 +6807,19 @@
       </c>
       <c r="O22" s="74">
         <f>'CAL_Rv1-2'!H24</f>
-        <v>24.950495049504955</v>
-      </c>
-      <c r="R22" s="146"/>
-      <c r="U22" s="147"/>
+        <v>2.2909090909090915</v>
+      </c>
+      <c r="R22" s="94"/>
+      <c r="U22" s="95"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.35">
       <c r="E23" s="73" t="str">
-        <f>CAL_Cboot!M5</f>
-        <v>Cboot (nF)</v>
+        <f>CAL_Cboot!M4</f>
+        <v>Cboot,th (nF)</v>
       </c>
       <c r="F23" s="85">
-        <f>CAL_Cboot!N5</f>
-        <v>180</v>
+        <f>CAL_Cboot!N4</f>
+        <v>167.44099069148933</v>
       </c>
       <c r="N23" s="73" t="str">
         <f>'CAL_Rv1-2'!J5</f>
@@ -6830,154 +6827,154 @@
       </c>
       <c r="O23" s="74">
         <f>'CAL_Rv1-2'!K5</f>
-        <v>24.950495049504951</v>
-      </c>
-      <c r="R23" s="145"/>
+        <v>2.2909090909090915</v>
+      </c>
+      <c r="R23" s="93"/>
       <c r="T23" s="151"/>
       <c r="U23" s="151"/>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.35">
       <c r="E24" s="73" t="str">
-        <f>CAL_Cboot!P24</f>
-        <v>Prboot (mW)</v>
+        <f>CAL_Cboot!M5</f>
+        <v>Cboot (nF)</v>
       </c>
       <c r="F24" s="85">
-        <f>CAL_Cboot!Q24</f>
-        <v>23.654290993548383</v>
-      </c>
-      <c r="N24" s="171" t="str">
+        <f>CAL_Cboot!N5</f>
+        <v>180</v>
+      </c>
+      <c r="N24" s="126" t="str">
         <f>'CAL_Rv1-2'!J25</f>
         <v>ΔVlsb,fullscale (mV/bit)</v>
       </c>
-      <c r="O24" s="172">
+      <c r="O24" s="127">
         <f>'CAL_Rv1-2'!K25</f>
-        <v>13.070588235294117</v>
-      </c>
-      <c r="Q24" s="152"/>
-      <c r="U24" s="146"/>
+        <v>142.35294117647058</v>
+      </c>
+      <c r="Q24" s="115"/>
+      <c r="U24" s="94"/>
     </row>
     <row r="25" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E25" s="73" t="str">
+        <f>CAL_Cboot!P23</f>
+        <v>Prboot (mW)</v>
+      </c>
+      <c r="F25" s="85">
+        <f>CAL_Cboot!Q23</f>
+        <v>49.417752774193538</v>
+      </c>
+      <c r="N25" s="128" t="str">
+        <f>'CAL_Rv1-2'!G14</f>
+        <v>Prv1,rv2 (mW)</v>
+      </c>
+      <c r="O25" s="134">
+        <f>'CAL_Rv1-2'!H14</f>
+        <v>111.36363636363636</v>
+      </c>
+      <c r="U25" s="94"/>
+    </row>
+    <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E26" s="73" t="str">
         <f>CAL_Cboot!M13</f>
         <v>t_recharge (µs)</v>
       </c>
-      <c r="F25" s="78">
+      <c r="F26" s="78">
         <f>CAL_Cboot!N13</f>
         <v>1.2624999999999995</v>
       </c>
-      <c r="N25" s="173" t="str">
-        <f>'CAL_Rv1-2'!G14</f>
-        <v>Prv1,rv2 (mW)</v>
-      </c>
-      <c r="O25" s="179">
-        <f>'CAL_Rv1-2'!H14</f>
-        <v>1212.8712871287128</v>
-      </c>
-      <c r="U25" s="146"/>
-    </row>
-    <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E26" s="173" t="str">
+      <c r="U26" s="94"/>
+    </row>
+    <row r="27" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E27" s="128" t="str">
         <f>CAL_Cboot!P8</f>
         <v>Vboot,max@Dmax (V)</v>
       </c>
-      <c r="F26" s="174">
+      <c r="F27" s="129">
         <f>CAL_Cboot!Q8</f>
         <v>10.255157760457088</v>
       </c>
-      <c r="U26" s="146"/>
-    </row>
-    <row r="27" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N27" s="169" t="s">
+      <c r="N27" s="139" t="s">
         <v>269</v>
       </c>
-      <c r="O27" s="170"/>
-      <c r="U27" s="146"/>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E28" s="169" t="s">
+      <c r="O27" s="140"/>
+      <c r="U27" s="94"/>
+    </row>
+    <row r="28" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N28" s="141" t="s">
+        <v>131</v>
+      </c>
+      <c r="O28" s="142"/>
+      <c r="U28" s="96"/>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="E29" s="124" t="s">
         <v>230</v>
       </c>
-      <c r="F28" s="170"/>
-      <c r="N28" s="162" t="s">
+      <c r="F29" s="125"/>
+      <c r="N29" s="119" t="s">
+        <v>268</v>
+      </c>
+      <c r="O29" s="61">
+        <v>100</v>
+      </c>
+      <c r="U29" s="93"/>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="E30" s="117" t="s">
         <v>131</v>
       </c>
-      <c r="O28" s="163"/>
-      <c r="U28" s="144"/>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E29" s="162" t="s">
-        <v>131</v>
-      </c>
-      <c r="F29" s="163"/>
-      <c r="N29" s="164" t="s">
-        <v>268</v>
-      </c>
-      <c r="O29" s="187">
-        <v>100</v>
-      </c>
-      <c r="U29" s="145"/>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E30" s="164" t="s">
+      <c r="F30" s="118"/>
+      <c r="N30" s="136" t="s">
+        <v>214</v>
+      </c>
+      <c r="O30" s="138">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="E31" s="119" t="s">
         <v>149</v>
       </c>
-      <c r="F30" s="61">
+      <c r="F31" s="61">
         <v>3.3</v>
       </c>
-      <c r="N30" s="184" t="s">
-        <v>214</v>
-      </c>
-      <c r="O30" s="186">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E31" s="164" t="s">
+      <c r="N31" s="136" t="s">
+        <v>295</v>
+      </c>
+      <c r="O31" s="138">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="E32" s="119" t="s">
         <v>142</v>
       </c>
-      <c r="F31" s="61">
+      <c r="F32" s="61">
         <v>10</v>
       </c>
-      <c r="N31" s="184" t="s">
-        <v>295</v>
-      </c>
-      <c r="O31" s="186">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="E32" s="184" t="s">
+      <c r="N32" s="136" t="s">
+        <v>296</v>
+      </c>
+      <c r="O32" s="138">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="5:15" x14ac:dyDescent="0.35">
+      <c r="E33" s="136" t="s">
         <v>240</v>
       </c>
-      <c r="F32" s="185">
+      <c r="F33" s="137">
         <v>1.5</v>
       </c>
-      <c r="N32" s="184" t="s">
-        <v>296</v>
-      </c>
-      <c r="O32" s="186">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="5:15" x14ac:dyDescent="0.35">
-      <c r="E33" s="162" t="s">
+      <c r="N33" s="141" t="s">
         <v>130</v>
       </c>
-      <c r="F33" s="163"/>
-      <c r="N33" s="162" t="s">
+      <c r="O33" s="142"/>
+    </row>
+    <row r="34" spans="5:15" x14ac:dyDescent="0.35">
+      <c r="E34" s="117" t="s">
         <v>130</v>
       </c>
-      <c r="O33" s="163"/>
-    </row>
-    <row r="34" spans="5:15" x14ac:dyDescent="0.35">
-      <c r="E34" s="73" t="str">
-        <f>CAL_Rg!J5</f>
-        <v>Ig,max,on (A)</v>
-      </c>
-      <c r="F34" s="78">
-        <f>CAL_Rg!K5</f>
-        <v>1.7389830508474575</v>
-      </c>
+      <c r="F34" s="118"/>
       <c r="N34" s="73" t="str">
         <f>'CAL_Rv1-2'!M22</f>
         <v>Cadc,ext,real (pF)</v>
@@ -6989,119 +6986,108 @@
     </row>
     <row r="35" spans="5:15" x14ac:dyDescent="0.35">
       <c r="E35" s="73" t="str">
+        <f>CAL_Rg!J5</f>
+        <v>Ig,max,on (A)</v>
+      </c>
+      <c r="F35" s="78">
+        <f>CAL_Rg!K5</f>
+        <v>1.7389830508474575</v>
+      </c>
+      <c r="N35" s="126" t="str">
+        <f>'CAL_Rv1-2'!M30</f>
+        <v>Tfill,adc,ext (ns)</v>
+      </c>
+      <c r="O35" s="135">
+        <f>'CAL_Rv1-2'!N30</f>
+        <v>282.62727272727278</v>
+      </c>
+    </row>
+    <row r="36" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E36" s="73" t="str">
         <f>CAL_Rg!J6</f>
         <v>Ig,max,off (A)</v>
       </c>
-      <c r="F35" s="78">
+      <c r="F36" s="78">
         <f>CAL_Rg!K6</f>
         <v>2.2768614691527969</v>
       </c>
-      <c r="N35" s="171" t="str">
-        <f>'CAL_Rv1-2'!M30</f>
-        <v>Tfill,adc,ext (ns)</v>
-      </c>
-      <c r="O35" s="180">
-        <f>'CAL_Rv1-2'!N30</f>
-        <v>12.870297029702972</v>
-      </c>
-    </row>
-    <row r="36" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E36" s="171" t="str">
+      <c r="N36" s="177" t="str">
+        <f>'CAL_Rv1-2'!P13</f>
+        <v>Tfill,samp (ns)</v>
+      </c>
+      <c r="O36" s="178">
+        <f>'CAL_Rv1-2'!Q13</f>
+        <v>169.57636363636365</v>
+      </c>
+    </row>
+    <row r="37" spans="5:15" x14ac:dyDescent="0.35">
+      <c r="E37" s="126" t="str">
         <f>CAL_Rg!J25</f>
         <v>t_rise (ns)</v>
       </c>
-      <c r="F36" s="175">
+      <c r="F37" s="130">
         <f>CAL_Rg!K25</f>
         <v>9.8825000000000003</v>
       </c>
-      <c r="N36" s="173" t="str">
-        <f>'CAL_Rv1-2'!P13</f>
-        <v>Tfill,samp (ns)</v>
-      </c>
-      <c r="O36" s="179">
-        <f>'CAL_Rv1-2'!Q13</f>
-        <v>7.7221782178217833</v>
-      </c>
-    </row>
-    <row r="37" spans="5:15" x14ac:dyDescent="0.35">
-      <c r="E37" s="171" t="str">
+      <c r="N37" s="67" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="38" spans="5:15" x14ac:dyDescent="0.35">
+      <c r="E38" s="126" t="str">
         <f>CAL_Rg!J26</f>
         <v>t_fall (ns)</v>
       </c>
-      <c r="F37" s="175">
+      <c r="F38" s="130">
         <f>CAL_Rg!K26</f>
         <v>7.5478900375939855</v>
       </c>
-      <c r="N37" s="67" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="38" spans="5:15" x14ac:dyDescent="0.35">
-      <c r="E38" s="181" t="str">
+      <c r="N38" s="67" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="39" spans="5:15" x14ac:dyDescent="0.35">
+      <c r="E39" s="73" t="str">
         <f>CAL_Rg!M11</f>
         <v>Pg,loss (mW)</v>
       </c>
-      <c r="F38" s="183">
+      <c r="F39" s="78">
         <f>CAL_Rg!N11</f>
         <v>40.383359999999996</v>
       </c>
-      <c r="N38" s="67" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="39" spans="5:15" x14ac:dyDescent="0.35">
-      <c r="E39" s="171" t="str">
+    </row>
+    <row r="40" spans="5:15" x14ac:dyDescent="0.35">
+      <c r="E40" s="126" t="str">
         <f>CAL_Rg!P13</f>
         <v>Prg,on+off (mW)</v>
       </c>
-      <c r="F39" s="175">
+      <c r="F40" s="130">
         <f>CAL_Rg!Q13</f>
         <v>27.360304480749178</v>
       </c>
     </row>
-    <row r="40" spans="5:15" x14ac:dyDescent="0.35">
-      <c r="E40" s="171" t="str">
+    <row r="41" spans="5:15" x14ac:dyDescent="0.35">
+      <c r="E41" s="126" t="str">
         <f>CAL_Rg!P20</f>
         <v>Prg,off (mW)</v>
       </c>
-      <c r="F40" s="175">
+      <c r="F41" s="130">
         <f>CAL_Rg!Q20</f>
         <v>3.8750645831104009</v>
       </c>
     </row>
-    <row r="41" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E41" s="87" t="str">
+    <row r="42" spans="5:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E42" s="87" t="str">
         <f>CAL_Rg!P26</f>
         <v>Prgdint,mean (mW)</v>
       </c>
-      <c r="F41" s="89">
+      <c r="F42" s="89">
         <f>CAL_Rg!Q26</f>
         <v>9.1479909361404168</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="B18:C18"/>
+  <mergeCells count="38">
     <mergeCell ref="T23:U23"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
@@ -7118,11 +7104,28 @@
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="N14:O14"/>
     <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="K14:L14"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="N33:O33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7695,14 +7698,14 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="143" t="str">
+      <c r="A16" t="str">
         <f>IF(B16&gt;=1000,C16&amp; "kΩ, ",B16&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>51Ω, 2012m</v>
       </c>
       <c r="B16">
         <v>51</v>
       </c>
-      <c r="C16" s="143">
+      <c r="C16">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>5.0999999999999997E-2</v>
       </c>
@@ -7720,14 +7723,14 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="143" t="str">
+      <c r="A17" t="str">
         <f>IF(B17&gt;=1000,C17&amp; "kΩ, ",B17&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>56Ω, 2012m</v>
       </c>
       <c r="B17">
         <v>56</v>
       </c>
-      <c r="C17" s="143">
+      <c r="C17">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>5.6000000000000001E-2</v>
       </c>
@@ -7745,14 +7748,14 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="143" t="str">
+      <c r="A18" t="str">
         <f>IF(B18&gt;=1000,C18&amp; "kΩ, ",B18&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>62Ω, 2012m</v>
       </c>
       <c r="B18">
         <v>62</v>
       </c>
-      <c r="C18" s="143">
+      <c r="C18">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>6.2E-2</v>
       </c>
@@ -7770,14 +7773,14 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="143" t="str">
+      <c r="A19" t="str">
         <f>IF(B19&gt;=1000,C19&amp; "kΩ, ",B19&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>68Ω, 2012m</v>
       </c>
       <c r="B19">
         <v>68</v>
       </c>
-      <c r="C19" s="143">
+      <c r="C19">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>6.8000000000000005E-2</v>
       </c>
@@ -7795,14 +7798,14 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="143" t="str">
+      <c r="A20" t="str">
         <f>IF(B20&gt;=1000,C20&amp; "kΩ, ",B20&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>75Ω, 2012m</v>
       </c>
       <c r="B20">
         <v>75</v>
       </c>
-      <c r="C20" s="143">
+      <c r="C20">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>7.4999999999999997E-2</v>
       </c>
@@ -7820,14 +7823,14 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="143" t="str">
+      <c r="A21" t="str">
         <f>IF(B21&gt;=1000,C21&amp; "kΩ, ",B21&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>82Ω, 2012m</v>
       </c>
       <c r="B21">
         <v>82</v>
       </c>
-      <c r="C21" s="143">
+      <c r="C21">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>8.2000000000000003E-2</v>
       </c>
@@ -7845,14 +7848,14 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="143" t="str">
+      <c r="A22" t="str">
         <f>IF(B22&gt;=1000,C22&amp; "kΩ, ",B22&amp; "Ω, ")  &amp; DB_R[[#This Row],[Package (m)]]</f>
         <v>91Ω, 2012m</v>
       </c>
       <c r="B22">
         <v>91</v>
       </c>
-      <c r="C22" s="143">
+      <c r="C22">
         <f>DB_R[[#This Row],[R (Ω)]]/1000</f>
         <v>9.0999999999999998E-2</v>
       </c>
@@ -10350,7 +10353,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="3.1796875" style="67" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" style="67" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.1796875" style="67" customWidth="1"/>
     <col min="5" max="6" width="3.1796875" style="67" customWidth="1"/>
     <col min="7" max="7" width="23.453125" style="67" customWidth="1"/>
@@ -10385,19 +10388,19 @@
         <v>10.5</v>
       </c>
       <c r="J2" s="68" t="str">
-        <f>C29</f>
+        <f>C30</f>
         <v>Qg,typ @ 10V (nC)</v>
       </c>
       <c r="K2" s="84">
-        <f>D29</f>
+        <f>D30</f>
         <v>41</v>
       </c>
       <c r="M2" s="68" t="str">
-        <f>C19</f>
+        <f>C20</f>
         <v>Safety margin on Cboot</v>
       </c>
       <c r="N2" s="84">
-        <f>D19</f>
+        <f>D20</f>
         <v>3</v>
       </c>
       <c r="P2" s="68" t="str">
@@ -10411,11 +10414,11 @@
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B3" s="63"/>
-      <c r="C3" s="91" t="s">
+      <c r="C3" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="92"/>
-      <c r="E3" s="124"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="64"/>
       <c r="G3" s="70" t="str">
         <f>C11</f>
         <v>Vhbr (V)</v>
@@ -10434,7 +10437,7 @@
       </c>
       <c r="M3" s="70" t="str">
         <f>C18</f>
-        <v>Expected derating (%)</v>
+        <v>Expected derating max (%)</v>
       </c>
       <c r="N3" s="61">
         <f>D18</f>
@@ -10458,7 +10461,7 @@
         <f>HMI!B4</f>
         <v>V1.0</v>
       </c>
-      <c r="E4" s="125"/>
+      <c r="E4" s="65"/>
       <c r="G4" s="70" t="str">
         <f>C12</f>
         <v>Vhbh,max (V)</v>
@@ -10501,12 +10504,12 @@
         <f>_xlfn.XLOOKUP(D4, DB_limits[Name], DB_limits[Dmax (%)])</f>
         <v>90</v>
       </c>
-      <c r="E5" s="125"/>
+      <c r="E5" s="65"/>
       <c r="G5" s="70" t="s">
         <v>208</v>
       </c>
       <c r="H5" s="61">
-        <f>D22</f>
+        <f>D23</f>
         <v>0.24</v>
       </c>
       <c r="J5" s="70" t="str">
@@ -10543,7 +10546,7 @@
         <f>_xlfn.XLOOKUP(D4,DB_limits[Name],DB_limits[Fmax (kHz)])</f>
         <v>64</v>
       </c>
-      <c r="E6" s="125"/>
+      <c r="E6" s="65"/>
       <c r="G6" s="87" t="s">
         <v>219</v>
       </c>
@@ -10573,14 +10576,14 @@
     <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B7" s="63"/>
       <c r="C7" s="36" t="str">
-        <f>HMI!B20</f>
+        <f>HMI!B21</f>
         <v>t_blank@V_sw=0 (ns)</v>
       </c>
       <c r="D7" s="2">
-        <f>HMI!C20</f>
+        <f>HMI!C21</f>
         <v>300</v>
       </c>
-      <c r="E7" s="125"/>
+      <c r="E7" s="65"/>
       <c r="G7" s="81"/>
       <c r="H7" s="82"/>
       <c r="J7" s="70" t="str">
@@ -10595,7 +10598,7 @@
       <c r="N7" s="72"/>
       <c r="P7" s="70" t="str">
         <f>C18</f>
-        <v>Expected derating (%)</v>
+        <v>Expected derating max (%)</v>
       </c>
       <c r="Q7" s="85">
         <f>D18</f>
@@ -10604,11 +10607,11 @@
     </row>
     <row r="8" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="63"/>
-      <c r="C8" s="91" t="s">
+      <c r="C8" s="158" t="s">
         <v>205</v>
       </c>
-      <c r="D8" s="92"/>
-      <c r="E8" s="124"/>
+      <c r="D8" s="159"/>
+      <c r="E8" s="64"/>
       <c r="G8" s="75"/>
       <c r="H8" s="76"/>
       <c r="J8" s="87" t="s">
@@ -10623,7 +10626,7 @@
       <c r="P8" s="87" t="s">
         <v>221</v>
       </c>
-      <c r="Q8" s="123">
+      <c r="Q8" s="107">
         <f>Q2-(Q2-Q3)*EXP(-Q4/Q5/Q6/(1-Q7%)*10^3)</f>
         <v>10.255157760457088</v>
       </c>
@@ -10637,7 +10640,7 @@
         <f>HMI!E3</f>
         <v>Infineon 2EDL8024</v>
       </c>
-      <c r="E9" s="125"/>
+      <c r="E9" s="65"/>
       <c r="J9" s="81"/>
       <c r="K9" s="82"/>
       <c r="P9" s="81"/>
@@ -10652,7 +10655,7 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Vfint,100mA (V)])</f>
         <v>2.15</v>
       </c>
-      <c r="E10" s="126"/>
+      <c r="E10" s="66"/>
       <c r="G10" s="68" t="str">
         <f>G2</f>
         <v>Vdd (V)</v>
@@ -10672,7 +10675,7 @@
         <v>90</v>
       </c>
       <c r="P10" s="75"/>
-      <c r="Q10" s="114"/>
+      <c r="Q10" s="102"/>
     </row>
     <row r="11" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="63"/>
@@ -10683,7 +10686,7 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Vhbr (V)])</f>
         <v>6</v>
       </c>
-      <c r="E11" s="125"/>
+      <c r="E11" s="65"/>
       <c r="G11" s="70" t="str">
         <f>G6</f>
         <v>ΔVboot,max (V)</v>
@@ -10713,7 +10716,7 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Vhbh,max (V)])</f>
         <v>0.5</v>
       </c>
-      <c r="E12" s="125"/>
+      <c r="E12" s="65"/>
       <c r="G12" s="87" t="s">
         <v>220</v>
       </c>
@@ -10748,7 +10751,7 @@
         <f>HMI!F5</f>
         <v>10.5</v>
       </c>
-      <c r="E13" s="125"/>
+      <c r="E13" s="65"/>
       <c r="G13" s="81"/>
       <c r="H13" s="82"/>
       <c r="J13" s="68" t="str">
@@ -10762,17 +10765,17 @@
       <c r="M13" s="87" t="s">
         <v>217</v>
       </c>
-      <c r="N13" s="123">
+      <c r="N13" s="107">
         <f>((1-N10%)/N11)*1000-N12/1000</f>
         <v>1.2624999999999995</v>
       </c>
       <c r="P13" s="70" t="str">
-        <f>P7</f>
-        <v>Expected derating (%)</v>
+        <f>C19</f>
+        <v>Expected derating min (%)</v>
       </c>
       <c r="Q13" s="85">
-        <f>Q7</f>
-        <v>60</v>
+        <f>D19</f>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10785,7 +10788,7 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Ihb (mA)])</f>
         <v>0.7</v>
       </c>
-      <c r="E14" s="125"/>
+      <c r="E14" s="65"/>
       <c r="G14" s="75"/>
       <c r="H14" s="76"/>
       <c r="J14" s="70" t="str">
@@ -10799,12 +10802,12 @@
       <c r="M14" s="81"/>
       <c r="N14" s="82"/>
       <c r="P14" s="70" t="str">
-        <f>G18</f>
-        <v>Vboot,max (V)</v>
-      </c>
-      <c r="Q14" s="78">
-        <f>H18</f>
-        <v>10.26</v>
+        <f>G6</f>
+        <v>ΔVboot,max (V)</v>
+      </c>
+      <c r="Q14" s="85">
+        <f>H6</f>
+        <v>3.76</v>
       </c>
     </row>
     <row r="15" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10817,7 +10820,7 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Ihbs (mA)])</f>
         <v>1.25</v>
       </c>
-      <c r="E15" s="125"/>
+      <c r="E15" s="65"/>
       <c r="J15" s="87" t="s">
         <v>147</v>
       </c>
@@ -10828,12 +10831,12 @@
       <c r="M15" s="71"/>
       <c r="N15" s="72"/>
       <c r="P15" s="70" t="str">
-        <f>G6</f>
-        <v>ΔVboot,max (V)</v>
+        <f>C6</f>
+        <v>Fmax (kHz)</v>
       </c>
       <c r="Q15" s="85">
-        <f>H6</f>
-        <v>3.76</v>
+        <f>D6</f>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10846,7 +10849,7 @@
         <f>_xlfn.XLOOKUP(D9, DB_GD[Part], DB_GD[Rboot,int (Ω)])</f>
         <v>21.5</v>
       </c>
-      <c r="E16" s="125"/>
+      <c r="E16" s="65"/>
       <c r="G16" s="68" t="str">
         <f>G2</f>
         <v>Vdd (V)</v>
@@ -10859,22 +10862,21 @@
       <c r="K16" s="82"/>
       <c r="M16" s="75"/>
       <c r="N16" s="76"/>
-      <c r="P16" s="70" t="str">
-        <f>C6</f>
-        <v>Fmax (kHz)</v>
-      </c>
-      <c r="Q16" s="85">
-        <f>D6</f>
-        <v>64</v>
+      <c r="P16" s="87" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q16" s="88">
+        <f>0.5*Q12*(1-Q13%)*Q14^2*Q15*10^-3</f>
+        <v>57.002803199999988</v>
       </c>
     </row>
     <row r="17" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="63"/>
-      <c r="C17" s="91" t="s">
+      <c r="C17" s="158" t="s">
         <v>213</v>
       </c>
-      <c r="D17" s="92"/>
-      <c r="E17" s="124"/>
+      <c r="D17" s="159"/>
+      <c r="E17" s="64"/>
       <c r="G17" s="70" t="str">
         <f>G5</f>
         <v>Vf (V)</v>
@@ -10885,56 +10887,51 @@
       </c>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
-      <c r="P17" s="87" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q17" s="88">
-        <f>Q12*10^-6*(1-Q13%)*Q14*Q15*Q16*10^3</f>
-        <v>177.76558079999998</v>
-      </c>
+      <c r="P17" s="81"/>
+      <c r="Q17" s="82"/>
     </row>
     <row r="18" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="63"/>
       <c r="C18" s="36" t="str">
         <f>HMI!E16</f>
-        <v>Expected derating (%)</v>
+        <v>Expected derating max (%)</v>
       </c>
       <c r="D18" s="2">
         <f>HMI!F16</f>
         <v>60</v>
       </c>
-      <c r="E18" s="125"/>
+      <c r="E18" s="65"/>
       <c r="G18" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="H18" s="123">
+      <c r="H18" s="107">
         <f>H16-H17</f>
         <v>10.26</v>
       </c>
       <c r="J18" s="75"/>
       <c r="K18" s="76"/>
       <c r="M18" s="68" t="str">
-        <f>C26</f>
+        <f>C27</f>
         <v>Rboot,ext (Ω)</v>
       </c>
       <c r="N18" s="69">
-        <f>D26</f>
+        <f>D27</f>
         <v>3.3</v>
       </c>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="82"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="102"/>
     </row>
     <row r="19" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="63"/>
       <c r="C19" s="36" t="str">
         <f>HMI!E17</f>
-        <v>Safety margin on Cboot</v>
+        <v>Expected derating min (%)</v>
       </c>
       <c r="D19" s="2">
         <f>HMI!F17</f>
-        <v>3</v>
-      </c>
-      <c r="E19" s="125"/>
+        <v>30</v>
+      </c>
+      <c r="E19" s="65"/>
       <c r="G19" s="81"/>
       <c r="H19" s="82"/>
       <c r="M19" s="70" t="str">
@@ -10945,22 +10942,24 @@
         <f>D16</f>
         <v>21.5</v>
       </c>
-      <c r="P19" s="75"/>
-      <c r="Q19" s="114"/>
     </row>
     <row r="20" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="63"/>
-      <c r="C20" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="D20" s="92"/>
-      <c r="E20" s="124"/>
+      <c r="C20" s="36" t="str">
+        <f>HMI!E18</f>
+        <v>Safety margin on Cboot</v>
+      </c>
+      <c r="D20" s="2">
+        <f>HMI!F18</f>
+        <v>3</v>
+      </c>
+      <c r="E20" s="65"/>
       <c r="G20" s="75"/>
       <c r="H20" s="76"/>
-      <c r="J20" s="127" t="s">
+      <c r="J20" s="156" t="s">
         <v>229</v>
       </c>
-      <c r="K20" s="128"/>
+      <c r="K20" s="157"/>
       <c r="M20" s="87" t="s">
         <v>222</v>
       </c>
@@ -10968,43 +10967,47 @@
         <f>N19*N18/(N18+N19)</f>
         <v>2.8608870967741935</v>
       </c>
+      <c r="P20" s="68" t="str">
+        <f>C27</f>
+        <v>Rboot,ext (Ω)</v>
+      </c>
+      <c r="Q20" s="84">
+        <f>D27</f>
+        <v>3.3</v>
+      </c>
     </row>
     <row r="21" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B21" s="63"/>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="91" t="s">
+        <v>210</v>
+      </c>
+      <c r="D21" s="92"/>
+      <c r="E21" s="64"/>
+      <c r="J21" s="152">
+        <v>47</v>
+      </c>
+      <c r="K21" s="153"/>
+      <c r="M21" s="81"/>
+      <c r="N21" s="82"/>
+      <c r="P21" s="70" t="str">
+        <f>C16</f>
+        <v>Rboot,int (Ω)</v>
+      </c>
+      <c r="Q21" s="61">
+        <f>D16</f>
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B22" s="63"/>
+      <c r="C22" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="D21" s="2" t="str">
+      <c r="D22" s="2" t="str">
         <f>HMI!E8</f>
         <v>Rohm RB161QS-40</v>
       </c>
-      <c r="E21" s="125"/>
-      <c r="J21" s="101">
-        <v>47</v>
-      </c>
-      <c r="K21" s="102"/>
-      <c r="M21" s="81"/>
-      <c r="N21" s="82"/>
-      <c r="P21" s="68" t="str">
-        <f>C26</f>
-        <v>Rboot,ext (Ω)</v>
-      </c>
-      <c r="Q21" s="84">
-        <f>D26</f>
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B22" s="63"/>
-      <c r="C22" s="36" t="str">
-        <f>DB_diode[[#Headers],[Vf@100mA (V)]]</f>
-        <v>Vf@100mA (V)</v>
-      </c>
-      <c r="D22" s="2">
-        <f>_xlfn.XLOOKUP(D21, DB_diode[Ref], DB_diode[Vf@100mA (V)])</f>
-        <v>0.24</v>
-      </c>
-      <c r="E22" s="125"/>
+      <c r="E22" s="65"/>
       <c r="G22" s="68" t="str">
         <f>G18</f>
         <v>Vboot,max (V)</v>
@@ -11013,198 +11016,188 @@
         <f>H18</f>
         <v>10.26</v>
       </c>
-      <c r="J22" s="101">
+      <c r="J22" s="152">
         <v>56</v>
       </c>
-      <c r="K22" s="102"/>
-      <c r="M22" s="117"/>
-      <c r="N22" s="118"/>
+      <c r="K22" s="153"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="106"/>
       <c r="P22" s="70" t="str">
-        <f>C16</f>
-        <v>Rboot,int (Ω)</v>
-      </c>
-      <c r="Q22" s="61">
-        <f>D16</f>
-        <v>21.5</v>
+        <f>P16</f>
+        <v>Pboot (mW)</v>
+      </c>
+      <c r="Q22" s="85">
+        <f>Q16</f>
+        <v>57.002803199999988</v>
       </c>
     </row>
     <row r="23" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="63"/>
-      <c r="C23" s="91" t="s">
-        <v>216</v>
-      </c>
-      <c r="D23" s="92"/>
-      <c r="E23" s="124"/>
+      <c r="C23" s="36" t="str">
+        <f>DB_diode[[#Headers],[Vf@100mA (V)]]</f>
+        <v>Vf@100mA (V)</v>
+      </c>
+      <c r="D23" s="2">
+        <f>_xlfn.XLOOKUP(D22, DB_diode[Ref], DB_diode[Vf@100mA (V)])</f>
+        <v>0.24</v>
+      </c>
+      <c r="E23" s="65"/>
       <c r="G23" s="70" t="str">
-        <f>C24</f>
+        <f>C25</f>
         <v>Rpd,gate (kΩ)</v>
       </c>
       <c r="H23" s="61">
-        <f>D24</f>
+        <f>D25</f>
         <v>10</v>
       </c>
-      <c r="J23" s="101">
+      <c r="J23" s="152">
         <v>68</v>
       </c>
-      <c r="K23" s="102"/>
+      <c r="K23" s="153"/>
       <c r="M23" s="75"/>
       <c r="N23" s="76"/>
-      <c r="P23" s="70" t="str">
-        <f>P17</f>
-        <v>Pboot (mW)</v>
-      </c>
-      <c r="Q23" s="85">
-        <f>Q17</f>
-        <v>177.76558079999998</v>
+      <c r="P23" s="87" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q23" s="107">
+        <f>Q21/(Q20+Q21)*Q22</f>
+        <v>49.417752774193538</v>
       </c>
     </row>
     <row r="24" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="63"/>
-      <c r="C24" s="36" t="str">
+      <c r="C24" s="91" t="s">
+        <v>216</v>
+      </c>
+      <c r="D24" s="92"/>
+      <c r="E24" s="64"/>
+      <c r="G24" s="87" t="s">
+        <v>212</v>
+      </c>
+      <c r="H24" s="107">
+        <f>H22/H23</f>
+        <v>1.026</v>
+      </c>
+      <c r="J24" s="152">
+        <v>82</v>
+      </c>
+      <c r="K24" s="153"/>
+      <c r="P24" s="81"/>
+      <c r="Q24" s="82"/>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B25" s="63"/>
+      <c r="C25" s="36" t="str">
         <f>HMI!E12</f>
         <v>Rpd,gate (kΩ)</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D25" s="2">
         <f>HMI!F12</f>
         <v>10</v>
       </c>
-      <c r="E24" s="125"/>
-      <c r="G24" s="87" t="s">
-        <v>212</v>
-      </c>
-      <c r="H24" s="123">
-        <f>H22/H23</f>
-        <v>1.026</v>
-      </c>
-      <c r="J24" s="101">
-        <v>82</v>
-      </c>
-      <c r="K24" s="102"/>
-      <c r="P24" s="87" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q24" s="88">
-        <f>Q21/(Q22+Q21)*Q23</f>
-        <v>23.654290993548383</v>
-      </c>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B25" s="63"/>
-      <c r="C25" s="91" t="s">
-        <v>226</v>
-      </c>
-      <c r="D25" s="92"/>
-      <c r="E25" s="124"/>
+      <c r="E25" s="65"/>
       <c r="G25" s="81"/>
       <c r="H25" s="82"/>
-      <c r="J25" s="101">
+      <c r="J25" s="152">
         <v>100</v>
       </c>
-      <c r="K25" s="102"/>
-      <c r="P25" s="81"/>
-      <c r="Q25" s="82"/>
+      <c r="K25" s="153"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="72"/>
     </row>
     <row r="26" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="63"/>
-      <c r="C26" s="36" t="str">
-        <f>HMI!E18</f>
-        <v>Rboot,ext (Ω)</v>
-      </c>
-      <c r="D26" s="2">
-        <f>HMI!F18</f>
-        <v>3.3</v>
-      </c>
-      <c r="E26" s="125"/>
+      <c r="C26" s="91" t="s">
+        <v>226</v>
+      </c>
+      <c r="D26" s="92"/>
+      <c r="E26" s="64"/>
       <c r="G26" s="75"/>
       <c r="H26" s="76"/>
-      <c r="J26" s="101">
+      <c r="J26" s="152">
         <v>120</v>
       </c>
-      <c r="K26" s="102"/>
-      <c r="P26" s="71"/>
-      <c r="Q26" s="72"/>
-    </row>
-    <row r="27" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K26" s="153"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="76"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B27" s="63"/>
-      <c r="C27" s="91" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" s="92"/>
-      <c r="E27" s="124"/>
-      <c r="J27" s="101">
+      <c r="C27" s="36" t="str">
+        <f>HMI!E19</f>
+        <v>Rboot,ext (Ω)</v>
+      </c>
+      <c r="D27" s="2">
+        <f>HMI!F19</f>
+        <v>3.3</v>
+      </c>
+      <c r="E27" s="65"/>
+      <c r="J27" s="152">
         <v>150</v>
       </c>
-      <c r="K27" s="102"/>
-      <c r="P27" s="75"/>
-      <c r="Q27" s="76"/>
+      <c r="K27" s="153"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B28" s="63"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="91" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="92"/>
+      <c r="E28" s="64"/>
+      <c r="J28" s="152">
+        <v>180</v>
+      </c>
+      <c r="K28" s="153"/>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B29" s="63"/>
+      <c r="C29" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="D28" s="2" t="str">
+      <c r="D29" s="2" t="str">
         <f>HMI!H4</f>
         <v>TI CSD18540Q5B</v>
       </c>
-      <c r="E28" s="125"/>
-      <c r="J28" s="101">
-        <v>180</v>
-      </c>
-      <c r="K28" s="102"/>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B29" s="63"/>
-      <c r="C29" s="36" t="str">
+      <c r="E29" s="65"/>
+      <c r="J29" s="152">
+        <v>220</v>
+      </c>
+      <c r="K29" s="153"/>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B30" s="63"/>
+      <c r="C30" s="36" t="str">
         <f>HMI!H6</f>
         <v>Qg,typ @ 10V (nC)</v>
       </c>
-      <c r="D29" s="2">
-        <f>_xlfn.XLOOKUP(D28, DB_Mostfet[Part],DB_Mostfet[Qg,typ @ 10V (nC)])</f>
+      <c r="D30" s="2">
+        <f>_xlfn.XLOOKUP(D29, DB_Mostfet[Part],DB_Mostfet[Qg,typ @ 10V (nC)])</f>
         <v>41</v>
       </c>
-      <c r="E29" s="125"/>
-      <c r="J29" s="101">
-        <v>220</v>
-      </c>
-      <c r="K29" s="102"/>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B30" s="63"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
-      <c r="J30" s="101">
+      <c r="E30" s="65"/>
+      <c r="J30" s="152">
         <v>470</v>
       </c>
-      <c r="K30" s="102"/>
+      <c r="K30" s="153"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="J31" s="101">
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="J31" s="152">
         <v>680</v>
       </c>
-      <c r="K31" s="102"/>
+      <c r="K31" s="153"/>
     </row>
     <row r="32" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J32" s="99">
+      <c r="J32" s="154">
         <v>1000</v>
       </c>
-      <c r="K32" s="100"/>
+      <c r="K32" s="155"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J30:K30"/>
+  <mergeCells count="16">
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="J21:K21"/>
@@ -11213,6 +11206,14 @@
     <mergeCell ref="J26:K26"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="J28:K28"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11260,10 +11261,10 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B3" s="63"/>
-      <c r="C3" s="91" t="s">
+      <c r="C3" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="92"/>
+      <c r="D3" s="159"/>
       <c r="E3" s="64"/>
       <c r="G3" s="70" t="str">
         <f>C7</f>
@@ -11395,11 +11396,11 @@
     </row>
     <row r="11" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="63"/>
-      <c r="C11" s="91" t="str">
+      <c r="C11" s="158" t="str">
         <f>HMI!H2</f>
         <v>MOSFET</v>
       </c>
-      <c r="D11" s="92"/>
+      <c r="D11" s="159"/>
       <c r="E11" s="65"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.35">
@@ -11444,10 +11445,10 @@
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B14" s="63"/>
-      <c r="C14" s="91" t="s">
+      <c r="C14" s="158" t="s">
         <v>315</v>
       </c>
-      <c r="D14" s="92"/>
+      <c r="D14" s="159"/>
       <c r="E14" s="65"/>
       <c r="G14" s="70" t="str">
         <f>C7</f>
@@ -11461,11 +11462,11 @@
     <row r="15" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B15" s="63"/>
       <c r="C15" s="36" t="str">
-        <f>HMI!E36</f>
+        <f>HMI!E37</f>
         <v>t_rise (ns)</v>
       </c>
       <c r="D15" s="7">
-        <f>HMI!F36</f>
+        <f>HMI!F37</f>
         <v>9.8825000000000003</v>
       </c>
       <c r="E15" s="63"/>
@@ -11481,11 +11482,11 @@
     <row r="16" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B16" s="63"/>
       <c r="C16" s="36" t="str">
-        <f>HMI!E37</f>
+        <f>HMI!E38</f>
         <v>t_fall (ns)</v>
       </c>
       <c r="D16" s="7">
-        <f>HMI!F37</f>
+        <f>HMI!F38</f>
         <v>7.5478900375939855</v>
       </c>
       <c r="E16" s="64"/>
@@ -11653,13 +11654,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E1" s="130"/>
+      <c r="E1" s="108"/>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B2" s="63"/>
       <c r="C2" s="63"/>
       <c r="D2" s="63"/>
-      <c r="E2" s="125"/>
+      <c r="E2" s="65"/>
       <c r="G2" s="68" t="str">
         <f>C8</f>
         <v>Rg,off (Ω)</v>
@@ -11695,11 +11696,11 @@
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B3" s="63"/>
-      <c r="C3" s="91" t="s">
+      <c r="C3" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="92"/>
-      <c r="E3" s="125"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="65"/>
       <c r="G3" s="70" t="str">
         <f>C9</f>
         <v>Rg,on+off (Ω)</v>
@@ -11742,7 +11743,7 @@
         <f>HMI!B4</f>
         <v>V1.0</v>
       </c>
-      <c r="E4" s="125"/>
+      <c r="E4" s="65"/>
       <c r="G4" s="79" t="s">
         <v>236</v>
       </c>
@@ -11786,8 +11787,8 @@
         <v>90</v>
       </c>
       <c r="E5" s="63"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="132"/>
+      <c r="G5" s="160"/>
+      <c r="H5" s="161"/>
       <c r="J5" s="73" t="s">
         <v>302</v>
       </c>
@@ -11820,61 +11821,61 @@
         <f>HMI!C7</f>
         <v>64</v>
       </c>
-      <c r="E6" s="124"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="134"/>
+      <c r="E6" s="64"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="163"/>
       <c r="J6" s="87" t="s">
         <v>303</v>
       </c>
-      <c r="K6" s="123">
+      <c r="K6" s="107">
         <f>K2/K4</f>
         <v>2.2768614691527969</v>
       </c>
-      <c r="M6" s="131"/>
-      <c r="N6" s="132"/>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="110"/>
+      <c r="M6" s="160"/>
+      <c r="N6" s="161"/>
+      <c r="P6" s="97"/>
+      <c r="Q6" s="98"/>
     </row>
     <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="63"/>
-      <c r="C7" s="91" t="s">
+      <c r="C7" s="158" t="s">
         <v>231</v>
       </c>
-      <c r="D7" s="92"/>
-      <c r="E7" s="125"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="136"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="65"/>
+      <c r="G7" s="164"/>
+      <c r="H7" s="165"/>
       <c r="J7" s="71"/>
       <c r="K7" s="72"/>
-      <c r="M7" s="135"/>
-      <c r="N7" s="136"/>
-      <c r="P7" s="111"/>
-      <c r="Q7" s="112"/>
+      <c r="M7" s="164"/>
+      <c r="N7" s="165"/>
+      <c r="P7" s="99"/>
+      <c r="Q7" s="100"/>
     </row>
     <row r="8" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="63"/>
       <c r="C8" s="36" t="str">
-        <f>HMI!E31</f>
+        <f>HMI!E32</f>
         <v>Rg,off (Ω)</v>
       </c>
       <c r="D8" s="2">
-        <f>HMI!F31</f>
+        <f>HMI!F32</f>
         <v>10</v>
       </c>
-      <c r="E8" s="125"/>
+      <c r="E8" s="65"/>
       <c r="J8" s="71"/>
       <c r="K8" s="72"/>
-      <c r="P8" s="113"/>
-      <c r="Q8" s="114"/>
+      <c r="P8" s="101"/>
+      <c r="Q8" s="102"/>
     </row>
     <row r="9" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="63"/>
       <c r="C9" s="36" t="str">
-        <f>HMI!E30</f>
+        <f>HMI!E31</f>
         <v>Rg,on+off (Ω)</v>
       </c>
       <c r="D9" s="2">
-        <f>HMI!F30</f>
+        <f>HMI!F31</f>
         <v>3.3</v>
       </c>
       <c r="E9" s="63"/>
@@ -11899,11 +11900,11 @@
     </row>
     <row r="10" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="63"/>
-      <c r="C10" s="91" t="s">
+      <c r="C10" s="158" t="s">
         <v>232</v>
       </c>
-      <c r="D10" s="92"/>
-      <c r="E10" s="124"/>
+      <c r="D10" s="159"/>
+      <c r="E10" s="64"/>
       <c r="G10" s="70" t="str">
         <f>C13</f>
         <v>Rpu,ls (Ω)</v>
@@ -11940,7 +11941,7 @@
         <f>HMI!E3</f>
         <v>Infineon 2EDL8024</v>
       </c>
-      <c r="E11" s="125"/>
+      <c r="E11" s="65"/>
       <c r="G11" s="70" t="str">
         <f>C9</f>
         <v>Rg,on+off (Ω)</v>
@@ -11975,7 +11976,7 @@
         <f>_xlfn.XLOOKUP(D11, DB_GD[Part], DB_GD[Rpu,hs (Ω)])</f>
         <v>1</v>
       </c>
-      <c r="E12" s="125"/>
+      <c r="E12" s="65"/>
       <c r="G12" s="70" t="str">
         <f>C24</f>
         <v>Rg,int,max (Ω)</v>
@@ -11992,8 +11993,8 @@
         <f>D23</f>
         <v>4</v>
       </c>
-      <c r="M12" s="119"/>
-      <c r="N12" s="120"/>
+      <c r="M12" s="166"/>
+      <c r="N12" s="167"/>
       <c r="P12" s="70" t="str">
         <f>P5</f>
         <v>Prg,mean (mW)</v>
@@ -12013,7 +12014,7 @@
         <f>_xlfn.XLOOKUP(D11, DB_GD[Part], DB_GD[Rpu,ls (Ω)])</f>
         <v>1</v>
       </c>
-      <c r="E13" s="125"/>
+      <c r="E13" s="65"/>
       <c r="G13" s="79" t="s">
         <v>233</v>
       </c>
@@ -12029,8 +12030,8 @@
         <f>H13</f>
         <v>5.9</v>
       </c>
-      <c r="M13" s="121"/>
-      <c r="N13" s="122"/>
+      <c r="M13" s="168"/>
+      <c r="N13" s="169"/>
       <c r="P13" s="79" t="s">
         <v>314</v>
       </c>
@@ -12049,9 +12050,9 @@
         <f>_xlfn.XLOOKUP(D11, DB_GD[Part], DB_GD[Rpd,hs (Ω)])</f>
         <v>0.5</v>
       </c>
-      <c r="E14" s="125"/>
-      <c r="G14" s="137"/>
-      <c r="H14" s="138"/>
+      <c r="E14" s="65"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="110"/>
       <c r="J14" s="70" t="str">
         <f>G22</f>
         <v>Req,off (Ω)</v>
@@ -12060,8 +12061,8 @@
         <f>H22</f>
         <v>4.5062030075187973</v>
       </c>
-      <c r="P14" s="137"/>
-      <c r="Q14" s="138"/>
+      <c r="P14" s="109"/>
+      <c r="Q14" s="110"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B15" s="63"/>
@@ -12073,9 +12074,9 @@
         <f>_xlfn.XLOOKUP(D11, DB_GD[Part], DB_GD[Rpd,ls (Ω)])</f>
         <v>0.35</v>
       </c>
-      <c r="E15" s="125"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="140"/>
+      <c r="E15" s="65"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="112"/>
       <c r="J15" s="73" t="s">
         <v>305</v>
       </c>
@@ -12091,26 +12092,26 @@
         <f>D5</f>
         <v>90</v>
       </c>
-      <c r="P15" s="139"/>
-      <c r="Q15" s="140"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="112"/>
     </row>
     <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="63"/>
       <c r="C16" s="36" t="str">
-        <f>HMI!E21</f>
+        <f>HMI!E22</f>
         <v>Vboot,max (V)</v>
       </c>
       <c r="D16" s="2">
-        <f>HMI!F21</f>
+        <f>HMI!F22</f>
         <v>10.26</v>
       </c>
-      <c r="E16" s="125"/>
-      <c r="G16" s="141"/>
-      <c r="H16" s="142"/>
+      <c r="E16" s="65"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="114"/>
       <c r="J16" s="87" t="s">
         <v>306</v>
       </c>
-      <c r="K16" s="123">
+      <c r="K16" s="107">
         <f>K12/K14</f>
         <v>0.8876652901180494</v>
       </c>
@@ -12122,20 +12123,20 @@
         <f>H9</f>
         <v>1</v>
       </c>
-      <c r="P16" s="141"/>
-      <c r="Q16" s="142"/>
+      <c r="P16" s="113"/>
+      <c r="Q16" s="114"/>
     </row>
     <row r="17" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="63"/>
       <c r="C17" s="36" t="str">
-        <f>HMI!E23</f>
+        <f>HMI!E24</f>
         <v>Cboot (nF)</v>
       </c>
       <c r="D17" s="2">
-        <f>HMI!F23</f>
+        <f>HMI!F24</f>
         <v>180</v>
       </c>
-      <c r="E17" s="125"/>
+      <c r="E17" s="65"/>
       <c r="J17" s="71"/>
       <c r="K17" s="72"/>
       <c r="M17" s="70" t="str">
@@ -12150,14 +12151,14 @@
     <row r="18" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B18" s="63"/>
       <c r="C18" s="36" t="str">
-        <f>HMI!E32</f>
+        <f>HMI!E33</f>
         <v>Safety margin on losses</v>
       </c>
       <c r="D18" s="7">
-        <f>HMI!F32</f>
+        <f>HMI!F33</f>
         <v>1.5</v>
       </c>
-      <c r="E18" s="126"/>
+      <c r="E18" s="66"/>
       <c r="G18" s="68" t="str">
         <f>C14</f>
         <v>Rpd,hs (Ω)</v>
@@ -12187,10 +12188,10 @@
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" s="63"/>
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="158" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="92"/>
+      <c r="D19" s="159"/>
       <c r="E19" s="63"/>
       <c r="G19" s="70" t="str">
         <f>C15</f>
@@ -12228,7 +12229,7 @@
         <f>HMI!H4</f>
         <v>TI CSD18540Q5B</v>
       </c>
-      <c r="E20" s="124"/>
+      <c r="E20" s="64"/>
       <c r="G20" s="70" t="str">
         <f>G4</f>
         <v>Rg,eq,off</v>
@@ -12264,7 +12265,7 @@
         <f>_xlfn.XLOOKUP(D20, DB_Mostfet[Part],DB_Mostfet[Qg,typ @ 10V (nC)])</f>
         <v>41</v>
       </c>
-      <c r="E21" s="125"/>
+      <c r="E21" s="65"/>
       <c r="G21" s="70" t="str">
         <f>C24</f>
         <v>Rg,int,max (Ω)</v>
@@ -12273,10 +12274,10 @@
         <f>D24</f>
         <v>1.6</v>
       </c>
-      <c r="M21" s="131"/>
-      <c r="N21" s="132"/>
-      <c r="P21" s="137"/>
-      <c r="Q21" s="138"/>
+      <c r="M21" s="160"/>
+      <c r="N21" s="161"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="110"/>
     </row>
     <row r="22" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="63"/>
@@ -12288,7 +12289,7 @@
         <f>_xlfn.XLOOKUP(D20, DB_Mostfet[Part],DB_Mostfet[Qgd,typ (nC)])</f>
         <v>6.7</v>
       </c>
-      <c r="E22" s="124"/>
+      <c r="E22" s="64"/>
       <c r="G22" s="79" t="s">
         <v>307</v>
       </c>
@@ -12304,10 +12305,10 @@
         <f>D22</f>
         <v>6.7</v>
       </c>
-      <c r="M22" s="133"/>
-      <c r="N22" s="134"/>
-      <c r="P22" s="141"/>
-      <c r="Q22" s="142"/>
+      <c r="M22" s="162"/>
+      <c r="N22" s="163"/>
+      <c r="P22" s="113"/>
+      <c r="Q22" s="114"/>
     </row>
     <row r="23" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="63"/>
@@ -12319,9 +12320,9 @@
         <f>_xlfn.XLOOKUP(D20, DB_Mostfet[Part],DB_Mostfet[Vmiller (V)])</f>
         <v>4</v>
       </c>
-      <c r="E23" s="124"/>
-      <c r="G23" s="137"/>
-      <c r="H23" s="138"/>
+      <c r="E23" s="64"/>
+      <c r="G23" s="109"/>
+      <c r="H23" s="110"/>
       <c r="J23" s="70" t="str">
         <f>J15</f>
         <v>Imiller,on (A)</v>
@@ -12330,8 +12331,8 @@
         <f>K15</f>
         <v>0.67796610169491522</v>
       </c>
-      <c r="M23" s="135"/>
-      <c r="N23" s="136"/>
+      <c r="M23" s="164"/>
+      <c r="N23" s="165"/>
     </row>
     <row r="24" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="63"/>
@@ -12343,9 +12344,9 @@
         <f>_xlfn.XLOOKUP(D20, DB_Mostfet[Part],DB_Mostfet[Rg,int,max (Ω)])</f>
         <v>1.6</v>
       </c>
-      <c r="E24" s="125"/>
-      <c r="G24" s="139"/>
-      <c r="H24" s="140"/>
+      <c r="E24" s="65"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="112"/>
       <c r="J24" s="70" t="str">
         <f>J16</f>
         <v>Imiller,off (A)</v>
@@ -12367,9 +12368,9 @@
       <c r="B25" s="63"/>
       <c r="C25" s="63"/>
       <c r="D25" s="63"/>
-      <c r="E25" s="125"/>
-      <c r="G25" s="141"/>
-      <c r="H25" s="142"/>
+      <c r="E25" s="65"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="114"/>
       <c r="J25" s="73" t="s">
         <v>309</v>
       </c>
@@ -12398,7 +12399,7 @@
       <c r="J26" s="87" t="s">
         <v>308</v>
       </c>
-      <c r="K26" s="123">
+      <c r="K26" s="107">
         <f>K22/K24</f>
         <v>7.5478900375939855</v>
       </c>
@@ -12429,8 +12430,8 @@
         <f>H4</f>
         <v>2.481203007518797</v>
       </c>
-      <c r="P27" s="137"/>
-      <c r="Q27" s="138"/>
+      <c r="P27" s="109"/>
+      <c r="Q27" s="110"/>
     </row>
     <row r="28" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J28" s="71"/>
@@ -12442,24 +12443,24 @@
         <f>(N25%*N26+(1-N25%)*N27)/2</f>
         <v>1.6090601503759396</v>
       </c>
-      <c r="P28" s="141"/>
-      <c r="Q28" s="142"/>
+      <c r="P28" s="113"/>
+      <c r="Q28" s="114"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.35">
       <c r="J29" s="71"/>
       <c r="K29" s="72"/>
-      <c r="M29" s="137"/>
-      <c r="N29" s="138"/>
+      <c r="M29" s="109"/>
+      <c r="N29" s="110"/>
     </row>
     <row r="30" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J30" s="75"/>
       <c r="K30" s="76"/>
-      <c r="M30" s="139"/>
-      <c r="N30" s="140"/>
+      <c r="M30" s="111"/>
+      <c r="N30" s="112"/>
     </row>
     <row r="31" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="M31" s="141"/>
-      <c r="N31" s="142"/>
+      <c r="M31" s="113"/>
+      <c r="N31" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -12506,18 +12507,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="173" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="98"/>
+      <c r="C2" s="174"/>
+      <c r="D2" s="174"/>
+      <c r="E2" s="174"/>
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="175"/>
       <c r="M2" s="8" t="str">
         <f>HMI!B13</f>
         <v>Vph spike (V) @ disarm</v>
@@ -13321,7 +13322,7 @@
         <v>64</v>
       </c>
       <c r="N16" s="2">
-        <f>HMI!C19</f>
+        <f>HMI!C20</f>
         <v>480</v>
       </c>
       <c r="O16" s="3" t="s">
@@ -13466,11 +13467,11 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M19" s="93" t="s">
+      <c r="M19" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="N19" s="94"/>
-      <c r="O19" s="95"/>
+      <c r="N19" s="171"/>
+      <c r="O19" s="172"/>
       <c r="Q19" t="s">
         <v>20</v>
       </c>
@@ -14343,10 +14344,10 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B3" s="63"/>
-      <c r="C3" s="91" t="s">
+      <c r="C3" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="92"/>
+      <c r="D3" s="159"/>
       <c r="E3" s="64"/>
       <c r="G3" s="70" t="str">
         <f>C5</f>
@@ -14445,8 +14446,8 @@
         <v>12.905000000000001</v>
       </c>
       <c r="E7" s="66"/>
-      <c r="J7" s="115"/>
-      <c r="K7" s="116"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="104"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B8" s="63"/>
@@ -14467,8 +14468,8 @@
         <f>H4</f>
         <v>10.625</v>
       </c>
-      <c r="J8" s="117"/>
-      <c r="K8" s="118"/>
+      <c r="J8" s="105"/>
+      <c r="K8" s="106"/>
     </row>
     <row r="9" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="63"/>
@@ -14494,10 +14495,10 @@
     </row>
     <row r="10" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="63"/>
-      <c r="C10" s="91" t="s">
+      <c r="C10" s="158" t="s">
         <v>242</v>
       </c>
-      <c r="D10" s="92"/>
+      <c r="D10" s="159"/>
       <c r="E10" s="63"/>
       <c r="G10" s="87" t="s">
         <v>248</v>
@@ -14531,10 +14532,10 @@
     </row>
     <row r="12" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="63"/>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="158" t="s">
         <v>246</v>
       </c>
-      <c r="D12" s="92"/>
+      <c r="D12" s="159"/>
       <c r="E12" s="64"/>
       <c r="G12" s="75"/>
       <c r="H12" s="76"/>
@@ -14777,14 +14778,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="176" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
       <c r="I2" s="8" t="s">
         <v>48</v>
       </c>
@@ -15214,7 +15215,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="B1:AC39"/>
+  <dimension ref="B1:Y38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.1796875" style="67" customWidth="1"/>
@@ -15223,8 +15224,8 @@
     <col min="4" max="4" width="20.36328125" style="67" customWidth="1"/>
     <col min="5" max="5" width="3.26953125" style="67" customWidth="1"/>
     <col min="6" max="6" width="3.1796875" style="67" customWidth="1"/>
-    <col min="7" max="7" width="20.81640625" style="67" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.90625" style="67" customWidth="1"/>
+    <col min="7" max="7" width="19.08984375" style="67" customWidth="1"/>
+    <col min="8" max="8" width="8.36328125" style="67" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.1796875" style="67" customWidth="1"/>
     <col min="10" max="10" width="21.26953125" style="67" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.54296875" style="67" customWidth="1"/>
@@ -15261,11 +15262,11 @@
       </c>
       <c r="M2" s="68" t="str">
         <f>G6</f>
-        <v>Rv1 (kΩ)</v>
+        <v>Rv1 (Ω)</v>
       </c>
       <c r="N2" s="69">
         <f>H6</f>
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="P2" s="68" t="str">
         <f t="shared" ref="P2:Q4" si="0">C13</f>
@@ -15278,10 +15279,10 @@
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B3" s="63"/>
-      <c r="C3" s="91" t="s">
+      <c r="C3" s="158" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="92"/>
+      <c r="D3" s="159"/>
       <c r="E3" s="64"/>
       <c r="G3" s="70" t="str">
         <f>C5</f>
@@ -15293,11 +15294,11 @@
       </c>
       <c r="J3" s="70" t="str">
         <f>G6</f>
-        <v>Rv1 (kΩ)</v>
+        <v>Rv1 (Ω)</v>
       </c>
       <c r="K3" s="85">
         <f>H6</f>
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="M3" s="70" t="str">
         <f>C18</f>
@@ -15347,7 +15348,7 @@
       </c>
       <c r="N4" s="88">
         <f>N2*N3/(N3+N2)</f>
-        <v>9.9009900990099009</v>
+        <v>909.09090909090912</v>
       </c>
       <c r="P4" s="70" t="str">
         <f t="shared" si="0"/>
@@ -15370,18 +15371,18 @@
       </c>
       <c r="E5" s="65"/>
       <c r="G5" s="73" t="s">
-        <v>324</v>
-      </c>
-      <c r="H5" s="74">
-        <f>H2*(H3/H4-1)/1000</f>
-        <v>9.6060606060606073</v>
+        <v>330</v>
+      </c>
+      <c r="H5" s="85">
+        <f>H2*(H3/H4-1)</f>
+        <v>9606.0606060606078</v>
       </c>
       <c r="J5" s="79" t="s">
         <v>277</v>
       </c>
       <c r="K5" s="80">
         <f>K2/(K3+K4)*10^3</f>
-        <v>24.950495049504951</v>
+        <v>2.2909090909090915</v>
       </c>
       <c r="M5" s="81"/>
       <c r="N5" s="82"/>
@@ -15405,11 +15406,11 @@
       </c>
       <c r="E6" s="65"/>
       <c r="G6" s="79" t="s">
-        <v>325</v>
-      </c>
-      <c r="H6" s="80">
+        <v>329</v>
+      </c>
+      <c r="H6" s="86">
         <f>_xlfn.MINIFS(DB_R[R (Ω)],DB_R[R (Ω)],"&gt;="&amp;H5)</f>
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="J6" s="81"/>
       <c r="K6" s="82"/>
@@ -15420,10 +15421,10 @@
     </row>
     <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="63"/>
-      <c r="C7" s="91" t="s">
+      <c r="C7" s="158" t="s">
         <v>246</v>
       </c>
-      <c r="D7" s="92"/>
+      <c r="D7" s="159"/>
       <c r="E7" s="63"/>
       <c r="G7" s="81"/>
       <c r="H7" s="82"/>
@@ -15493,7 +15494,7 @@
       </c>
       <c r="K10" s="77">
         <f>H23</f>
-        <v>34.653465346534652</v>
+        <v>3.1818181818181817</v>
       </c>
       <c r="M10" s="75"/>
       <c r="N10" s="76"/>
@@ -15503,7 +15504,7 @@
       </c>
       <c r="Q10" s="85">
         <f>N27</f>
-        <v>9.9009900990099009</v>
+        <v>909.09090909090912</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15519,11 +15520,11 @@
       <c r="E11" s="65"/>
       <c r="G11" s="68" t="str">
         <f>G6</f>
-        <v>Rv1 (kΩ)</v>
+        <v>Rv1 (Ω)</v>
       </c>
       <c r="H11" s="69">
         <f>H6</f>
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="J11" s="70" t="str">
         <f>G24</f>
@@ -15531,7 +15532,7 @@
       </c>
       <c r="K11" s="74">
         <f>H24</f>
-        <v>24.950495049504955</v>
+        <v>2.2909090909090915</v>
       </c>
       <c r="P11" s="70" t="str">
         <f>M28</f>
@@ -15575,7 +15576,7 @@
       </c>
       <c r="N12" s="69">
         <f>N4</f>
-        <v>9.9009900990099009</v>
+        <v>909.09090909090912</v>
       </c>
       <c r="P12" s="70" t="str">
         <f>P5</f>
@@ -15610,7 +15611,7 @@
       </c>
       <c r="K13" s="85">
         <f>K10/K12*1000</f>
-        <v>1050.1050105010502</v>
+        <v>96.418732782369133</v>
       </c>
       <c r="M13" s="70" t="str">
         <f>C20</f>
@@ -15625,7 +15626,7 @@
       </c>
       <c r="Q13" s="83">
         <f>Q9*(Q10+Q11)*(Q12)*10^-3</f>
-        <v>7.7221782178217833</v>
+        <v>169.57636363636365</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -15644,14 +15645,14 @@
       </c>
       <c r="H14" s="86">
         <f>H13^2/(H11+H12)*1000</f>
-        <v>1212.8712871287128</v>
+        <v>111.36363636363636</v>
       </c>
       <c r="J14" s="79" t="s">
         <v>274</v>
       </c>
       <c r="K14" s="86">
         <f>K11/K12*1000</f>
-        <v>756.07560756075623</v>
+        <v>69.421487603305792</v>
       </c>
       <c r="M14" s="70" t="str">
         <f>C22</f>
@@ -15684,18 +15685,18 @@
       </c>
       <c r="N15" s="83">
         <f>1/2/PI()/(N12+N13)/N14/10^-6</f>
-        <v>37.098198135890676</v>
+        <v>1.6893798842138847</v>
       </c>
       <c r="P15" s="71"/>
       <c r="Q15" s="72"/>
     </row>
     <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="64"/>
-      <c r="C16" s="91" t="str">
+      <c r="C16" s="158" t="str">
         <f>HMI!N2</f>
         <v>Rv2 &amp; Rtrace</v>
       </c>
-      <c r="D16" s="92"/>
+      <c r="D16" s="159"/>
       <c r="E16" s="64"/>
       <c r="G16" s="71"/>
       <c r="H16" s="72"/>
@@ -15706,7 +15707,7 @@
       <c r="P16" s="75"/>
       <c r="Q16" s="76"/>
     </row>
-    <row r="17" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="65"/>
       <c r="C17" s="36" t="str">
         <f>HMI!N4</f>
@@ -15724,7 +15725,7 @@
       <c r="M17" s="71"/>
       <c r="N17" s="72"/>
     </row>
-    <row r="18" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="63"/>
       <c r="C18" s="36" t="s">
         <v>255</v>
@@ -15738,18 +15739,8 @@
       <c r="K18" s="72"/>
       <c r="M18" s="75"/>
       <c r="N18" s="76"/>
-      <c r="T18" s="104"/>
-      <c r="U18" s="104"/>
-      <c r="V18" s="104"/>
-      <c r="W18" s="104"/>
-      <c r="X18" s="104"/>
-      <c r="Y18" s="104"/>
-      <c r="Z18" s="104"/>
-      <c r="AA18" s="104"/>
-      <c r="AB18" s="104"/>
-      <c r="AC18" s="104"/>
-    </row>
-    <row r="19" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="63"/>
       <c r="C19" s="36" t="str">
         <f>HMI!N6</f>
@@ -15762,26 +15753,16 @@
       <c r="E19" s="64"/>
       <c r="G19" s="68" t="str">
         <f>G6</f>
-        <v>Rv1 (kΩ)</v>
+        <v>Rv1 (Ω)</v>
       </c>
       <c r="H19" s="69">
         <f>H6</f>
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="J19" s="75"/>
       <c r="K19" s="76"/>
-      <c r="T19" s="104"/>
-      <c r="U19" s="104"/>
-      <c r="V19" s="104"/>
-      <c r="W19" s="104"/>
-      <c r="X19" s="104"/>
-      <c r="Y19" s="104"/>
-      <c r="Z19" s="104"/>
-      <c r="AA19" s="104"/>
-      <c r="AB19" s="104"/>
-      <c r="AC19" s="104"/>
-    </row>
-    <row r="20" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="63"/>
       <c r="C20" s="36" t="s">
         <v>286</v>
@@ -15807,23 +15788,13 @@
         <f>D22</f>
         <v>100</v>
       </c>
-      <c r="T20" s="104"/>
-      <c r="U20" s="104"/>
-      <c r="V20" s="104"/>
-      <c r="W20" s="104"/>
-      <c r="X20" s="104"/>
-      <c r="Y20" s="104"/>
-      <c r="Z20" s="104"/>
-      <c r="AA20" s="104"/>
-      <c r="AB20" s="104"/>
-      <c r="AC20" s="104"/>
-    </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B21" s="63"/>
-      <c r="C21" s="91" t="s">
+      <c r="C21" s="158" t="s">
         <v>269</v>
       </c>
-      <c r="D21" s="92"/>
+      <c r="D21" s="159"/>
       <c r="E21" s="65"/>
       <c r="G21" s="70" t="str">
         <f>C5</f>
@@ -15839,7 +15810,7 @@
       </c>
       <c r="K21" s="77">
         <f>H23</f>
-        <v>34.653465346534652</v>
+        <v>3.1818181818181817</v>
       </c>
       <c r="M21" s="70" t="str">
         <f>C23</f>
@@ -15849,18 +15820,10 @@
         <f>D23</f>
         <v>40</v>
       </c>
-      <c r="T21" s="104"/>
-      <c r="U21" s="104"/>
-      <c r="V21" s="105"/>
-      <c r="W21" s="104"/>
-      <c r="X21" s="104"/>
-      <c r="Y21" s="106"/>
-      <c r="Z21" s="104"/>
-      <c r="AA21" s="104"/>
-      <c r="AB21" s="104"/>
-      <c r="AC21" s="104"/>
-    </row>
-    <row r="22" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="V21" s="93"/>
+      <c r="Y21" s="94"/>
+    </row>
+    <row r="22" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="63"/>
       <c r="C22" s="36" t="str">
         <f>HMI!N29</f>
@@ -15894,18 +15857,10 @@
         <f>N20*(1-N21%)</f>
         <v>60</v>
       </c>
-      <c r="T22" s="104"/>
-      <c r="U22" s="104"/>
-      <c r="V22" s="106"/>
-      <c r="W22" s="104"/>
-      <c r="X22" s="104"/>
-      <c r="Y22" s="107"/>
-      <c r="Z22" s="104"/>
-      <c r="AA22" s="104"/>
-      <c r="AB22" s="104"/>
-      <c r="AC22" s="104"/>
-    </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="V22" s="94"/>
+      <c r="Y22" s="95"/>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B23" s="63"/>
       <c r="C23" s="36" t="str">
         <f>HMI!N30</f>
@@ -15921,7 +15876,7 @@
       </c>
       <c r="H23" s="74">
         <f>H20*H21/(H20+H19)</f>
-        <v>34.653465346534652</v>
+        <v>3.1818181818181817</v>
       </c>
       <c r="J23" s="70" t="str">
         <f>C10</f>
@@ -15933,18 +15888,10 @@
       </c>
       <c r="M23" s="81"/>
       <c r="N23" s="82"/>
-      <c r="T23" s="104"/>
-      <c r="U23" s="104"/>
-      <c r="V23" s="107"/>
-      <c r="W23" s="104"/>
-      <c r="X23" s="104"/>
-      <c r="Y23" s="106"/>
-      <c r="Z23" s="104"/>
-      <c r="AA23" s="104"/>
-      <c r="AB23" s="104"/>
-      <c r="AC23" s="104"/>
-    </row>
-    <row r="24" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="V23" s="95"/>
+      <c r="Y23" s="94"/>
+    </row>
+    <row r="24" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="63"/>
       <c r="C24" s="36" t="str">
         <f>HMI!N31</f>
@@ -15960,7 +15907,7 @@
       </c>
       <c r="H24" s="80">
         <f>H20*H22/(H20+H19)</f>
-        <v>24.950495049504955</v>
+        <v>2.2909090909090915</v>
       </c>
       <c r="J24" s="70" t="str">
         <f>C5</f>
@@ -15972,18 +15919,10 @@
       </c>
       <c r="M24" s="75"/>
       <c r="N24" s="76"/>
-      <c r="T24" s="104"/>
-      <c r="U24" s="104"/>
-      <c r="V24" s="108"/>
-      <c r="W24" s="104"/>
-      <c r="X24" s="104"/>
-      <c r="Y24" s="106"/>
-      <c r="Z24" s="104"/>
-      <c r="AA24" s="104"/>
-      <c r="AB24" s="104"/>
-      <c r="AC24" s="104"/>
-    </row>
-    <row r="25" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="V24" s="96"/>
+      <c r="Y24" s="94"/>
+    </row>
+    <row r="25" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B25" s="63"/>
       <c r="C25" s="36" t="str">
         <f>HMI!N32</f>
@@ -16001,20 +15940,11 @@
       </c>
       <c r="K25" s="83">
         <f>K22/K21/(2^K23-1)*K24*1000</f>
-        <v>13.070588235294117</v>
-      </c>
-      <c r="T25" s="104"/>
-      <c r="U25" s="104"/>
-      <c r="V25" s="104"/>
-      <c r="W25" s="104"/>
-      <c r="X25" s="104"/>
-      <c r="Y25" s="107"/>
-      <c r="Z25" s="104"/>
-      <c r="AA25" s="104"/>
-      <c r="AB25" s="104"/>
-      <c r="AC25" s="104"/>
-    </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.35">
+        <v>142.35294117647058</v>
+      </c>
+      <c r="Y25" s="95"/>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B26" s="63"/>
       <c r="C26" s="63"/>
       <c r="D26" s="63"/>
@@ -16031,21 +15961,12 @@
         <f>D25</f>
         <v>5</v>
       </c>
-      <c r="T26" s="104"/>
-      <c r="U26" s="104"/>
-      <c r="V26" s="104"/>
-      <c r="W26" s="104"/>
-      <c r="X26" s="104"/>
-      <c r="Y26" s="107"/>
-      <c r="Z26" s="104"/>
-      <c r="AA26" s="104"/>
-      <c r="AB26" s="104"/>
-      <c r="AC26" s="104"/>
-    </row>
-    <row r="27" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="Y26" s="95"/>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B27" s="63"/>
-      <c r="C27" s="129"/>
-      <c r="D27" s="129"/>
+      <c r="C27"/>
+      <c r="D27"/>
       <c r="E27" s="63"/>
       <c r="G27" s="71"/>
       <c r="H27" s="72"/>
@@ -16057,20 +15978,11 @@
       </c>
       <c r="N27" s="85">
         <f>N12</f>
-        <v>9.9009900990099009</v>
-      </c>
-      <c r="T27" s="104"/>
-      <c r="U27" s="104"/>
-      <c r="V27" s="104"/>
-      <c r="W27" s="104"/>
-      <c r="X27" s="104"/>
-      <c r="Y27" s="105"/>
-      <c r="Z27" s="104"/>
-      <c r="AA27" s="104"/>
-      <c r="AB27" s="104"/>
-      <c r="AC27" s="104"/>
-    </row>
-    <row r="28" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>909.09090909090912</v>
+      </c>
+      <c r="Y27" s="93"/>
+    </row>
+    <row r="28" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B28" s="63"/>
       <c r="E28" s="63"/>
       <c r="G28" s="71"/>
@@ -16085,18 +15997,8 @@
         <f>N13</f>
         <v>33</v>
       </c>
-      <c r="T28" s="104"/>
-      <c r="U28" s="104"/>
-      <c r="V28" s="104"/>
-      <c r="W28" s="104"/>
-      <c r="X28" s="104"/>
-      <c r="Y28" s="104"/>
-      <c r="Z28" s="104"/>
-      <c r="AA28" s="104"/>
-      <c r="AB28" s="104"/>
-      <c r="AC28" s="104"/>
-    </row>
-    <row r="29" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B29" s="63"/>
       <c r="E29" s="63"/>
       <c r="G29" s="75"/>
@@ -16109,18 +16011,9 @@
         <f>N22</f>
         <v>60</v>
       </c>
-      <c r="T29" s="104"/>
-      <c r="U29" s="104"/>
-      <c r="V29" s="108"/>
-      <c r="W29" s="104"/>
-      <c r="X29" s="104"/>
-      <c r="Y29" s="104"/>
-      <c r="Z29" s="104"/>
-      <c r="AA29" s="104"/>
-      <c r="AB29" s="104"/>
-      <c r="AC29" s="104"/>
-    </row>
-    <row r="30" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="V29" s="96"/>
+    </row>
+    <row r="30" spans="2:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="63"/>
       <c r="E30" s="63"/>
       <c r="M30" s="79" t="s">
@@ -16128,150 +16021,50 @@
       </c>
       <c r="N30" s="83">
         <f>N26*(N27+N28)*N29*10^-3</f>
-        <v>12.870297029702972</v>
-      </c>
-      <c r="T30" s="104"/>
-      <c r="U30" s="104"/>
-      <c r="V30" s="108"/>
-      <c r="W30" s="104"/>
-      <c r="X30" s="104"/>
-      <c r="Y30" s="104"/>
-      <c r="Z30" s="104"/>
-      <c r="AA30" s="104"/>
-      <c r="AB30" s="104"/>
-      <c r="AC30" s="104"/>
-    </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.35">
+        <v>282.62727272727278</v>
+      </c>
+      <c r="V30" s="96"/>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B31" s="63"/>
       <c r="E31" s="63"/>
       <c r="M31" s="81"/>
       <c r="N31" s="82"/>
-      <c r="T31" s="104"/>
-      <c r="U31" s="104"/>
-      <c r="V31" s="108"/>
-      <c r="W31" s="104"/>
-      <c r="X31" s="104"/>
-      <c r="Y31" s="104"/>
-      <c r="Z31" s="104"/>
-      <c r="AA31" s="104"/>
-      <c r="AB31" s="104"/>
-      <c r="AC31" s="104"/>
-    </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="V31" s="96"/>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B32" s="63"/>
       <c r="E32" s="63"/>
       <c r="M32" s="71"/>
       <c r="N32" s="72"/>
-      <c r="T32" s="104"/>
-      <c r="U32" s="104"/>
-      <c r="V32" s="104"/>
-      <c r="W32" s="104"/>
-      <c r="X32" s="104"/>
-      <c r="Y32" s="104"/>
-      <c r="Z32" s="104"/>
-      <c r="AA32" s="104"/>
-      <c r="AB32" s="104"/>
-      <c r="AC32" s="104"/>
-    </row>
-    <row r="33" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B33" s="63"/>
       <c r="E33" s="63"/>
       <c r="M33" s="75"/>
       <c r="N33" s="76"/>
-      <c r="T33" s="104"/>
-      <c r="U33" s="104"/>
-      <c r="V33" s="104"/>
-      <c r="W33" s="104"/>
-      <c r="X33" s="104"/>
-      <c r="Y33" s="104"/>
-      <c r="Z33" s="104"/>
-      <c r="AA33" s="104"/>
-      <c r="AB33" s="104"/>
-      <c r="AC33" s="104"/>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B34" s="63"/>
       <c r="E34" s="63"/>
-      <c r="T34" s="104"/>
-      <c r="U34" s="104"/>
-      <c r="V34" s="104"/>
-      <c r="W34" s="104"/>
-      <c r="X34" s="104"/>
-      <c r="Y34" s="104"/>
-      <c r="Z34" s="104"/>
-      <c r="AA34" s="104"/>
-      <c r="AB34" s="104"/>
-      <c r="AC34" s="104"/>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B35" s="63"/>
       <c r="E35" s="63"/>
-      <c r="T35" s="104"/>
-      <c r="U35" s="104"/>
-      <c r="V35" s="104"/>
-      <c r="W35" s="104"/>
-      <c r="X35" s="104"/>
-      <c r="Y35" s="104"/>
-      <c r="Z35" s="104"/>
-      <c r="AA35" s="104"/>
-      <c r="AB35" s="104"/>
-      <c r="AC35" s="104"/>
-    </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B36" s="63"/>
       <c r="E36" s="63"/>
-      <c r="T36" s="104"/>
-      <c r="U36" s="104"/>
-      <c r="V36" s="104"/>
-      <c r="W36" s="104"/>
-      <c r="X36" s="104"/>
-      <c r="Y36" s="104"/>
-      <c r="Z36" s="104"/>
-      <c r="AA36" s="104"/>
-      <c r="AB36" s="104"/>
-      <c r="AC36" s="104"/>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B37" s="63"/>
       <c r="E37" s="63"/>
-      <c r="T37" s="104"/>
-      <c r="U37" s="104"/>
-      <c r="V37" s="104"/>
-      <c r="W37" s="104"/>
-      <c r="X37" s="104"/>
-      <c r="Y37" s="104"/>
-      <c r="Z37" s="104"/>
-      <c r="AA37" s="104"/>
-      <c r="AB37" s="104"/>
-      <c r="AC37" s="104"/>
-    </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B38" s="63"/>
       <c r="C38" s="63"/>
       <c r="D38" s="63"/>
       <c r="E38" s="63"/>
-      <c r="T38" s="104"/>
-      <c r="U38" s="104"/>
-      <c r="V38" s="104"/>
-      <c r="W38" s="104"/>
-      <c r="X38" s="104"/>
-      <c r="Y38" s="104"/>
-      <c r="Z38" s="104"/>
-      <c r="AA38" s="104"/>
-      <c r="AB38" s="104"/>
-      <c r="AC38" s="104"/>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.35">
-      <c r="T39" s="104"/>
-      <c r="U39" s="104"/>
-      <c r="V39" s="104"/>
-      <c r="W39" s="104"/>
-      <c r="X39" s="104"/>
-      <c r="Y39" s="104"/>
-      <c r="Z39" s="104"/>
-      <c r="AA39" s="104"/>
-      <c r="AB39" s="104"/>
-      <c r="AC39" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -16311,6 +16104,7 @@
     <col min="17" max="18" width="15.08984375" customWidth="1"/>
     <col min="19" max="20" width="17.26953125" customWidth="1"/>
     <col min="21" max="22" width="18.54296875" customWidth="1"/>
+    <col min="24" max="24" width="21.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.35">
@@ -16384,7 +16178,7 @@
         <v>163</v>
       </c>
       <c r="X1" t="s">
-        <v>224</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.35">
@@ -16461,6 +16255,9 @@
         <f>DB_limits[[#This Row],[Iph typ (A)]]*DB_limits[[#This Row],[ToF Iph typ (%)]]%+DB_limits[[#This Row],[Iph max (A@Xs)]]*DB_limits[[#This Row],[ToF Iph max (%)]]%+DB_limits[[#This Row],[Iph spike (A@Xms)]]*DB_limits[[#This Row],[ToF Iph spike (%)]]%</f>
         <v>12.905000000000001</v>
       </c>
+      <c r="X2" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -16536,6 +16333,9 @@
         <f>DB_limits[[#This Row],[Iph typ (A)]]*DB_limits[[#This Row],[ToF Iph typ (%)]]%+DB_limits[[#This Row],[Iph max (A@Xs)]]*DB_limits[[#This Row],[ToF Iph max (%)]]%+DB_limits[[#This Row],[Iph spike (A@Xms)]]*DB_limits[[#This Row],[ToF Iph spike (%)]]%</f>
         <v>12.905000000000001</v>
       </c>
+      <c r="X3" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -16611,6 +16411,9 @@
         <f>DB_limits[[#This Row],[Iph typ (A)]]*DB_limits[[#This Row],[ToF Iph typ (%)]]%+DB_limits[[#This Row],[Iph max (A@Xs)]]*DB_limits[[#This Row],[ToF Iph max (%)]]%+DB_limits[[#This Row],[Iph spike (A@Xms)]]*DB_limits[[#This Row],[ToF Iph spike (%)]]%</f>
         <v>14.625</v>
       </c>
+      <c r="X4" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -16686,6 +16489,9 @@
         <f>DB_limits[[#This Row],[Iph typ (A)]]*DB_limits[[#This Row],[ToF Iph typ (%)]]%+DB_limits[[#This Row],[Iph max (A@Xs)]]*DB_limits[[#This Row],[ToF Iph max (%)]]%+DB_limits[[#This Row],[Iph spike (A@Xms)]]*DB_limits[[#This Row],[ToF Iph spike (%)]]%</f>
         <v>12.905000000000001</v>
       </c>
+      <c r="X5" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -16761,6 +16567,9 @@
         <f>DB_limits[[#This Row],[Iph typ (A)]]*DB_limits[[#This Row],[ToF Iph typ (%)]]%+DB_limits[[#This Row],[Iph max (A@Xs)]]*DB_limits[[#This Row],[ToF Iph max (%)]]%+DB_limits[[#This Row],[Iph spike (A@Xms)]]*DB_limits[[#This Row],[ToF Iph spike (%)]]%</f>
         <v>16.850000000000001</v>
       </c>
+      <c r="X6" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -16835,6 +16644,9 @@
       <c r="W7">
         <f>DB_limits[[#This Row],[Iph typ (A)]]*DB_limits[[#This Row],[ToF Iph typ (%)]]%+DB_limits[[#This Row],[Iph max (A@Xs)]]*DB_limits[[#This Row],[ToF Iph max (%)]]%+DB_limits[[#This Row],[Iph spike (A@Xms)]]*DB_limits[[#This Row],[ToF Iph spike (%)]]%</f>
         <v>14.625</v>
+      </c>
+      <c r="X7" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Kururugi-ESC-calculs.xlsx
+++ b/resources/Kururugi-ESC-calculs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\binon\Desktop\Kururugi-ESC-Dev-Board\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12BFBB8-41B2-4D3F-997D-FD9DE4FA52C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB35476-FF1B-4E9A-8D37-AAAC2894930E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5775" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="783" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
+    <workbookView xWindow="-55" yWindow="-55" windowWidth="19310" windowHeight="10190" tabRatio="783" activeTab="1" xr2:uid="{A7311F5B-F8BB-4208-8795-7C9379CFEF1C}"/>
   </bookViews>
   <sheets>
     <sheet name="HMI" sheetId="6" r:id="rId1"/>
@@ -4561,7 +4561,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
+      <xdr:colOff>390525</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>94355</xdr:rowOff>
     </xdr:to>
@@ -4608,7 +4608,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
+      <xdr:colOff>342900</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>58127</xdr:rowOff>
     </xdr:to>
@@ -4655,7 +4655,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
+      <xdr:colOff>381000</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>112669</xdr:rowOff>
     </xdr:to>
@@ -14312,7 +14312,7 @@
     <col min="7" max="7" width="25.81640625" style="67" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="67" customWidth="1"/>
     <col min="9" max="9" width="3.1796875" style="67" customWidth="1"/>
-    <col min="10" max="10" width="23.26953125" style="67" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.54296875" style="67" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.7265625" style="67" customWidth="1"/>
     <col min="12" max="13" width="8.7265625" style="67"/>
     <col min="14" max="14" width="11.81640625" style="67" bestFit="1" customWidth="1"/>
